--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CED83A92-01AD-456D-B8A3-C2FA243C4A99}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DFA43EA-996D-40BE-BE3C-35083BDCFAA8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="329">
   <si>
     <t>Job</t>
   </si>
@@ -59,9 +59,6 @@
     <t>1084466 - 00057025 - DG Label</t>
   </si>
   <si>
-    <t>1084465 - 00053318 - DG Label</t>
-  </si>
-  <si>
     <t>1084464 - 00050442 - DG Label</t>
   </si>
   <si>
@@ -86,33 +83,15 @@
     <t>9 Kaka Road, Taihape</t>
   </si>
   <si>
-    <t>1084304 - 00053706 - DG Label</t>
-  </si>
-  <si>
     <t>1084171 - 00014163 - DG Label</t>
   </si>
   <si>
-    <t>1084166 - 00020534 - DG Label</t>
-  </si>
-  <si>
-    <t>1084164 - 00045748 - DG Label</t>
-  </si>
-  <si>
-    <t>1084162 - 00035457 - DG Label</t>
-  </si>
-  <si>
-    <t>1933 SH 3, Turakina</t>
-  </si>
-  <si>
     <t>1084156 - 00027186 - DG Label</t>
   </si>
   <si>
     <t>The Lido</t>
   </si>
   <si>
-    <t>1084084 - 00057184 - DG Label</t>
-  </si>
-  <si>
     <t>1084083 - 00057507 - DG Label</t>
   </si>
   <si>
@@ -125,12 +104,6 @@
     <t>1084079 - 00059083 - DG Label</t>
   </si>
   <si>
-    <t>1084060 - 00023511 - DG Label</t>
-  </si>
-  <si>
-    <t>289 Kairanga Bunnythorpe Road</t>
-  </si>
-  <si>
     <t>1084059 - 00051796 - DG Label</t>
   </si>
   <si>
@@ -164,24 +137,12 @@
     <t>49 Weld Street, Martinborough</t>
   </si>
   <si>
-    <t>1083911 - 00055085 - DG Label</t>
-  </si>
-  <si>
-    <t>171 Great North Road, Otamatea</t>
-  </si>
-  <si>
     <t>1083909 - 00051891 - DG Label</t>
   </si>
   <si>
     <t>16 Mersey Street, Rongotea</t>
   </si>
   <si>
-    <t>1083907 - 00044159 - DG Label</t>
-  </si>
-  <si>
-    <t>11 Springwater Drive, Feilding</t>
-  </si>
-  <si>
     <t>1083906 - 00047054 - DG Label</t>
   </si>
   <si>
@@ -212,12 +173,6 @@
     <t>290D Dakins Road, Carterton</t>
   </si>
   <si>
-    <t>1083716 - 00054934 - DG Label</t>
-  </si>
-  <si>
-    <t>57 Somerset Road, Springvale</t>
-  </si>
-  <si>
     <t>1083715 - 00056130 - DG Label</t>
   </si>
   <si>
@@ -272,24 +227,12 @@
     <t>10 Alton Grove, Masterton</t>
   </si>
   <si>
-    <t>1083701 - 00027885 - DG Label</t>
-  </si>
-  <si>
-    <t>110 Port Street East, Feilding</t>
-  </si>
-  <si>
     <t>1083699 - 00059938 - DG Label</t>
   </si>
   <si>
     <t>1009 Taonui Road, Colyton</t>
   </si>
   <si>
-    <t>1083698 - 00051118 - DG Label</t>
-  </si>
-  <si>
-    <t>21 Waharua Place, Tawhero</t>
-  </si>
-  <si>
     <t>1083697 - 00050711 - DG Label</t>
   </si>
   <si>
@@ -302,12 +245,6 @@
     <t>48 Raetihi Ohakune Road, Raetihi</t>
   </si>
   <si>
-    <t>1083656 - 00055415 - DG Label</t>
-  </si>
-  <si>
-    <t>46 Tongariro Street, Castlecliff</t>
-  </si>
-  <si>
     <t>1083539 - 00047551 - DG Label</t>
   </si>
   <si>
@@ -476,12 +413,6 @@
     <t>16 Parkers Road, Carterton</t>
   </si>
   <si>
-    <t>1083187 - 00047452 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Ferndale Place, Feilding</t>
-  </si>
-  <si>
     <t>1083186 - 00051708 - DG Label</t>
   </si>
   <si>
@@ -521,12 +452,6 @@
     <t>20 Langley Avenue, Milson</t>
   </si>
   <si>
-    <t>1083028 - 00033796 - DG Label</t>
-  </si>
-  <si>
-    <t>243 Napier Road, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1083023 - 00022620 - DG Label</t>
   </si>
   <si>
@@ -557,18 +482,6 @@
     <t>429A Black Rock Road, Masterton</t>
   </si>
   <si>
-    <t>1082796 - 00041294 - DG Label</t>
-  </si>
-  <si>
-    <t>27A Parrs Road, Bunnythorpe, 4470</t>
-  </si>
-  <si>
-    <t>1082794 - 00025227 - DG Label</t>
-  </si>
-  <si>
-    <t>1C WYNDHAM STREET, ASHHURST, 4810</t>
-  </si>
-  <si>
     <t>1082793 - 00047634 - DG Label</t>
   </si>
   <si>
@@ -686,21 +599,6 @@
     <t>1082300 - 00046363 - DG Label</t>
   </si>
   <si>
-    <t>1082226 - 00041473 - DG Label</t>
-  </si>
-  <si>
-    <t>1082225 - 00051233 - DG Label</t>
-  </si>
-  <si>
-    <t>7 OAK CRES, ASHHURST</t>
-  </si>
-  <si>
-    <t>1082224 - 00052577 - DG Label</t>
-  </si>
-  <si>
-    <t>1055 VALLEY RD, ASHHURST</t>
-  </si>
-  <si>
     <t>1082166 - 00052136 - DG Label</t>
   </si>
   <si>
@@ -797,18 +695,6 @@
     <t>34 Jellicoe Street, Martinborough</t>
   </si>
   <si>
-    <t>1082676 - 00055845 - DG Label - 0000022362CPC8E</t>
-  </si>
-  <si>
-    <t>346 Botanical Road, Palmerston North</t>
-  </si>
-  <si>
-    <t>1082649 - 00040553 - DG Label -0900085009PC066</t>
-  </si>
-  <si>
-    <t>14 PARNELL HEIGHTS DRIVE , KELVIN GROVE, PALMERSTON NORTH, 4414</t>
-  </si>
-  <si>
     <t>1082613 - 00037301  - DG Label - 0068841000WR999</t>
   </si>
   <si>
@@ -887,12 +773,6 @@
     <t>2 VISCOUNT PLACE, WEST END, PALMERSTON NORTH, 4412</t>
   </si>
   <si>
-    <t>1082566 - 00030742 - DG Label - 0000053096CP589</t>
-  </si>
-  <si>
-    <t>9 PUKETIRO DRIVE, FEILDING, 4702</t>
-  </si>
-  <si>
     <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
   </si>
   <si>
@@ -935,12 +815,6 @@
     <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
   </si>
   <si>
-    <t>1082499 - 00052869 - DG Label - 0900090812PCBD3</t>
-  </si>
-  <si>
-    <t>4 STONEBRIDGE HEIGHTS, FEILDING, 4702</t>
-  </si>
-  <si>
     <t>1082492 - 00055639 - DG Label - 0000037890CP0D3</t>
   </si>
   <si>
@@ -968,36 +842,12 @@
     <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
   </si>
   <si>
-    <t>1082475 - 00050997 - DG Label - 0900090099PC040</t>
-  </si>
-  <si>
-    <t>45A SHERWILL STREET EAST, FEILDING, 4702</t>
-  </si>
-  <si>
-    <t>1082462 - 00057612 - DG Label - 1000564472PC01D</t>
-  </si>
-  <si>
-    <t>17 Wescombe Grove, Feilding, 4702</t>
-  </si>
-  <si>
-    <t>1082460 - 00055909 - DG Label - 0000042708CPFB6</t>
-  </si>
-  <si>
-    <t>27 RAILWAY ROAD, PALMERSTON NORTH</t>
-  </si>
-  <si>
     <t>1082458 - 00054943 - DG Label - 1000624687PC063</t>
   </si>
   <si>
     <t>8 Sardinia Grove, Fitzherbert, Palmerston North</t>
   </si>
   <si>
-    <t>1082457 - 00047081 - DG Label - 0000022942CPBD1</t>
-  </si>
-  <si>
-    <t>15 CARDIFF STREET, AWAPUNI, PALMERSTON NORTH, 4412</t>
-  </si>
-  <si>
     <t>1082455 - 00044025 - DG Label - 1000621883PC042</t>
   </si>
   <si>
@@ -1034,9 +884,6 @@
     <t>231 Valley Views, Palmerston North</t>
   </si>
   <si>
-    <t>326 Creek Road, Whanganui</t>
-  </si>
-  <si>
     <t>99A Lees Pakaraka Road, Masterton</t>
   </si>
   <si>
@@ -1049,18 +896,6 @@
     <t>89 Dublin Street, Martinborough</t>
   </si>
   <si>
-    <t>15 Wapiti Avenue, Feilding</t>
-  </si>
-  <si>
-    <t>10 Tangaroa View, Whanganui</t>
-  </si>
-  <si>
-    <t>21 Waipounamu Street, Whanganui</t>
-  </si>
-  <si>
-    <t>49 Hereford Street, Whanganui</t>
-  </si>
-  <si>
     <t>1853 Rongotea Road, Rongotea</t>
   </si>
   <si>
@@ -1076,9 +911,6 @@
     <t>46A Main Street, Greytown</t>
   </si>
   <si>
-    <t>44 LINCOLN STREET, Ashhurst</t>
-  </si>
-  <si>
     <t>95 Pyke Road, Rangitou</t>
   </si>
   <si>
@@ -1109,18 +941,6 @@
     <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
   </si>
   <si>
-    <t>1084695 - 00062451 - DG Label</t>
-  </si>
-  <si>
-    <t>10 Webster Place, Otamatea</t>
-  </si>
-  <si>
-    <t>677 Rapanui Road, Wanganui</t>
-  </si>
-  <si>
-    <t>1084696 - 00059596 - DG Label</t>
-  </si>
-  <si>
     <t>45D Brandon Street, Featherston</t>
   </si>
   <si>
@@ -1151,12 +971,6 @@
     <t>1084703 - 00056419 - DG Label</t>
   </si>
   <si>
-    <t>163 Nannestads Line, Feilding</t>
-  </si>
-  <si>
-    <t>1084704 - 00063979 - DG Label</t>
-  </si>
-  <si>
     <t>37 Pukenaua Road, Taihape</t>
   </si>
   <si>
@@ -1172,12 +986,6 @@
     <t>1084709 - 00022620 - DG Label</t>
   </si>
   <si>
-    <t>Aerowork Airport Road, Whanganui</t>
-  </si>
-  <si>
-    <t>1084710 - 233751 - DG Label</t>
-  </si>
-  <si>
     <t>37 Fry Road, Halcombe</t>
   </si>
   <si>
@@ -1212,12 +1020,6 @@
   </si>
   <si>
     <t>1084779 - 00048369 - DG Label</t>
-  </si>
-  <si>
-    <t>75 Somerset Road, Springvale</t>
-  </si>
-  <si>
-    <t>1084780 - 00050330 - DG Label</t>
   </si>
   <si>
     <t>5 Pukeko Place, Riversdale Beach</t>
@@ -1604,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C197"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -1620,2163 +1422,1800 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>329</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
       <c r="B3" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="B9" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="B10" t="s">
-        <v>269</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="B11" t="s">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="B12" t="s">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="C12" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="B14" t="s">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="B16" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="C19" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>290</v>
+        <v>256</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>257</v>
       </c>
       <c r="C21" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="B22" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="C23" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>263</v>
       </c>
       <c r="C24" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="C25" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C26" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="C27" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="C28" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="C29" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s">
-        <v>355</v>
+        <v>274</v>
       </c>
       <c r="C30" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C31" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C32" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>313</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>314</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>315</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>316</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>317</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>318</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>319</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>320</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="B37" t="s">
-        <v>322</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>324</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>325</v>
+        <v>162</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B40" t="s">
-        <v>353</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B42" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C42" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="B43" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C43" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C44" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B45" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="C47" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="C51" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C52" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C53" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B54" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C54" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
-        <v>352</v>
+        <v>193</v>
       </c>
       <c r="C55" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C56" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="B57" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C57" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C58" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C59" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s">
-        <v>345</v>
+        <v>203</v>
       </c>
       <c r="C60" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C61" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C62" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B63" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C63" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B64" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="C64" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B65" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="C65" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B67" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="C67" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>231</v>
+        <v>278</v>
       </c>
       <c r="C68" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>233</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>235</v>
+        <v>280</v>
       </c>
       <c r="C70" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="C71" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>238</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="C72" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="C73" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="C74" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>244</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>247</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>249</v>
-      </c>
-      <c r="C77" t="s">
-        <v>326</v>
+        <v>284</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="B78" t="s">
-        <v>251</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>328</v>
+        <v>294</v>
       </c>
       <c r="C79" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>285</v>
       </c>
       <c r="C80" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>330</v>
+        <v>286</v>
       </c>
       <c r="C81" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>332</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B84" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="C85" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B86" t="s">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="C86" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C87" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C88" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>336</v>
+        <v>31</v>
       </c>
       <c r="C89" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>327</v>
+        <v>33</v>
+      </c>
+      <c r="C90" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>337</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>327</v>
+        <v>35</v>
+      </c>
+      <c r="C91" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B92" t="s">
-        <v>338</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C93" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B94" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C94" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>339</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B96" t="s">
-        <v>350</v>
+        <v>45</v>
       </c>
       <c r="C96" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B97" t="s">
-        <v>340</v>
+        <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
-        <v>341</v>
+        <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B99" t="s">
-        <v>342</v>
+        <v>51</v>
       </c>
       <c r="C99" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B100" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B101" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C102" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B103" t="s">
-        <v>348</v>
+        <v>59</v>
       </c>
       <c r="C103" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B104" t="s">
-        <v>349</v>
+        <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="B105" t="s">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="C105" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C106" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>39</v>
-      </c>
-      <c r="B107" t="s">
-        <v>40</v>
-      </c>
-      <c r="C107" t="s">
-        <v>326</v>
+      <c r="A107" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B108" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C108" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C109" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B110" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C110" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C112" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B113" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C113" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C114" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C115" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="B116" t="s">
-        <v>58</v>
+        <v>289</v>
       </c>
       <c r="C116" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B117" t="s">
-        <v>60</v>
+        <v>291</v>
       </c>
       <c r="C117" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B118" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C118" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B119" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C119" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B120" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C120" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C121" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="C122" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C123" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="B124" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C124" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C125" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B126" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C126" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B127" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C127" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B128" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C128" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B129" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C129" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>326</v>
+      <c r="A130" t="s">
+        <v>110</v>
+      </c>
+      <c r="B130" t="s">
+        <v>111</v>
+      </c>
+      <c r="C130" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B131" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C131" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="B132" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C132" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="B133" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C133" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B134" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C134" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B135" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C135" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B136" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C136" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B137" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C137" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B138" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C138" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B139" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="C139" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="B140" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="C140" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="B141" t="s">
-        <v>347</v>
+        <v>132</v>
       </c>
       <c r="C141" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B142" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C142" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B143" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C143" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B144" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C144" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="B145" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B146" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C146" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C147" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C149" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>123</v>
+        <v>314</v>
       </c>
       <c r="B150" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C150" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>125</v>
+        <v>313</v>
       </c>
       <c r="B151" t="s">
-        <v>126</v>
+        <v>312</v>
       </c>
       <c r="C151" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="B152" t="s">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="C152" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>129</v>
+        <v>309</v>
       </c>
       <c r="B153" t="s">
-        <v>130</v>
+        <v>308</v>
       </c>
       <c r="C153" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>131</v>
+        <v>307</v>
       </c>
       <c r="B154" t="s">
-        <v>132</v>
+        <v>306</v>
       </c>
       <c r="C154" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>133</v>
+        <v>305</v>
       </c>
       <c r="B155" t="s">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="C155" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="B156" t="s">
-        <v>136</v>
+        <v>302</v>
       </c>
       <c r="C156" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="B157" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C157" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>139</v>
+        <v>328</v>
       </c>
       <c r="B158" t="s">
-        <v>140</v>
+        <v>327</v>
       </c>
       <c r="C158" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>141</v>
+        <v>326</v>
       </c>
       <c r="B159" t="s">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="C159" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>143</v>
+        <v>324</v>
       </c>
       <c r="B160" t="s">
-        <v>144</v>
+        <v>323</v>
       </c>
       <c r="C160" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>145</v>
+        <v>322</v>
       </c>
       <c r="B161" t="s">
-        <v>146</v>
+        <v>321</v>
       </c>
       <c r="C161" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>147</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>148</v>
+        <v>319</v>
       </c>
       <c r="C162" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>149</v>
+        <v>318</v>
       </c>
       <c r="B163" t="s">
-        <v>150</v>
+        <v>317</v>
       </c>
       <c r="C163" t="s">
-        <v>326</v>
+        <v>276</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>151</v>
+        <v>316</v>
       </c>
       <c r="B164" t="s">
-        <v>152</v>
+        <v>315</v>
       </c>
       <c r="C164" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>153</v>
-      </c>
-      <c r="B165" t="s">
-        <v>346</v>
-      </c>
-      <c r="C165" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>154</v>
-      </c>
-      <c r="B166" t="s">
-        <v>155</v>
-      </c>
-      <c r="C166" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>156</v>
-      </c>
-      <c r="B167" t="s">
-        <v>157</v>
-      </c>
-      <c r="C167" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>158</v>
-      </c>
-      <c r="B168" t="s">
-        <v>159</v>
-      </c>
-      <c r="C168" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>160</v>
-      </c>
-      <c r="B169" t="s">
-        <v>161</v>
-      </c>
-      <c r="C169" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>162</v>
-      </c>
-      <c r="B170" t="s">
-        <v>163</v>
-      </c>
-      <c r="C170" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>164</v>
-      </c>
-      <c r="B171" t="s">
-        <v>165</v>
-      </c>
-      <c r="C171" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>166</v>
-      </c>
-      <c r="B172" t="s">
-        <v>167</v>
-      </c>
-      <c r="C172" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>168</v>
-      </c>
-      <c r="B173" t="s">
-        <v>169</v>
-      </c>
-      <c r="C173" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>170</v>
-      </c>
-      <c r="B174" t="s">
-        <v>171</v>
-      </c>
-      <c r="C174" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>172</v>
-      </c>
-      <c r="B175" t="s">
-        <v>173</v>
-      </c>
-      <c r="C175" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>174</v>
-      </c>
-      <c r="B176" t="s">
-        <v>175</v>
-      </c>
-      <c r="C176" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>176</v>
-      </c>
-      <c r="B177" t="s">
-        <v>177</v>
-      </c>
-      <c r="C177" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>378</v>
-      </c>
-      <c r="B178" t="s">
-        <v>377</v>
-      </c>
-      <c r="C178" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>376</v>
-      </c>
-      <c r="B179" t="s">
-        <v>163</v>
-      </c>
-      <c r="C179" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>375</v>
-      </c>
-      <c r="B180" t="s">
-        <v>374</v>
-      </c>
-      <c r="C180" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>373</v>
-      </c>
-      <c r="B181" t="s">
-        <v>372</v>
-      </c>
-      <c r="C181" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>371</v>
-      </c>
-      <c r="B182" t="s">
-        <v>370</v>
-      </c>
-      <c r="C182" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>369</v>
-      </c>
-      <c r="B183" t="s">
-        <v>368</v>
-      </c>
-      <c r="C183" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>367</v>
-      </c>
-      <c r="B184" t="s">
-        <v>366</v>
-      </c>
-      <c r="C184" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>365</v>
-      </c>
-      <c r="B185" t="s">
-        <v>364</v>
-      </c>
-      <c r="C185" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>363</v>
-      </c>
-      <c r="B186" t="s">
-        <v>362</v>
-      </c>
-      <c r="C186" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>361</v>
-      </c>
-      <c r="B187" t="s">
-        <v>360</v>
-      </c>
-      <c r="C187" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>359</v>
-      </c>
-      <c r="B188" t="s">
-        <v>358</v>
-      </c>
-      <c r="C188" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>356</v>
-      </c>
-      <c r="B189" t="s">
-        <v>357</v>
-      </c>
-      <c r="C189" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>394</v>
-      </c>
-      <c r="B190" t="s">
-        <v>393</v>
-      </c>
-      <c r="C190" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>392</v>
-      </c>
-      <c r="B191" t="s">
-        <v>391</v>
-      </c>
-      <c r="C191" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>390</v>
-      </c>
-      <c r="B192" t="s">
-        <v>389</v>
-      </c>
-      <c r="C192" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>388</v>
-      </c>
-      <c r="B193" t="s">
-        <v>387</v>
-      </c>
-      <c r="C193" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>386</v>
-      </c>
-      <c r="B194" t="s">
-        <v>385</v>
-      </c>
-      <c r="C194" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>384</v>
-      </c>
-      <c r="B195" t="s">
-        <v>383</v>
-      </c>
-      <c r="C195" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>382</v>
-      </c>
-      <c r="B196" t="s">
-        <v>381</v>
-      </c>
-      <c r="C196" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>380</v>
-      </c>
-      <c r="B197" t="s">
-        <v>379</v>
-      </c>
-      <c r="C197" t="s">
-        <v>327</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DFA43EA-996D-40BE-BE3C-35083BDCFAA8}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B15212CD-8CAC-437C-AB06-F3738C8EB622}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="353">
   <si>
     <t>Job</t>
   </si>
@@ -1026,6 +1026,78 @@
   </si>
   <si>
     <t>1084781 - 00059954 - DG Label</t>
+  </si>
+  <si>
+    <t>1244A Rangitikei Line, Kauwhata</t>
+  </si>
+  <si>
+    <t>1085276 - 00054364 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Millennium Way, Feilding</t>
+  </si>
+  <si>
+    <t>1085277 - 00061586 - DG Label</t>
+  </si>
+  <si>
+    <t>64A Thomas Road, Carrington</t>
+  </si>
+  <si>
+    <t>1085279 - 00063713 - DG Label</t>
+  </si>
+  <si>
+    <t>220 Somerset Road, Carterton</t>
+  </si>
+  <si>
+    <t>1085281 - 00063711 - DG Label</t>
+  </si>
+  <si>
+    <t>788 Tangimoana Road, Ōhakea</t>
+  </si>
+  <si>
+    <t>1085282 - 00063388 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Tangaroa View, Otamatea</t>
+  </si>
+  <si>
+    <t>1085283 - 00062392 - DG Label</t>
+  </si>
+  <si>
+    <t>142 West Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085285 - 00054784 - DG Label</t>
+  </si>
+  <si>
+    <t>40 Ruapehu Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085286 - 00056531 - DG Label</t>
+  </si>
+  <si>
+    <t>5B Blennerville Close, Marton</t>
+  </si>
+  <si>
+    <t>1085287 - 00056035 - DG Label</t>
+  </si>
+  <si>
+    <t>40 Campbell Place, Marton</t>
+  </si>
+  <si>
+    <t>1085288 - 00052613 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Barracks Avenue, Solway</t>
+  </si>
+  <si>
+    <t>1085290 - 00059953 - DG Label</t>
+  </si>
+  <si>
+    <t>1965B State Highway 2, Greytown</t>
+  </si>
+  <si>
+    <t>1085291 - 00059958 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3218,6 +3290,138 @@
         <v>277</v>
       </c>
     </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>352</v>
+      </c>
+      <c r="B165" t="s">
+        <v>351</v>
+      </c>
+      <c r="C165" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>350</v>
+      </c>
+      <c r="B166" t="s">
+        <v>349</v>
+      </c>
+      <c r="C166" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>348</v>
+      </c>
+      <c r="B167" t="s">
+        <v>347</v>
+      </c>
+      <c r="C167" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>346</v>
+      </c>
+      <c r="B168" t="s">
+        <v>345</v>
+      </c>
+      <c r="C168" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>344</v>
+      </c>
+      <c r="B169" t="s">
+        <v>343</v>
+      </c>
+      <c r="C169" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>342</v>
+      </c>
+      <c r="B170" t="s">
+        <v>341</v>
+      </c>
+      <c r="C170" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>338</v>
+      </c>
+      <c r="B172" t="s">
+        <v>337</v>
+      </c>
+      <c r="C172" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>336</v>
+      </c>
+      <c r="B173" t="s">
+        <v>335</v>
+      </c>
+      <c r="C173" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>334</v>
+      </c>
+      <c r="B174" t="s">
+        <v>333</v>
+      </c>
+      <c r="C174" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>332</v>
+      </c>
+      <c r="B175" t="s">
+        <v>331</v>
+      </c>
+      <c r="C175" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>330</v>
+      </c>
+      <c r="B176" t="s">
+        <v>329</v>
+      </c>
+      <c r="C176" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B15212CD-8CAC-437C-AB06-F3738C8EB622}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD6A732-98E4-4CE5-B221-B716FD9955FA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="367">
   <si>
     <t>Job</t>
   </si>
@@ -1098,6 +1098,48 @@
   </si>
   <si>
     <t>1085291 - 00059958 - DG Label</t>
+  </si>
+  <si>
+    <t>1085378 - 00050724 - DG Label</t>
+  </si>
+  <si>
+    <t>51A Southdown Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>1085377 - 00052076 - DG Label</t>
+  </si>
+  <si>
+    <t>8C Michael Street, Masterton</t>
+  </si>
+  <si>
+    <t>1085376 - 00064756 - DG Label</t>
+  </si>
+  <si>
+    <t>6A Garrity Lane, Greytown</t>
+  </si>
+  <si>
+    <t>1085373 - 00037564 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Kowhai Street, Castelcliff</t>
+  </si>
+  <si>
+    <t>1085371 - 00053149 - DG Label</t>
+  </si>
+  <si>
+    <t>56 Willoughby Street, Halcombe</t>
+  </si>
+  <si>
+    <t>1085370 - 00061230 - DG Label</t>
+  </si>
+  <si>
+    <t>130 Mount Biggs Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1085369 - 00053697 - DG Label</t>
+  </si>
+  <si>
+    <t>121 Taikorea Road, Glen Oroua</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C176"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3422,6 +3464,83 @@
         <v>276</v>
       </c>
     </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>353</v>
+      </c>
+      <c r="B177" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B178" t="s">
+        <v>356</v>
+      </c>
+      <c r="C178" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>357</v>
+      </c>
+      <c r="B179" t="s">
+        <v>358</v>
+      </c>
+      <c r="C179" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>359</v>
+      </c>
+      <c r="B180" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>361</v>
+      </c>
+      <c r="B181" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" t="s">
+        <v>276</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD6A732-98E4-4CE5-B221-B716FD9955FA}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE64BFAB-F577-4249-A9EA-FF99EB5F363D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="359">
   <si>
     <t>Job</t>
   </si>
@@ -68,9 +68,6 @@
     <t>1084461 - 00050984 - DG Label</t>
   </si>
   <si>
-    <t>1084460 - 00053371 - DG Label</t>
-  </si>
-  <si>
     <t>1084307 - 00059085 - DG Label</t>
   </si>
   <si>
@@ -383,12 +380,6 @@
     <t>142A Dublin Street, Martinborough</t>
   </si>
   <si>
-    <t>1083505 - 00056798 - DG Label</t>
-  </si>
-  <si>
-    <t>12 Campbell Drive, Martinborough</t>
-  </si>
-  <si>
     <t>1083503 - 00055234 - DG Label</t>
   </si>
   <si>
@@ -497,12 +488,6 @@
     <t>56 FREDERICK ST, CARTERTON</t>
   </si>
   <si>
-    <t>1082790 - 00033944 - DG Label</t>
-  </si>
-  <si>
-    <t>214A Dry River Road, Dyerville</t>
-  </si>
-  <si>
     <t>1082789 - 00029633 - DG Label</t>
   </si>
   <si>
@@ -641,12 +626,6 @@
     <t>11 Moore Street, Featherston</t>
   </si>
   <si>
-    <t>1081143 - 00042916 - DG Label</t>
-  </si>
-  <si>
-    <t>12 Cherry Lane, Martinborough</t>
-  </si>
-  <si>
     <t>1081142 - 00042583 - DG Label</t>
   </si>
   <si>
@@ -924,9 +903,6 @@
   </si>
   <si>
     <t>3 Paterson Lane, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>26 Romina Way, Martinborough</t>
   </si>
   <si>
     <t>Nga Waka Winery, Martinborough</t>
@@ -1520,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -1536,1932 +1512,1932 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B19" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="B23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C23" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C26" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B28" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C31" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B32" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C32" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>288</v>
       </c>
       <c r="C46" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>296</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B49" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C49" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C50" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B52" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C52" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B54" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C55" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C57" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B58" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C58" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C59" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B63" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>214</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>271</v>
       </c>
       <c r="C66" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C68" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C71" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>282</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>283</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>295</v>
-      </c>
-      <c r="C74" t="s">
         <v>277</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>287</v>
       </c>
       <c r="C76" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>284</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="C77" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>279</v>
       </c>
       <c r="C78" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C79" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>286</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C82" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="C83" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>292</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>293</v>
+        <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C87" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C89" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B90" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B95" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C97" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B99" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B100" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C100" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B101" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C102" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>60</v>
-      </c>
-      <c r="B104" t="s">
-        <v>61</v>
-      </c>
-      <c r="C104" t="s">
-        <v>277</v>
+      <c r="A104" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B105" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C105" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C106" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>276</v>
+      <c r="A107" t="s">
+        <v>71</v>
+      </c>
+      <c r="B107" t="s">
+        <v>72</v>
+      </c>
+      <c r="C107" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B108" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B109" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C109" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B111" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C112" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>79</v>
+        <v>282</v>
       </c>
       <c r="C113" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="C114" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B115" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B116" t="s">
-        <v>289</v>
+        <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B117" t="s">
-        <v>291</v>
+        <v>90</v>
       </c>
       <c r="C117" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C119" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B120" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C120" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B122" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B123" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B124" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B125" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B126" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C126" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B127" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C127" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B128" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B129" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C129" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B131" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C131" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B132" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C133" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B134" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C134" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B135" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C135" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B136" t="s">
-        <v>123</v>
+        <v>283</v>
       </c>
       <c r="C136" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B137" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C137" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B138" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C138" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B139" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B140" t="s">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="C140" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C141" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C142" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C144" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>141</v>
+        <v>306</v>
       </c>
       <c r="B146" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C146" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>143</v>
+        <v>305</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="C147" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>302</v>
       </c>
       <c r="C148" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>300</v>
       </c>
       <c r="C149" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B150" t="s">
-        <v>138</v>
+        <v>298</v>
       </c>
       <c r="C150" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B151" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B152" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="B153" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C154" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="C155" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B156" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="C156" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B157" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C157" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="C158" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C159" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B160" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C160" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="B161" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C161" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="B162" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C162" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B163" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C163" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="B164" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C164" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B165" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C165" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B166" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C166" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B167" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="C167" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="B168" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="C168" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B169" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="C169" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="B170" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="C170" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C171" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="B172" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C172" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B173" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C173" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B174" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C174" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B175" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C175" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="B176" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C176" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3472,7 +3448,7 @@
         <v>354</v>
       </c>
       <c r="C177" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3483,7 +3459,7 @@
         <v>356</v>
       </c>
       <c r="C178" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3494,51 +3470,7 @@
         <v>358</v>
       </c>
       <c r="C179" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>359</v>
-      </c>
-      <c r="B180" t="s">
-        <v>360</v>
-      </c>
-      <c r="C180" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>361</v>
-      </c>
-      <c r="B181" t="s">
-        <v>362</v>
-      </c>
-      <c r="C181" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>363</v>
-      </c>
-      <c r="B182" t="s">
-        <v>364</v>
-      </c>
-      <c r="C182" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>365</v>
-      </c>
-      <c r="B183" t="s">
-        <v>366</v>
-      </c>
-      <c r="C183" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE64BFAB-F577-4249-A9EA-FF99EB5F363D}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7284FF-052E-471C-B7A7-A8973B5C7845}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="365">
   <si>
     <t>Job</t>
   </si>
@@ -1116,6 +1116,24 @@
   </si>
   <si>
     <t>121 Taikorea Road, Glen Oroua</t>
+  </si>
+  <si>
+    <t>1085457 - 00055046 - DG Label</t>
+  </si>
+  <si>
+    <t>63 Otawa Drive, Carterton</t>
+  </si>
+  <si>
+    <t>1085460 - 00026995 - DG Label</t>
+  </si>
+  <si>
+    <t>73 Young Street, Whanganui East</t>
+  </si>
+  <si>
+    <t>1085458 - 00044870 - DG Label</t>
+  </si>
+  <si>
+    <t>70B Duddings Lane, Featherson</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C179"/>
+  <dimension ref="A1:C182"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3473,6 +3491,39 @@
         <v>269</v>
       </c>
     </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>359</v>
+      </c>
+      <c r="B180" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>361</v>
+      </c>
+      <c r="B181" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA7284FF-052E-471C-B7A7-A8973B5C7845}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D751C798-9842-41FC-9857-15A61752D38E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="383">
   <si>
     <t>Job</t>
   </si>
@@ -1134,13 +1134,67 @@
   </si>
   <si>
     <t>70B Duddings Lane, Featherson</t>
+  </si>
+  <si>
+    <t>1085533 - 00050342 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Whisky Way, Aokautere</t>
+  </si>
+  <si>
+    <t>1085531 - 00056810 - DG Label</t>
+  </si>
+  <si>
+    <t>289A Fabians Road, Greytown</t>
+  </si>
+  <si>
+    <t>1085529 - 00052073 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Valkyrie Close, Carterton</t>
+  </si>
+  <si>
+    <t>1085528 - 00052070 - DG Label</t>
+  </si>
+  <si>
+    <t>72 Jellicoe Street, Greytown</t>
+  </si>
+  <si>
+    <t>1085526 - 00052065 - DG Label</t>
+  </si>
+  <si>
+    <t>966 Kahutara Road, Kahutara</t>
+  </si>
+  <si>
+    <t>1085525 - 00050727 - DG Label</t>
+  </si>
+  <si>
+    <t>138 Loop Line, Opaki</t>
+  </si>
+  <si>
+    <t>1085524 - 00050503 - DG Label</t>
+  </si>
+  <si>
+    <t>29 Harrison Street West, Featherston</t>
+  </si>
+  <si>
+    <t>1085522 - 00050476 - DG Label</t>
+  </si>
+  <si>
+    <t>194 Kiriwhakapapa Road, Masterton</t>
+  </si>
+  <si>
+    <t>1085521 - 00048180 - DG Label</t>
+  </si>
+  <si>
+    <t>49 Wards Line, Greytown</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1514,15 +1568,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C182"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C191"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1533,7 +1587,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>211</v>
       </c>
@@ -1544,7 +1598,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -1555,7 +1609,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -1566,7 +1620,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -1577,7 +1631,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>219</v>
       </c>
@@ -1588,7 +1642,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -1599,7 +1653,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -1610,7 +1664,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>225</v>
       </c>
@@ -1621,7 +1675,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>227</v>
       </c>
@@ -1632,7 +1686,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>229</v>
       </c>
@@ -1643,7 +1697,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>231</v>
       </c>
@@ -1654,7 +1708,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>233</v>
       </c>
@@ -1665,7 +1719,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>235</v>
       </c>
@@ -1676,7 +1730,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>237</v>
       </c>
@@ -1687,7 +1741,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>239</v>
       </c>
@@ -1698,7 +1752,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>241</v>
       </c>
@@ -1709,7 +1763,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>243</v>
       </c>
@@ -1720,7 +1774,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>245</v>
       </c>
@@ -1731,7 +1785,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -1742,7 +1796,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>249</v>
       </c>
@@ -1753,7 +1807,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>251</v>
       </c>
@@ -1764,7 +1818,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>253</v>
       </c>
@@ -1775,7 +1829,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -1786,7 +1840,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>257</v>
       </c>
@@ -1797,7 +1851,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>259</v>
       </c>
@@ -1808,7 +1862,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>260</v>
       </c>
@@ -1819,7 +1873,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>262</v>
       </c>
@@ -1830,7 +1884,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>264</v>
       </c>
@@ -1841,7 +1895,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>266</v>
       </c>
@@ -1852,7 +1906,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>268</v>
       </c>
@@ -1863,7 +1917,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>146</v>
       </c>
@@ -1874,7 +1928,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -1885,7 +1939,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -1896,7 +1950,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -1907,7 +1961,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -1918,7 +1972,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -1929,7 +1983,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -1940,7 +1994,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>159</v>
       </c>
@@ -1951,7 +2005,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -1962,7 +2016,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -1973,7 +2027,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3">
       <c r="A42" t="s">
         <v>165</v>
       </c>
@@ -1984,7 +2038,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -1995,7 +2049,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>169</v>
       </c>
@@ -2006,7 +2060,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3">
       <c r="A45" t="s">
         <v>171</v>
       </c>
@@ -2017,7 +2071,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3">
       <c r="A46" t="s">
         <v>173</v>
       </c>
@@ -2028,7 +2082,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>174</v>
       </c>
@@ -2039,7 +2093,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>176</v>
       </c>
@@ -2050,7 +2104,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>178</v>
       </c>
@@ -2061,7 +2115,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>180</v>
       </c>
@@ -2072,7 +2126,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>181</v>
       </c>
@@ -2083,7 +2137,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -2094,7 +2148,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>185</v>
       </c>
@@ -2105,7 +2159,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3">
       <c r="A54" t="s">
         <v>187</v>
       </c>
@@ -2116,7 +2170,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>189</v>
       </c>
@@ -2127,7 +2181,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>191</v>
       </c>
@@ -2138,7 +2192,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>193</v>
       </c>
@@ -2149,7 +2203,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3">
       <c r="A58" t="s">
         <v>195</v>
       </c>
@@ -2160,7 +2214,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -2171,7 +2225,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -2182,7 +2236,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="A61" t="s">
         <v>201</v>
       </c>
@@ -2193,7 +2247,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="A62" t="s">
         <v>203</v>
       </c>
@@ -2204,7 +2258,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="A63" t="s">
         <v>205</v>
       </c>
@@ -2215,7 +2269,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="A64" t="s">
         <v>207</v>
       </c>
@@ -2226,7 +2280,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3">
       <c r="A65" t="s">
         <v>209</v>
       </c>
@@ -2237,7 +2291,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2248,7 +2302,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -2259,7 +2313,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2270,7 +2324,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2281,7 +2335,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -2292,7 +2346,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2303,7 +2357,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -2314,7 +2368,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -2325,7 +2379,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -2336,7 +2390,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -2347,7 +2401,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2358,7 +2412,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -2369,7 +2423,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -2380,7 +2434,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -2391,7 +2445,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -2402,7 +2456,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -2413,7 +2467,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -2424,7 +2478,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -2435,7 +2489,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>65</v>
       </c>
@@ -2446,7 +2500,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -2457,7 +2511,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -2468,7 +2522,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -2479,7 +2533,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="A88" t="s">
         <v>33</v>
       </c>
@@ -2490,7 +2544,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -2501,7 +2555,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="A90" t="s">
         <v>37</v>
       </c>
@@ -2512,7 +2566,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -2523,7 +2577,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="A92" t="s">
         <v>41</v>
       </c>
@@ -2534,7 +2588,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="A93" t="s">
         <v>43</v>
       </c>
@@ -2545,7 +2599,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="A94" t="s">
         <v>45</v>
       </c>
@@ -2556,7 +2610,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -2567,7 +2621,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="A96" t="s">
         <v>49</v>
       </c>
@@ -2578,7 +2632,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -2589,7 +2643,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -2600,7 +2654,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3">
       <c r="A99" t="s">
         <v>55</v>
       </c>
@@ -2611,7 +2665,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3">
       <c r="A100" t="s">
         <v>57</v>
       </c>
@@ -2622,7 +2676,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>59</v>
       </c>
@@ -2633,7 +2687,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -2644,7 +2698,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3">
       <c r="A103" t="s">
         <v>63</v>
       </c>
@@ -2655,7 +2709,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3">
       <c r="A104" s="2" t="s">
         <v>26</v>
       </c>
@@ -2666,7 +2720,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3">
       <c r="A105" t="s">
         <v>67</v>
       </c>
@@ -2677,7 +2731,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -2688,7 +2742,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3">
       <c r="A107" t="s">
         <v>71</v>
       </c>
@@ -2699,7 +2753,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2710,7 +2764,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3">
       <c r="A109" t="s">
         <v>75</v>
       </c>
@@ -2721,7 +2775,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3">
       <c r="A110" t="s">
         <v>77</v>
       </c>
@@ -2732,7 +2786,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -2743,7 +2797,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3">
       <c r="A112" t="s">
         <v>81</v>
       </c>
@@ -2754,7 +2808,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3">
       <c r="A113" t="s">
         <v>83</v>
       </c>
@@ -2765,7 +2819,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3">
       <c r="A114" t="s">
         <v>84</v>
       </c>
@@ -2776,7 +2830,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3">
       <c r="A115" t="s">
         <v>85</v>
       </c>
@@ -2787,7 +2841,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3">
       <c r="A116" t="s">
         <v>87</v>
       </c>
@@ -2798,7 +2852,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3">
       <c r="A117" t="s">
         <v>89</v>
       </c>
@@ -2809,7 +2863,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -2820,7 +2874,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3">
       <c r="A119" t="s">
         <v>93</v>
       </c>
@@ -2831,7 +2885,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3">
       <c r="A120" t="s">
         <v>95</v>
       </c>
@@ -2842,7 +2896,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3">
       <c r="A121" t="s">
         <v>97</v>
       </c>
@@ -2853,7 +2907,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3">
       <c r="A122" t="s">
         <v>99</v>
       </c>
@@ -2864,7 +2918,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3">
       <c r="A123" t="s">
         <v>101</v>
       </c>
@@ -2875,7 +2929,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3">
       <c r="A124" t="s">
         <v>103</v>
       </c>
@@ -2886,7 +2940,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3">
       <c r="A125" t="s">
         <v>105</v>
       </c>
@@ -2897,7 +2951,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>107</v>
       </c>
@@ -2908,7 +2962,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3">
       <c r="A127" t="s">
         <v>109</v>
       </c>
@@ -2919,7 +2973,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3">
       <c r="A128" t="s">
         <v>111</v>
       </c>
@@ -2930,7 +2984,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3">
       <c r="A129" t="s">
         <v>113</v>
       </c>
@@ -2941,7 +2995,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3">
       <c r="A130" t="s">
         <v>115</v>
       </c>
@@ -2952,7 +3006,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3">
       <c r="A131" t="s">
         <v>117</v>
       </c>
@@ -2963,7 +3017,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3">
       <c r="A132" t="s">
         <v>119</v>
       </c>
@@ -2974,7 +3028,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3">
       <c r="A133" t="s">
         <v>121</v>
       </c>
@@ -2985,7 +3039,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3">
       <c r="A134" t="s">
         <v>123</v>
       </c>
@@ -2996,7 +3050,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3">
       <c r="A135" t="s">
         <v>125</v>
       </c>
@@ -3007,7 +3061,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3">
       <c r="A136" t="s">
         <v>127</v>
       </c>
@@ -3018,7 +3072,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3">
       <c r="A137" t="s">
         <v>128</v>
       </c>
@@ -3029,7 +3083,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3">
       <c r="A138" t="s">
         <v>130</v>
       </c>
@@ -3040,7 +3094,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3">
       <c r="A139" t="s">
         <v>132</v>
       </c>
@@ -3051,7 +3105,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -3062,7 +3116,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3">
       <c r="A141" t="s">
         <v>136</v>
       </c>
@@ -3073,7 +3127,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3">
       <c r="A142" t="s">
         <v>138</v>
       </c>
@@ -3084,7 +3138,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -3095,7 +3149,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -3106,7 +3160,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -3117,7 +3171,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3">
       <c r="A146" t="s">
         <v>306</v>
       </c>
@@ -3128,7 +3182,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3">
       <c r="A147" t="s">
         <v>305</v>
       </c>
@@ -3139,7 +3193,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3">
       <c r="A148" t="s">
         <v>303</v>
       </c>
@@ -3150,7 +3204,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3">
       <c r="A149" t="s">
         <v>301</v>
       </c>
@@ -3161,7 +3215,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3">
       <c r="A150" t="s">
         <v>299</v>
       </c>
@@ -3172,7 +3226,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>297</v>
       </c>
@@ -3183,7 +3237,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3">
       <c r="A152" t="s">
         <v>295</v>
       </c>
@@ -3194,7 +3248,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3">
       <c r="A153" t="s">
         <v>293</v>
       </c>
@@ -3205,7 +3259,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3">
       <c r="A154" t="s">
         <v>320</v>
       </c>
@@ -3216,7 +3270,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3">
       <c r="A155" t="s">
         <v>318</v>
       </c>
@@ -3227,7 +3281,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3">
       <c r="A156" t="s">
         <v>316</v>
       </c>
@@ -3238,7 +3292,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -3249,7 +3303,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3">
       <c r="A158" t="s">
         <v>312</v>
       </c>
@@ -3260,7 +3314,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3">
       <c r="A159" t="s">
         <v>310</v>
       </c>
@@ -3271,7 +3325,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3">
       <c r="A160" t="s">
         <v>308</v>
       </c>
@@ -3282,7 +3336,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3">
       <c r="A161" t="s">
         <v>344</v>
       </c>
@@ -3293,7 +3347,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3">
       <c r="A162" t="s">
         <v>342</v>
       </c>
@@ -3304,7 +3358,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3">
       <c r="A163" t="s">
         <v>340</v>
       </c>
@@ -3315,7 +3369,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3">
       <c r="A164" t="s">
         <v>338</v>
       </c>
@@ -3326,7 +3380,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3">
       <c r="A165" t="s">
         <v>336</v>
       </c>
@@ -3337,7 +3391,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3">
       <c r="A166" t="s">
         <v>334</v>
       </c>
@@ -3348,7 +3402,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -3359,7 +3413,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3">
       <c r="A168" t="s">
         <v>330</v>
       </c>
@@ -3370,7 +3424,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3">
       <c r="A169" t="s">
         <v>328</v>
       </c>
@@ -3381,7 +3435,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3">
       <c r="A170" t="s">
         <v>326</v>
       </c>
@@ -3392,7 +3446,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3">
       <c r="A171" t="s">
         <v>324</v>
       </c>
@@ -3403,7 +3457,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3">
       <c r="A172" t="s">
         <v>322</v>
       </c>
@@ -3414,7 +3468,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3">
       <c r="A173" t="s">
         <v>345</v>
       </c>
@@ -3425,7 +3479,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -3436,7 +3490,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -3447,7 +3501,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -3458,7 +3512,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3">
       <c r="A177" t="s">
         <v>353</v>
       </c>
@@ -3469,7 +3523,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3">
       <c r="A178" t="s">
         <v>355</v>
       </c>
@@ -3480,7 +3534,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3">
       <c r="A179" t="s">
         <v>357</v>
       </c>
@@ -3491,7 +3545,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -3502,7 +3556,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -3513,7 +3567,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3">
       <c r="A182" t="s">
         <v>363</v>
       </c>
@@ -3522,6 +3576,105 @@
       </c>
       <c r="C182" t="s">
         <v>270</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" t="s">
+        <v>367</v>
+      </c>
+      <c r="B184" t="s">
+        <v>368</v>
+      </c>
+      <c r="C184" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" t="s">
+        <v>369</v>
+      </c>
+      <c r="B185" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" t="s">
+        <v>371</v>
+      </c>
+      <c r="B186" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" t="s">
+        <v>373</v>
+      </c>
+      <c r="B187" t="s">
+        <v>374</v>
+      </c>
+      <c r="C187" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" t="s">
+        <v>375</v>
+      </c>
+      <c r="B188" t="s">
+        <v>376</v>
+      </c>
+      <c r="C188" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" t="s">
+        <v>378</v>
+      </c>
+      <c r="C189" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" t="s">
+        <v>379</v>
+      </c>
+      <c r="B190" t="s">
+        <v>380</v>
+      </c>
+      <c r="C190" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" t="s">
+        <v>381</v>
+      </c>
+      <c r="B191" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D751C798-9842-41FC-9857-15A61752D38E}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1CF938-9A9A-4C3F-BD57-B7419AD8CF58}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="395">
   <si>
     <t>Job</t>
   </si>
@@ -1188,6 +1188,42 @@
   </si>
   <si>
     <t>49 Wards Line, Greytown</t>
+  </si>
+  <si>
+    <t>1085554 - 00062941 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Boydfield Street, Whanganui East</t>
+  </si>
+  <si>
+    <t>1085553 - 00057633 - DG Label</t>
+  </si>
+  <si>
+    <t>2a Buxton Road, Westmere</t>
+  </si>
+  <si>
+    <t>1085551 - 00062161 - DG Label</t>
+  </si>
+  <si>
+    <t>72 Watt Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085550 - 00061611 - DG Label</t>
+  </si>
+  <si>
+    <t>180A Manchester Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085549 - 00061578 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Rothesay Place, Highbury</t>
+  </si>
+  <si>
+    <t>1085548 - 00061326 - DG Label</t>
+  </si>
+  <si>
+    <t>19 Mill Grove, Clareville</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C191"/>
+  <dimension ref="A1:C197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3677,6 +3713,72 @@
         <v>269</v>
       </c>
     </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>383</v>
+      </c>
+      <c r="B192" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" t="s">
+        <v>385</v>
+      </c>
+      <c r="B193" t="s">
+        <v>386</v>
+      </c>
+      <c r="C193" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" t="s">
+        <v>388</v>
+      </c>
+      <c r="C194" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B195" t="s">
+        <v>390</v>
+      </c>
+      <c r="C195" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" t="s">
+        <v>391</v>
+      </c>
+      <c r="B196" t="s">
+        <v>392</v>
+      </c>
+      <c r="C196" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" t="s">
+        <v>393</v>
+      </c>
+      <c r="B197" t="s">
+        <v>394</v>
+      </c>
+      <c r="C197" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1CF938-9A9A-4C3F-BD57-B7419AD8CF58}"/>
+  <xr:revisionPtr revIDLastSave="148" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB98B0D-F34D-42AF-9F55-7DD09F91BF47}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="415">
   <si>
     <t>Job</t>
   </si>
@@ -1224,13 +1224,73 @@
   </si>
   <si>
     <t>19 Mill Grove, Clareville</t>
+  </si>
+  <si>
+    <t>1085628 - 00042760 - DG Label</t>
+  </si>
+  <si>
+    <t>286 Central Mangaone Road, Eketahuna</t>
+  </si>
+  <si>
+    <t>1085627 - 00060729 - DG Label</t>
+  </si>
+  <si>
+    <t>1294 Turakina Valley Road, Turakina</t>
+  </si>
+  <si>
+    <t>1085626 - 00058779 - DG Label</t>
+  </si>
+  <si>
+    <t>154 Watershed Road, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085625 - 00059698 - DG Label</t>
+  </si>
+  <si>
+    <t>19 Bengston Street, Eketahuna</t>
+  </si>
+  <si>
+    <t>1085624 - 00045886 - DG Label</t>
+  </si>
+  <si>
+    <t>17 Pickwick Road, Otamatea</t>
+  </si>
+  <si>
+    <t>1085623 - 00035552 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Tangimoana Road, Ohakea</t>
+  </si>
+  <si>
+    <t>1085622 - 00055340 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Tayforth Road, Whanganui</t>
+  </si>
+  <si>
+    <t>1085621 - 00052867 - DG Label</t>
+  </si>
+  <si>
+    <t>8 Aotea Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085620 - 00053518 - DG Label</t>
+  </si>
+  <si>
+    <t>295 Dalefield Road, Dalefield</t>
+  </si>
+  <si>
+    <t>1085619 - 00054760 - DG Label</t>
+  </si>
+  <si>
+    <t>42 Johnstone Drive, Fitzherbert</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1604,15 +1664,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C197"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C207"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1683,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>211</v>
       </c>
@@ -1634,7 +1694,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -1645,7 +1705,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>215</v>
       </c>
@@ -1656,7 +1716,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>217</v>
       </c>
@@ -1667,7 +1727,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>219</v>
       </c>
@@ -1678,7 +1738,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>221</v>
       </c>
@@ -1689,7 +1749,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -1700,7 +1760,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>225</v>
       </c>
@@ -1711,7 +1771,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>227</v>
       </c>
@@ -1722,7 +1782,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>229</v>
       </c>
@@ -1733,7 +1793,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>231</v>
       </c>
@@ -1744,7 +1804,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>233</v>
       </c>
@@ -1755,7 +1815,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>235</v>
       </c>
@@ -1766,7 +1826,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>237</v>
       </c>
@@ -1777,7 +1837,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>239</v>
       </c>
@@ -1788,7 +1848,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>241</v>
       </c>
@@ -1799,7 +1859,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>243</v>
       </c>
@@ -1810,7 +1870,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>245</v>
       </c>
@@ -1821,7 +1881,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>247</v>
       </c>
@@ -1832,7 +1892,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>249</v>
       </c>
@@ -1843,7 +1903,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>251</v>
       </c>
@@ -1854,7 +1914,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>253</v>
       </c>
@@ -1865,7 +1925,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>255</v>
       </c>
@@ -1876,7 +1936,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>257</v>
       </c>
@@ -1887,7 +1947,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>259</v>
       </c>
@@ -1898,7 +1958,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>260</v>
       </c>
@@ -1909,7 +1969,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>262</v>
       </c>
@@ -1920,7 +1980,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>264</v>
       </c>
@@ -1931,7 +1991,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>266</v>
       </c>
@@ -1942,7 +2002,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>268</v>
       </c>
@@ -1953,7 +2013,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>146</v>
       </c>
@@ -1964,7 +2024,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>147</v>
       </c>
@@ -1975,7 +2035,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>149</v>
       </c>
@@ -1986,7 +2046,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -1997,7 +2057,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -2008,7 +2068,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -2019,7 +2079,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>157</v>
       </c>
@@ -2030,7 +2090,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>159</v>
       </c>
@@ -2041,7 +2101,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>161</v>
       </c>
@@ -2052,7 +2112,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>163</v>
       </c>
@@ -2063,7 +2123,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>165</v>
       </c>
@@ -2074,7 +2134,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -2085,7 +2145,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>169</v>
       </c>
@@ -2096,7 +2156,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>171</v>
       </c>
@@ -2107,7 +2167,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>173</v>
       </c>
@@ -2118,7 +2178,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>174</v>
       </c>
@@ -2129,7 +2189,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>176</v>
       </c>
@@ -2140,7 +2200,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>178</v>
       </c>
@@ -2151,7 +2211,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>180</v>
       </c>
@@ -2162,7 +2222,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>181</v>
       </c>
@@ -2173,7 +2233,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>183</v>
       </c>
@@ -2184,7 +2244,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>185</v>
       </c>
@@ -2195,7 +2255,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>187</v>
       </c>
@@ -2206,7 +2266,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>189</v>
       </c>
@@ -2217,7 +2277,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>191</v>
       </c>
@@ -2228,7 +2288,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>193</v>
       </c>
@@ -2239,7 +2299,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>195</v>
       </c>
@@ -2250,7 +2310,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>197</v>
       </c>
@@ -2261,7 +2321,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>199</v>
       </c>
@@ -2272,7 +2332,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>201</v>
       </c>
@@ -2283,7 +2343,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>203</v>
       </c>
@@ -2294,7 +2354,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>205</v>
       </c>
@@ -2305,7 +2365,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>207</v>
       </c>
@@ -2316,7 +2376,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>209</v>
       </c>
@@ -2327,7 +2387,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>2</v>
       </c>
@@ -2338,7 +2398,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -2349,7 +2409,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -2360,7 +2420,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2371,7 +2431,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>7</v>
       </c>
@@ -2382,7 +2442,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -2393,7 +2453,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -2404,7 +2464,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -2415,7 +2475,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -2426,7 +2486,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -2437,7 +2497,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -2448,7 +2508,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -2459,7 +2519,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -2470,7 +2530,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -2481,7 +2541,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -2492,7 +2552,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -2503,7 +2563,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -2514,7 +2574,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -2525,7 +2585,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>65</v>
       </c>
@@ -2536,7 +2596,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -2547,7 +2607,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>29</v>
       </c>
@@ -2558,7 +2618,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -2569,7 +2629,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>33</v>
       </c>
@@ -2580,7 +2640,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>35</v>
       </c>
@@ -2591,7 +2651,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>37</v>
       </c>
@@ -2602,7 +2662,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -2613,7 +2673,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>41</v>
       </c>
@@ -2624,7 +2684,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>43</v>
       </c>
@@ -2635,7 +2695,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>45</v>
       </c>
@@ -2646,7 +2706,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -2657,7 +2717,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>49</v>
       </c>
@@ -2668,7 +2728,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -2679,7 +2739,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -2690,7 +2750,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>55</v>
       </c>
@@ -2701,7 +2761,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>57</v>
       </c>
@@ -2712,7 +2772,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>59</v>
       </c>
@@ -2723,7 +2783,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>61</v>
       </c>
@@ -2734,7 +2794,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>63</v>
       </c>
@@ -2745,7 +2805,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>26</v>
       </c>
@@ -2756,7 +2816,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>67</v>
       </c>
@@ -2767,7 +2827,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -2778,7 +2838,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>71</v>
       </c>
@@ -2789,7 +2849,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>73</v>
       </c>
@@ -2800,7 +2860,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>75</v>
       </c>
@@ -2811,7 +2871,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>77</v>
       </c>
@@ -2822,7 +2882,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>79</v>
       </c>
@@ -2833,7 +2893,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>81</v>
       </c>
@@ -2844,7 +2904,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>83</v>
       </c>
@@ -2855,7 +2915,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>84</v>
       </c>
@@ -2866,7 +2926,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>85</v>
       </c>
@@ -2877,7 +2937,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>87</v>
       </c>
@@ -2888,7 +2948,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>89</v>
       </c>
@@ -2899,7 +2959,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -2910,7 +2970,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>93</v>
       </c>
@@ -2921,7 +2981,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>95</v>
       </c>
@@ -2932,7 +2992,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>97</v>
       </c>
@@ -2943,7 +3003,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>99</v>
       </c>
@@ -2954,7 +3014,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>101</v>
       </c>
@@ -2965,7 +3025,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>103</v>
       </c>
@@ -2976,7 +3036,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>105</v>
       </c>
@@ -2987,7 +3047,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>107</v>
       </c>
@@ -2998,7 +3058,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>109</v>
       </c>
@@ -3009,7 +3069,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>111</v>
       </c>
@@ -3020,7 +3080,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>113</v>
       </c>
@@ -3031,7 +3091,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>115</v>
       </c>
@@ -3042,7 +3102,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>117</v>
       </c>
@@ -3053,7 +3113,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>119</v>
       </c>
@@ -3064,7 +3124,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>121</v>
       </c>
@@ -3075,7 +3135,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>123</v>
       </c>
@@ -3086,7 +3146,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>125</v>
       </c>
@@ -3097,7 +3157,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>127</v>
       </c>
@@ -3108,7 +3168,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>128</v>
       </c>
@@ -3119,7 +3179,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>130</v>
       </c>
@@ -3130,7 +3190,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>132</v>
       </c>
@@ -3141,7 +3201,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>134</v>
       </c>
@@ -3152,7 +3212,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>136</v>
       </c>
@@ -3163,7 +3223,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>138</v>
       </c>
@@ -3174,7 +3234,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>140</v>
       </c>
@@ -3185,7 +3245,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -3196,7 +3256,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -3207,7 +3267,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>306</v>
       </c>
@@ -3218,7 +3278,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>305</v>
       </c>
@@ -3229,7 +3289,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>303</v>
       </c>
@@ -3240,7 +3300,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>301</v>
       </c>
@@ -3251,7 +3311,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>299</v>
       </c>
@@ -3262,7 +3322,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>297</v>
       </c>
@@ -3273,7 +3333,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>295</v>
       </c>
@@ -3284,7 +3344,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>293</v>
       </c>
@@ -3295,7 +3355,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>320</v>
       </c>
@@ -3306,7 +3366,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>318</v>
       </c>
@@ -3317,7 +3377,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>316</v>
       </c>
@@ -3328,7 +3388,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -3339,7 +3399,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>312</v>
       </c>
@@ -3350,7 +3410,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>310</v>
       </c>
@@ -3361,7 +3421,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>308</v>
       </c>
@@ -3372,7 +3432,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>344</v>
       </c>
@@ -3383,7 +3443,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>342</v>
       </c>
@@ -3394,7 +3454,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>340</v>
       </c>
@@ -3405,7 +3465,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>338</v>
       </c>
@@ -3416,7 +3476,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>336</v>
       </c>
@@ -3427,7 +3487,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>334</v>
       </c>
@@ -3438,7 +3498,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>332</v>
       </c>
@@ -3449,7 +3509,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>330</v>
       </c>
@@ -3460,7 +3520,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>328</v>
       </c>
@@ -3471,7 +3531,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>326</v>
       </c>
@@ -3482,7 +3542,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>324</v>
       </c>
@@ -3493,7 +3553,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>322</v>
       </c>
@@ -3504,7 +3564,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>345</v>
       </c>
@@ -3515,7 +3575,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>347</v>
       </c>
@@ -3526,7 +3586,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>349</v>
       </c>
@@ -3537,7 +3597,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>351</v>
       </c>
@@ -3548,7 +3608,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>353</v>
       </c>
@@ -3559,7 +3619,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>355</v>
       </c>
@@ -3570,7 +3630,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>357</v>
       </c>
@@ -3581,7 +3641,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>359</v>
       </c>
@@ -3592,7 +3652,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>361</v>
       </c>
@@ -3603,7 +3663,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>363</v>
       </c>
@@ -3614,7 +3674,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>365</v>
       </c>
@@ -3625,7 +3685,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>367</v>
       </c>
@@ -3636,7 +3696,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>369</v>
       </c>
@@ -3647,7 +3707,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>371</v>
       </c>
@@ -3658,7 +3718,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>373</v>
       </c>
@@ -3669,7 +3729,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>375</v>
       </c>
@@ -3680,7 +3740,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>377</v>
       </c>
@@ -3691,7 +3751,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="190" spans="1:3">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>379</v>
       </c>
@@ -3702,7 +3762,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>381</v>
       </c>
@@ -3713,7 +3773,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>383</v>
       </c>
@@ -3724,7 +3784,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>385</v>
       </c>
@@ -3735,7 +3795,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>387</v>
       </c>
@@ -3746,7 +3806,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>389</v>
       </c>
@@ -3757,7 +3817,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>391</v>
       </c>
@@ -3768,7 +3828,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>393</v>
       </c>
@@ -3776,6 +3836,116 @@
         <v>394</v>
       </c>
       <c r="C197" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>395</v>
+      </c>
+      <c r="B198" t="s">
+        <v>396</v>
+      </c>
+      <c r="C198" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>397</v>
+      </c>
+      <c r="B199" t="s">
+        <v>398</v>
+      </c>
+      <c r="C199" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>399</v>
+      </c>
+      <c r="B200" t="s">
+        <v>400</v>
+      </c>
+      <c r="C200" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>401</v>
+      </c>
+      <c r="B201" t="s">
+        <v>402</v>
+      </c>
+      <c r="C201" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>403</v>
+      </c>
+      <c r="B202" t="s">
+        <v>404</v>
+      </c>
+      <c r="C202" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>405</v>
+      </c>
+      <c r="B203" t="s">
+        <v>406</v>
+      </c>
+      <c r="C203" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>407</v>
+      </c>
+      <c r="B204" t="s">
+        <v>408</v>
+      </c>
+      <c r="C204" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>409</v>
+      </c>
+      <c r="B205" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>411</v>
+      </c>
+      <c r="B206" t="s">
+        <v>412</v>
+      </c>
+      <c r="C206" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>413</v>
+      </c>
+      <c r="B207" t="s">
+        <v>414</v>
+      </c>
+      <c r="C207" t="s">
         <v>270</v>
       </c>
     </row>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB98B0D-F34D-42AF-9F55-7DD09F91BF47}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF68EE7-DA39-4A83-9138-C38E883080C4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="449">
   <si>
     <t>Job</t>
   </si>
@@ -974,24 +974,6 @@
     <t>1084772 - 00060405 - DG Label</t>
   </si>
   <si>
-    <t>9A Belvedere Crescent, Takaro</t>
-  </si>
-  <si>
-    <t>1084774 - 00053598 - DG Label</t>
-  </si>
-  <si>
-    <t>7 Long Melford Road, Awapuni</t>
-  </si>
-  <si>
-    <t>1084776 - 00045583 - DG Label</t>
-  </si>
-  <si>
-    <t>115 Atawhai Road, Fitzherbert</t>
-  </si>
-  <si>
-    <t>1084778 - 00045588 - DG Label</t>
-  </si>
-  <si>
     <t>74 Cambridge Avenue, Ashhurst</t>
   </si>
   <si>
@@ -1046,12 +1028,6 @@
     <t>1085285 - 00054784 - DG Label</t>
   </si>
   <si>
-    <t>40 Ruapehu Drive, Fitzherbert</t>
-  </si>
-  <si>
-    <t>1085286 - 00056531 - DG Label</t>
-  </si>
-  <si>
     <t>5B Blennerville Close, Marton</t>
   </si>
   <si>
@@ -1284,6 +1260,132 @@
   </si>
   <si>
     <t>42 Johnstone Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085737 - 00064071 - DG Label</t>
+  </si>
+  <si>
+    <t>471 Lees Road, Feilding</t>
+  </si>
+  <si>
+    <t>1085735 - 00061413 - DG Label</t>
+  </si>
+  <si>
+    <t>85 Watt Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085734 - 00025403 - DG Label</t>
+  </si>
+  <si>
+    <t>7B Brassey Road, Saint Johns Hill</t>
+  </si>
+  <si>
+    <t>1085733 - 00031648 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Fox Road, Springvale</t>
+  </si>
+  <si>
+    <t>1085732 - 00030245 - DG Label</t>
+  </si>
+  <si>
+    <t>47 Kowhai Street, Castlecliff</t>
+  </si>
+  <si>
+    <t>1085731 - 00029753 - DG Label</t>
+  </si>
+  <si>
+    <t>119 Pharazyn Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085730 - 00038535 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Waicola Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085727 - 00046515 - DG Label</t>
+  </si>
+  <si>
+    <t>6 Hayward Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085726 - 00038396 - DG Label</t>
+  </si>
+  <si>
+    <t>182 Kimbolton Road, Feilding</t>
+  </si>
+  <si>
+    <t>1085725 - 00025168 - DG Label</t>
+  </si>
+  <si>
+    <t>388 Ruakokoputuna Road, Martinborough</t>
+  </si>
+  <si>
+    <t>1085724 - 00032739 - DG Label</t>
+  </si>
+  <si>
+    <t>2187 State Highway 3, Sanson</t>
+  </si>
+  <si>
+    <t>1085722 - 00047186 - DG Label</t>
+  </si>
+  <si>
+    <t>36 Cloverlea Road, Westbrook</t>
+  </si>
+  <si>
+    <t>1085721 - 00054363 - DG Label</t>
+  </si>
+  <si>
+    <t>71 Wightman Road, Sanson</t>
+  </si>
+  <si>
+    <t>1085720 - 00051231 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Spelman Court, Ashhurst</t>
+  </si>
+  <si>
+    <t>1085718 - 00025360 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Hartwell Drive, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085717 - 00057960 - DG Label</t>
+  </si>
+  <si>
+    <t>32 Harrison Street West, Featherston</t>
+  </si>
+  <si>
+    <t>1085716 - 00055342 - DG Label</t>
+  </si>
+  <si>
+    <t>52 Surrey Road, Springvale</t>
+  </si>
+  <si>
+    <t>1085715 - 00030535 - DG Label</t>
+  </si>
+  <si>
+    <t>2/31 Moore Street, Tawhero</t>
+  </si>
+  <si>
+    <t>1085714 - 00048298 - DG Label</t>
+  </si>
+  <si>
+    <t>6 Monmouth Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085712 - 00055446 - DG Label</t>
+  </si>
+  <si>
+    <t>262 Campbell Road, Brunswick</t>
+  </si>
+  <si>
+    <t>1085711 - 00060489 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Te Arakura Road, Newbury</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C207"/>
+  <dimension ref="A1:C224"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3357,10 +3459,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B154" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C154" t="s">
         <v>270</v>
@@ -3368,10 +3470,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B155" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C155" t="s">
         <v>269</v>
@@ -3379,21 +3481,21 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B156" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B157" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C157" t="s">
         <v>270</v>
@@ -3401,10 +3503,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B158" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
         <v>270</v>
@@ -3412,21 +3514,21 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="B159" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="B160" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C160" t="s">
         <v>270</v>
@@ -3434,10 +3536,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C161" t="s">
         <v>270</v>
@@ -3445,21 +3547,21 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="B162" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C162" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C163" t="s">
         <v>270</v>
@@ -3467,21 +3569,21 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B164" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C164" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B165" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C165" t="s">
         <v>269</v>
@@ -3489,21 +3591,21 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="B166" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C167" t="s">
         <v>270</v>
@@ -3511,10 +3613,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="B168" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="C168" t="s">
         <v>269</v>
@@ -3522,10 +3624,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B169" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="C169" t="s">
         <v>269</v>
@@ -3533,10 +3635,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B170" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="C170" t="s">
         <v>270</v>
@@ -3544,10 +3646,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B171" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="C171" t="s">
         <v>270</v>
@@ -3555,10 +3657,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="B172" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C172" t="s">
         <v>269</v>
@@ -3572,7 +3674,7 @@
         <v>346</v>
       </c>
       <c r="C173" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3583,7 +3685,7 @@
         <v>348</v>
       </c>
       <c r="C174" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3594,7 +3696,7 @@
         <v>350</v>
       </c>
       <c r="C175" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3605,7 +3707,7 @@
         <v>352</v>
       </c>
       <c r="C176" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3616,7 +3718,7 @@
         <v>354</v>
       </c>
       <c r="C177" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3627,7 +3729,7 @@
         <v>356</v>
       </c>
       <c r="C178" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3649,7 +3751,7 @@
         <v>360</v>
       </c>
       <c r="C180" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3660,7 +3762,7 @@
         <v>362</v>
       </c>
       <c r="C181" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3671,7 +3773,7 @@
         <v>364</v>
       </c>
       <c r="C182" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3770,7 +3872,7 @@
         <v>382</v>
       </c>
       <c r="C191" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -3781,7 +3883,7 @@
         <v>384</v>
       </c>
       <c r="C192" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -3814,7 +3916,7 @@
         <v>390</v>
       </c>
       <c r="C195" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -3825,7 +3927,7 @@
         <v>392</v>
       </c>
       <c r="C196" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -3847,7 +3949,7 @@
         <v>396</v>
       </c>
       <c r="C198" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -3891,7 +3993,7 @@
         <v>404</v>
       </c>
       <c r="C202" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -3902,7 +4004,7 @@
         <v>406</v>
       </c>
       <c r="C203" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -3913,7 +4015,7 @@
         <v>408</v>
       </c>
       <c r="C204" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -3924,7 +4026,7 @@
         <v>410</v>
       </c>
       <c r="C205" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -3947,6 +4049,193 @@
       </c>
       <c r="C207" t="s">
         <v>270</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>415</v>
+      </c>
+      <c r="B208" t="s">
+        <v>416</v>
+      </c>
+      <c r="C208" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>417</v>
+      </c>
+      <c r="B209" t="s">
+        <v>418</v>
+      </c>
+      <c r="C209" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>419</v>
+      </c>
+      <c r="B210" t="s">
+        <v>420</v>
+      </c>
+      <c r="C210" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>421</v>
+      </c>
+      <c r="B211" t="s">
+        <v>422</v>
+      </c>
+      <c r="C211" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>423</v>
+      </c>
+      <c r="B212" t="s">
+        <v>424</v>
+      </c>
+      <c r="C212" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>425</v>
+      </c>
+      <c r="B213" t="s">
+        <v>426</v>
+      </c>
+      <c r="C213" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>427</v>
+      </c>
+      <c r="B214" t="s">
+        <v>428</v>
+      </c>
+      <c r="C214" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>429</v>
+      </c>
+      <c r="B215" t="s">
+        <v>430</v>
+      </c>
+      <c r="C215" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>431</v>
+      </c>
+      <c r="B216" t="s">
+        <v>432</v>
+      </c>
+      <c r="C216" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>433</v>
+      </c>
+      <c r="B217" t="s">
+        <v>434</v>
+      </c>
+      <c r="C217" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>435</v>
+      </c>
+      <c r="B218" t="s">
+        <v>436</v>
+      </c>
+      <c r="C218" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>437</v>
+      </c>
+      <c r="B219" t="s">
+        <v>438</v>
+      </c>
+      <c r="C219" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>439</v>
+      </c>
+      <c r="B220" t="s">
+        <v>440</v>
+      </c>
+      <c r="C220" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>441</v>
+      </c>
+      <c r="B221" t="s">
+        <v>442</v>
+      </c>
+      <c r="C221" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>443</v>
+      </c>
+      <c r="B222" t="s">
+        <v>444</v>
+      </c>
+      <c r="C222" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>445</v>
+      </c>
+      <c r="B223" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>447</v>
+      </c>
+      <c r="B224" t="s">
+        <v>448</v>
+      </c>
+      <c r="C224" t="s">
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF68EE7-DA39-4A83-9138-C38E883080C4}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37618238-51C5-49B9-9327-84E12C9B4DA4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="393">
   <si>
     <t>Job</t>
   </si>
@@ -674,171 +674,6 @@
     <t>34 Jellicoe Street, Martinborough</t>
   </si>
   <si>
-    <t>1082613 - 00037301  - DG Label - 0068841000WR999</t>
-  </si>
-  <si>
-    <t>663 CHESTER ROAD , WEST TARATAHI, CARTERTON, 5791</t>
-  </si>
-  <si>
-    <t>1082609 - 00037241  - DG Label - 1000572372PC23E</t>
-  </si>
-  <si>
-    <t>11 Te Ore Ore Bideford Road , Te Ore Ore, Masterton, 5886</t>
-  </si>
-  <si>
-    <t>1082608 - 00037238  - DG Label - 1000605901PC3C4</t>
-  </si>
-  <si>
-    <t>32 TAMA ROAD , RIVERSDALE BEACH, MASTERTON, 5872</t>
-  </si>
-  <si>
-    <t>1082604 - 00037235 - DG Label - 1000583813PC6B9</t>
-  </si>
-  <si>
-    <t>39A WELD STREET , MARTINBOROUGH, MARTINBOROUGH, 5711</t>
-  </si>
-  <si>
-    <t>1082601 - 00036842 - DG Label - 1000544375PCB18</t>
-  </si>
-  <si>
-    <t>9 FAIRWAY DR , MARTINBOROUGH, MARTINBOROUGH, 5784</t>
-  </si>
-  <si>
-    <t>1082588 - 00035665 - DG Label - 1000624084PCAA5</t>
-  </si>
-  <si>
-    <t>219B GLENMORVEN ROAD , MORISON BUSH, GREYTOWN, 5794</t>
-  </si>
-  <si>
-    <t>1082586 - 00035670 - DG Label - 0060007400WR56A</t>
-  </si>
-  <si>
-    <t>274 HIGH STREET NORTH , CARTERTON, 5713</t>
-  </si>
-  <si>
-    <t>1082585 - 00035668 - DG Label - 0666003845PCD5A</t>
-  </si>
-  <si>
-    <t>433B WAIOHINE GORGE ROAD , CARTERTON, 5791</t>
-  </si>
-  <si>
-    <t>1082584 - 00034018 - DG Label - 0052489000WRDDE</t>
-  </si>
-  <si>
-    <t>1 TAMARISK DR , MASTERTON</t>
-  </si>
-  <si>
-    <t>1082582 - 00034014  - DG Label -0070568100WR40F</t>
-  </si>
-  <si>
-    <t>17 HOMESTEAD LANE , GREYTOWN, GREYTOWN, 5712</t>
-  </si>
-  <si>
-    <t>1082576 - 00031683  - DG Label -0666003622PC96B</t>
-  </si>
-  <si>
-    <t>70B DUBLIN STREET , MARTINBOROUGH, 5711</t>
-  </si>
-  <si>
-    <t>1082574 - 00014488  - DG Label -0037559000WRE8B</t>
-  </si>
-  <si>
-    <t>64 CORNWALL STREET , MASTERTON, 5810</t>
-  </si>
-  <si>
-    <t>1082571 - 00039316 - DG Label - 0000068226CP3F0</t>
-  </si>
-  <si>
-    <t>2 VISCOUNT PLACE, WEST END, PALMERSTON NORTH, 4412</t>
-  </si>
-  <si>
-    <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
-  </si>
-  <si>
-    <t>69 KERERU DRIVE, TURITEA, PALMERSTON NORTH, 4472</t>
-  </si>
-  <si>
-    <t>1082560 - 00052590 - DG Label - 0000048858CP6F1</t>
-  </si>
-  <si>
-    <t>9 HEATHCOTE PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
-  </si>
-  <si>
-    <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
-  </si>
-  <si>
-    <t>180B PHARAZYN ROAD, FEILDING, 4777</t>
-  </si>
-  <si>
-    <t>1082526 - 00044306 - DG Label - 1000605858PCC99</t>
-  </si>
-  <si>
-    <t>1 Cotterville Crescent, Greytown, 5712</t>
-  </si>
-  <si>
-    <t>1082525 - 00042914 - DG Label - 1000574372PC7FE</t>
-  </si>
-  <si>
-    <t>13 MERVYN BROWN PLACE, SOLWAY, MASTERTON, 5810</t>
-  </si>
-  <si>
-    <t>1082504 - 00050338 - DG Label - 1000579124PCE5E</t>
-  </si>
-  <si>
-    <t>4 HUFFINGTON PLACE, FEILDING, FEILDING, 4702</t>
-  </si>
-  <si>
-    <t>1082503 - 00050326 - DG Label - 0900086275PCEC2</t>
-  </si>
-  <si>
-    <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
-  </si>
-  <si>
-    <t>1082492 - 00055639 - DG Label - 0000037890CP0D3</t>
-  </si>
-  <si>
-    <t>41 ESCORT GROVE, AWAPUNI, PALMERSTON NORTH, 4412</t>
-  </si>
-  <si>
-    <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
-  </si>
-  <si>
-    <t>221B State Highway 2, Opaki, Masterton, 5871</t>
-  </si>
-  <si>
-    <t>1082487 - 00042599 - DG Label - 0070237600WR412</t>
-  </si>
-  <si>
-    <t>16 PAPAWAI ROAD, GREYTOWN</t>
-  </si>
-  <si>
-    <t>1082485 - 00052302 - DG Label - 1000615865PCCDB</t>
-  </si>
-  <si>
-    <t>8 GRATITUDE WAY, KELVIN GROVE, PALMERSTON NORTH, 4470</t>
-  </si>
-  <si>
-    <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
-  </si>
-  <si>
-    <t>1082458 - 00054943 - DG Label - 1000624687PC063</t>
-  </si>
-  <si>
-    <t>8 Sardinia Grove, Fitzherbert, Palmerston North</t>
-  </si>
-  <si>
-    <t>1082455 - 00044025 - DG Label - 1000621883PC042</t>
-  </si>
-  <si>
-    <t>6 CASTLEBRIDGE LANE, AOKAUTERE, PALMERSTON NORTH, 4471</t>
-  </si>
-  <si>
-    <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
-  </si>
-  <si>
-    <t>43 COUTTS WAY, FITZHERBERT, PALMERSTON NORTH, 4410</t>
-  </si>
-  <si>
     <t>1077616 - 00029329  - DG Label</t>
   </si>
   <si>
@@ -912,9 +747,6 @@
   </si>
   <si>
     <t>688 Aranui Road, Kairanga</t>
-  </si>
-  <si>
-    <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
   </si>
   <si>
     <t>45D Brandon Street, Featherston</t>
@@ -1782,337 +1614,29 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
         <v>217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>225</v>
-      </c>
-      <c r="B9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C11" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>233</v>
-      </c>
-      <c r="B13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" t="s">
-        <v>236</v>
-      </c>
-      <c r="C14" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>237</v>
-      </c>
-      <c r="B15" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" t="s">
-        <v>240</v>
-      </c>
-      <c r="C16" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>241</v>
-      </c>
-      <c r="B17" t="s">
-        <v>242</v>
-      </c>
-      <c r="C17" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" t="s">
-        <v>248</v>
-      </c>
-      <c r="C20" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" t="s">
-        <v>250</v>
-      </c>
-      <c r="C21" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>251</v>
-      </c>
-      <c r="B22" t="s">
-        <v>252</v>
-      </c>
-      <c r="C22" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>253</v>
-      </c>
-      <c r="B23" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" t="s">
-        <v>258</v>
-      </c>
-      <c r="C25" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>259</v>
-      </c>
-      <c r="B26" t="s">
-        <v>291</v>
-      </c>
-      <c r="C26" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>260</v>
-      </c>
-      <c r="B27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C27" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C28" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C29" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>235</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2120,10 +1644,10 @@
         <v>146</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2134,7 +1658,7 @@
         <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2145,7 +1669,7 @@
         <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2156,7 +1680,7 @@
         <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2167,7 +1691,7 @@
         <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2178,7 +1702,7 @@
         <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2189,7 +1713,7 @@
         <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2200,7 +1724,7 @@
         <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2211,7 +1735,7 @@
         <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2222,7 +1746,7 @@
         <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2233,7 +1757,7 @@
         <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2244,7 +1768,7 @@
         <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2255,7 +1779,7 @@
         <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2266,7 +1790,7 @@
         <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2274,10 +1798,10 @@
         <v>173</v>
       </c>
       <c r="B46" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2288,7 +1812,7 @@
         <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2299,7 +1823,7 @@
         <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2310,7 +1834,7 @@
         <v>179</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2321,7 +1845,7 @@
         <v>179</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2332,7 +1856,7 @@
         <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2343,7 +1867,7 @@
         <v>184</v>
       </c>
       <c r="C52" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2354,7 +1878,7 @@
         <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2365,7 +1889,7 @@
         <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,7 +1900,7 @@
         <v>190</v>
       </c>
       <c r="C55" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2387,7 +1911,7 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2398,7 +1922,7 @@
         <v>194</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,7 +1933,7 @@
         <v>196</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,7 +1944,7 @@
         <v>198</v>
       </c>
       <c r="C59" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2431,7 +1955,7 @@
         <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,7 +1966,7 @@
         <v>202</v>
       </c>
       <c r="C61" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,7 +1977,7 @@
         <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,7 +1988,7 @@
         <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,7 +1999,7 @@
         <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,7 +2010,7 @@
         <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2494,10 +2018,10 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2508,7 +2032,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2516,10 +2040,10 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="C68" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2527,10 +2051,10 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="C69" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2538,10 +2062,10 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="C70" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2549,10 +2073,10 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>276</v>
+        <v>221</v>
       </c>
       <c r="C71" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,7 +2087,7 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,7 +2098,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2582,10 +2106,10 @@
         <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>222</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,7 +2120,7 @@
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2604,10 +2128,10 @@
         <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>287</v>
+        <v>232</v>
       </c>
       <c r="C76" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2615,10 +2139,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>278</v>
+        <v>223</v>
       </c>
       <c r="C77" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2626,10 +2150,10 @@
         <v>18</v>
       </c>
       <c r="B78" t="s">
-        <v>279</v>
+        <v>224</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2637,10 +2161,10 @@
         <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>280</v>
+        <v>225</v>
       </c>
       <c r="C79" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,7 +2175,7 @@
         <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,7 +2186,7 @@
         <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2670,10 +2194,10 @@
         <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>285</v>
+        <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,10 +2205,10 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>286</v>
+        <v>231</v>
       </c>
       <c r="C83" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,7 +2219,7 @@
         <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2706,7 +2230,7 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2717,7 +2241,7 @@
         <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,7 +2252,7 @@
         <v>32</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2739,7 +2263,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,7 +2274,7 @@
         <v>36</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2761,7 +2285,7 @@
         <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,7 +2296,7 @@
         <v>40</v>
       </c>
       <c r="C91" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,7 +2307,7 @@
         <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2794,7 +2318,7 @@
         <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,7 +2329,7 @@
         <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,7 +2340,7 @@
         <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2827,7 +2351,7 @@
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2838,7 +2362,7 @@
         <v>52</v>
       </c>
       <c r="C97" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2849,7 +2373,7 @@
         <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2860,7 +2384,7 @@
         <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2871,7 +2395,7 @@
         <v>58</v>
       </c>
       <c r="C100" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,7 +2406,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,7 +2417,7 @@
         <v>62</v>
       </c>
       <c r="C102" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,7 +2428,7 @@
         <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2912,10 +2436,10 @@
         <v>26</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,7 +2450,7 @@
         <v>68</v>
       </c>
       <c r="C105" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,7 +2461,7 @@
         <v>70</v>
       </c>
       <c r="C106" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,7 +2472,7 @@
         <v>72</v>
       </c>
       <c r="C107" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,7 +2483,7 @@
         <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,7 +2494,7 @@
         <v>76</v>
       </c>
       <c r="C109" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,7 +2505,7 @@
         <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,7 +2516,7 @@
         <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,7 +2527,7 @@
         <v>82</v>
       </c>
       <c r="C112" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3011,10 +2535,10 @@
         <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>282</v>
+        <v>227</v>
       </c>
       <c r="C113" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3022,10 +2546,10 @@
         <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>284</v>
+        <v>229</v>
       </c>
       <c r="C114" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,7 +2560,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,7 +2571,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,7 +2582,7 @@
         <v>90</v>
       </c>
       <c r="C117" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,7 +2593,7 @@
         <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,7 +2604,7 @@
         <v>94</v>
       </c>
       <c r="C119" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,7 +2615,7 @@
         <v>96</v>
       </c>
       <c r="C120" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,7 +2626,7 @@
         <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,7 +2637,7 @@
         <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3124,7 +2648,7 @@
         <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,7 +2659,7 @@
         <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,7 +2670,7 @@
         <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,7 +2681,7 @@
         <v>108</v>
       </c>
       <c r="C126" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,7 +2692,7 @@
         <v>110</v>
       </c>
       <c r="C127" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,7 +2703,7 @@
         <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,7 +2714,7 @@
         <v>114</v>
       </c>
       <c r="C129" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,7 +2725,7 @@
         <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,7 +2736,7 @@
         <v>118</v>
       </c>
       <c r="C131" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,7 +2747,7 @@
         <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3234,7 +2758,7 @@
         <v>122</v>
       </c>
       <c r="C133" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,7 +2769,7 @@
         <v>124</v>
       </c>
       <c r="C134" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,7 +2780,7 @@
         <v>126</v>
       </c>
       <c r="C135" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3264,10 +2788,10 @@
         <v>127</v>
       </c>
       <c r="B136" t="s">
-        <v>283</v>
+        <v>228</v>
       </c>
       <c r="C136" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,7 +2802,7 @@
         <v>129</v>
       </c>
       <c r="C137" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3289,7 +2813,7 @@
         <v>131</v>
       </c>
       <c r="C138" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,7 +2824,7 @@
         <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,7 +2835,7 @@
         <v>135</v>
       </c>
       <c r="C140" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,7 +2846,7 @@
         <v>137</v>
       </c>
       <c r="C141" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3333,7 +2857,7 @@
         <v>139</v>
       </c>
       <c r="C142" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,7 +2868,7 @@
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,7 +2879,7 @@
         <v>143</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,876 +2890,876 @@
         <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="B146" t="s">
         <v>135</v>
       </c>
       <c r="C146" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="B147" t="s">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="B149" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="C150" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="B153" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="B154" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="C154" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="B157" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="B158" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="B159" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="C159" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
       <c r="B160" t="s">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="C160" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="C161" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="B162" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="C162" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="B163" t="s">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="C163" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="B164" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="B165" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>320</v>
+        <v>264</v>
       </c>
       <c r="B166" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="C166" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="B167" t="s">
-        <v>317</v>
+        <v>261</v>
       </c>
       <c r="C167" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="B168" t="s">
-        <v>315</v>
+        <v>259</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>281</v>
       </c>
       <c r="B169" t="s">
-        <v>338</v>
+        <v>282</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>339</v>
+        <v>283</v>
       </c>
       <c r="B170" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="C170" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="C171" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="B172" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="C172" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="B173" t="s">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="C173" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
       <c r="B174" t="s">
-        <v>348</v>
+        <v>292</v>
       </c>
       <c r="C174" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="B175" t="s">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="C175" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="C176" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>297</v>
       </c>
       <c r="B177" t="s">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="C177" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>355</v>
+        <v>299</v>
       </c>
       <c r="B178" t="s">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="C178" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="C179" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>303</v>
       </c>
       <c r="B180" t="s">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="C180" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="B181" t="s">
-        <v>362</v>
+        <v>306</v>
       </c>
       <c r="C181" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="B182" t="s">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="C182" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>309</v>
       </c>
       <c r="B183" t="s">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="C183" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>311</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>312</v>
       </c>
       <c r="C184" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>313</v>
       </c>
       <c r="B185" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="C185" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>315</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>316</v>
       </c>
       <c r="C186" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="B187" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
       <c r="C187" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="B188" t="s">
-        <v>376</v>
+        <v>320</v>
       </c>
       <c r="C188" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="B189" t="s">
-        <v>378</v>
+        <v>322</v>
       </c>
       <c r="C189" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>323</v>
       </c>
       <c r="B190" t="s">
-        <v>380</v>
+        <v>324</v>
       </c>
       <c r="C190" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>325</v>
       </c>
       <c r="B191" t="s">
-        <v>382</v>
+        <v>326</v>
       </c>
       <c r="C191" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>327</v>
       </c>
       <c r="B192" t="s">
-        <v>384</v>
+        <v>328</v>
       </c>
       <c r="C192" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>329</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="C193" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>331</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>332</v>
       </c>
       <c r="C194" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>333</v>
       </c>
       <c r="B195" t="s">
-        <v>390</v>
+        <v>334</v>
       </c>
       <c r="C195" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>335</v>
       </c>
       <c r="B196" t="s">
-        <v>392</v>
+        <v>336</v>
       </c>
       <c r="C196" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>337</v>
       </c>
       <c r="B197" t="s">
-        <v>394</v>
+        <v>338</v>
       </c>
       <c r="C197" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>395</v>
+        <v>339</v>
       </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>340</v>
       </c>
       <c r="C198" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>397</v>
+        <v>341</v>
       </c>
       <c r="B199" t="s">
-        <v>398</v>
+        <v>342</v>
       </c>
       <c r="C199" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>399</v>
+        <v>343</v>
       </c>
       <c r="B200" t="s">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="C200" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>401</v>
+        <v>345</v>
       </c>
       <c r="B201" t="s">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="C201" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>403</v>
+        <v>347</v>
       </c>
       <c r="B202" t="s">
-        <v>404</v>
+        <v>348</v>
       </c>
       <c r="C202" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="B203" t="s">
-        <v>406</v>
+        <v>350</v>
       </c>
       <c r="C203" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>407</v>
+        <v>351</v>
       </c>
       <c r="B204" t="s">
-        <v>408</v>
+        <v>352</v>
       </c>
       <c r="C204" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>409</v>
+        <v>353</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>354</v>
       </c>
       <c r="C205" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>411</v>
+        <v>355</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>356</v>
       </c>
       <c r="C206" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>358</v>
       </c>
       <c r="C207" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>359</v>
       </c>
       <c r="B208" t="s">
-        <v>416</v>
+        <v>360</v>
       </c>
       <c r="C208" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>361</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>362</v>
       </c>
       <c r="C209" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>419</v>
+        <v>363</v>
       </c>
       <c r="B210" t="s">
-        <v>420</v>
+        <v>364</v>
       </c>
       <c r="C210" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>365</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="C211" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>367</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>368</v>
       </c>
       <c r="C212" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>369</v>
       </c>
       <c r="B213" t="s">
-        <v>426</v>
+        <v>370</v>
       </c>
       <c r="C213" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>371</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>372</v>
       </c>
       <c r="C214" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="C215" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>375</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>376</v>
       </c>
       <c r="C216" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>378</v>
       </c>
       <c r="C217" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>379</v>
       </c>
       <c r="B218" t="s">
-        <v>436</v>
+        <v>380</v>
       </c>
       <c r="C218" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>381</v>
       </c>
       <c r="B219" t="s">
-        <v>438</v>
+        <v>382</v>
       </c>
       <c r="C219" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>383</v>
       </c>
       <c r="B220" t="s">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="B221" t="s">
-        <v>442</v>
+        <v>386</v>
       </c>
       <c r="C221" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>443</v>
+        <v>387</v>
       </c>
       <c r="B222" t="s">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="C222" t="s">
-        <v>270</v>
+        <v>215</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>445</v>
+        <v>389</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>390</v>
       </c>
       <c r="C223" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>392</v>
       </c>
       <c r="C224" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37618238-51C5-49B9-9327-84E12C9B4DA4}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDECF254-402A-40A1-BF0B-54913ABC69B0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="449">
   <si>
     <t>Job</t>
   </si>
@@ -674,6 +674,171 @@
     <t>34 Jellicoe Street, Martinborough</t>
   </si>
   <si>
+    <t>1082613 - 00037301  - DG Label - 0068841000WR999</t>
+  </si>
+  <si>
+    <t>663 CHESTER ROAD , WEST TARATAHI, CARTERTON, 5791</t>
+  </si>
+  <si>
+    <t>1082609 - 00037241  - DG Label - 1000572372PC23E</t>
+  </si>
+  <si>
+    <t>11 Te Ore Ore Bideford Road , Te Ore Ore, Masterton, 5886</t>
+  </si>
+  <si>
+    <t>1082608 - 00037238  - DG Label - 1000605901PC3C4</t>
+  </si>
+  <si>
+    <t>32 TAMA ROAD , RIVERSDALE BEACH, MASTERTON, 5872</t>
+  </si>
+  <si>
+    <t>1082604 - 00037235 - DG Label - 1000583813PC6B9</t>
+  </si>
+  <si>
+    <t>39A WELD STREET , MARTINBOROUGH, MARTINBOROUGH, 5711</t>
+  </si>
+  <si>
+    <t>1082601 - 00036842 - DG Label - 1000544375PCB18</t>
+  </si>
+  <si>
+    <t>9 FAIRWAY DR , MARTINBOROUGH, MARTINBOROUGH, 5784</t>
+  </si>
+  <si>
+    <t>1082588 - 00035665 - DG Label - 1000624084PCAA5</t>
+  </si>
+  <si>
+    <t>219B GLENMORVEN ROAD , MORISON BUSH, GREYTOWN, 5794</t>
+  </si>
+  <si>
+    <t>1082586 - 00035670 - DG Label - 0060007400WR56A</t>
+  </si>
+  <si>
+    <t>274 HIGH STREET NORTH , CARTERTON, 5713</t>
+  </si>
+  <si>
+    <t>1082585 - 00035668 - DG Label - 0666003845PCD5A</t>
+  </si>
+  <si>
+    <t>433B WAIOHINE GORGE ROAD , CARTERTON, 5791</t>
+  </si>
+  <si>
+    <t>1082584 - 00034018 - DG Label - 0052489000WRDDE</t>
+  </si>
+  <si>
+    <t>1 TAMARISK DR , MASTERTON</t>
+  </si>
+  <si>
+    <t>1082582 - 00034014  - DG Label -0070568100WR40F</t>
+  </si>
+  <si>
+    <t>17 HOMESTEAD LANE , GREYTOWN, GREYTOWN, 5712</t>
+  </si>
+  <si>
+    <t>1082576 - 00031683  - DG Label -0666003622PC96B</t>
+  </si>
+  <si>
+    <t>70B DUBLIN STREET , MARTINBOROUGH, 5711</t>
+  </si>
+  <si>
+    <t>1082574 - 00014488  - DG Label -0037559000WRE8B</t>
+  </si>
+  <si>
+    <t>64 CORNWALL STREET , MASTERTON, 5810</t>
+  </si>
+  <si>
+    <t>1082571 - 00039316 - DG Label - 0000068226CP3F0</t>
+  </si>
+  <si>
+    <t>2 VISCOUNT PLACE, WEST END, PALMERSTON NORTH, 4412</t>
+  </si>
+  <si>
+    <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
+  </si>
+  <si>
+    <t>69 KERERU DRIVE, TURITEA, PALMERSTON NORTH, 4472</t>
+  </si>
+  <si>
+    <t>1082560 - 00052590 - DG Label - 0000048858CP6F1</t>
+  </si>
+  <si>
+    <t>9 HEATHCOTE PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
+    <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
+  </si>
+  <si>
+    <t>180B PHARAZYN ROAD, FEILDING, 4777</t>
+  </si>
+  <si>
+    <t>1082526 - 00044306 - DG Label - 1000605858PCC99</t>
+  </si>
+  <si>
+    <t>1 Cotterville Crescent, Greytown, 5712</t>
+  </si>
+  <si>
+    <t>1082525 - 00042914 - DG Label - 1000574372PC7FE</t>
+  </si>
+  <si>
+    <t>13 MERVYN BROWN PLACE, SOLWAY, MASTERTON, 5810</t>
+  </si>
+  <si>
+    <t>1082504 - 00050338 - DG Label - 1000579124PCE5E</t>
+  </si>
+  <si>
+    <t>4 HUFFINGTON PLACE, FEILDING, FEILDING, 4702</t>
+  </si>
+  <si>
+    <t>1082503 - 00050326 - DG Label - 0900086275PCEC2</t>
+  </si>
+  <si>
+    <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
+    <t>1082492 - 00055639 - DG Label - 0000037890CP0D3</t>
+  </si>
+  <si>
+    <t>41 ESCORT GROVE, AWAPUNI, PALMERSTON NORTH, 4412</t>
+  </si>
+  <si>
+    <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
+  </si>
+  <si>
+    <t>221B State Highway 2, Opaki, Masterton, 5871</t>
+  </si>
+  <si>
+    <t>1082487 - 00042599 - DG Label - 0070237600WR412</t>
+  </si>
+  <si>
+    <t>16 PAPAWAI ROAD, GREYTOWN</t>
+  </si>
+  <si>
+    <t>1082485 - 00052302 - DG Label - 1000615865PCCDB</t>
+  </si>
+  <si>
+    <t>8 GRATITUDE WAY, KELVIN GROVE, PALMERSTON NORTH, 4470</t>
+  </si>
+  <si>
+    <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
+  </si>
+  <si>
+    <t>1082458 - 00054943 - DG Label - 1000624687PC063</t>
+  </si>
+  <si>
+    <t>8 Sardinia Grove, Fitzherbert, Palmerston North</t>
+  </si>
+  <si>
+    <t>1082455 - 00044025 - DG Label - 1000621883PC042</t>
+  </si>
+  <si>
+    <t>6 CASTLEBRIDGE LANE, AOKAUTERE, PALMERSTON NORTH, 4471</t>
+  </si>
+  <si>
+    <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
+  </si>
+  <si>
+    <t>43 COUTTS WAY, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
     <t>1077616 - 00029329  - DG Label</t>
   </si>
   <si>
@@ -747,6 +912,9 @@
   </si>
   <si>
     <t>688 Aranui Road, Kairanga</t>
+  </si>
+  <si>
+    <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
   </si>
   <si>
     <t>45D Brandon Street, Featherston</t>
@@ -1614,29 +1782,337 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>217</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B26" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C29" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>267</v>
       </c>
       <c r="C30" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="C31" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -1644,10 +2120,10 @@
         <v>146</v>
       </c>
       <c r="B32" t="s">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="C32" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1658,7 +2134,7 @@
         <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,7 +2145,7 @@
         <v>150</v>
       </c>
       <c r="C34" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1680,7 +2156,7 @@
         <v>152</v>
       </c>
       <c r="C35" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -1691,7 +2167,7 @@
         <v>154</v>
       </c>
       <c r="C36" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1702,7 +2178,7 @@
         <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1713,7 +2189,7 @@
         <v>158</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -1724,7 +2200,7 @@
         <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1735,7 +2211,7 @@
         <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1746,7 +2222,7 @@
         <v>164</v>
       </c>
       <c r="C41" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -1757,7 +2233,7 @@
         <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1768,7 +2244,7 @@
         <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1779,7 +2255,7 @@
         <v>170</v>
       </c>
       <c r="C44" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1790,7 +2266,7 @@
         <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1798,10 +2274,10 @@
         <v>173</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="C46" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1812,7 +2288,7 @@
         <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1823,7 +2299,7 @@
         <v>177</v>
       </c>
       <c r="C48" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1834,7 +2310,7 @@
         <v>179</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,7 +2321,7 @@
         <v>179</v>
       </c>
       <c r="C50" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1856,7 +2332,7 @@
         <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1867,7 +2343,7 @@
         <v>184</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1878,7 +2354,7 @@
         <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1889,7 +2365,7 @@
         <v>188</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1900,7 +2376,7 @@
         <v>190</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1911,7 +2387,7 @@
         <v>192</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1922,7 +2398,7 @@
         <v>194</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1933,7 +2409,7 @@
         <v>196</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1944,7 +2420,7 @@
         <v>198</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1955,7 +2431,7 @@
         <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1966,7 +2442,7 @@
         <v>202</v>
       </c>
       <c r="C61" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1977,7 +2453,7 @@
         <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1988,7 +2464,7 @@
         <v>206</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1999,7 +2475,7 @@
         <v>208</v>
       </c>
       <c r="C64" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2010,7 +2486,7 @@
         <v>210</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2018,10 +2494,10 @@
         <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>271</v>
       </c>
       <c r="C66" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2032,7 +2508,7 @@
         <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2040,10 +2516,10 @@
         <v>5</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>273</v>
       </c>
       <c r="C68" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2051,10 +2527,10 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2062,10 +2538,10 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2073,10 +2549,10 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="C71" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2087,7 +2563,7 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2098,7 +2574,7 @@
         <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2106,10 +2582,10 @@
         <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2120,7 +2596,7 @@
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2128,10 +2604,10 @@
         <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2139,10 +2615,10 @@
         <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="C77" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2150,10 +2626,10 @@
         <v>18</v>
       </c>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>279</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2161,10 +2637,10 @@
         <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2175,7 +2651,7 @@
         <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2186,7 +2662,7 @@
         <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2194,10 +2670,10 @@
         <v>24</v>
       </c>
       <c r="B82" t="s">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="C82" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2205,10 +2681,10 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="C83" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2219,7 +2695,7 @@
         <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2230,7 +2706,7 @@
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2241,7 +2717,7 @@
         <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2252,7 +2728,7 @@
         <v>32</v>
       </c>
       <c r="C87" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2263,7 +2739,7 @@
         <v>34</v>
       </c>
       <c r="C88" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2274,7 +2750,7 @@
         <v>36</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2285,7 +2761,7 @@
         <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2296,7 +2772,7 @@
         <v>40</v>
       </c>
       <c r="C91" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2307,7 +2783,7 @@
         <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2318,7 +2794,7 @@
         <v>44</v>
       </c>
       <c r="C93" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2329,7 +2805,7 @@
         <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2340,7 +2816,7 @@
         <v>48</v>
       </c>
       <c r="C95" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2351,7 +2827,7 @@
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2362,7 +2838,7 @@
         <v>52</v>
       </c>
       <c r="C97" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2373,7 +2849,7 @@
         <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2384,7 +2860,7 @@
         <v>56</v>
       </c>
       <c r="C99" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2395,7 +2871,7 @@
         <v>58</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2406,7 +2882,7 @@
         <v>60</v>
       </c>
       <c r="C101" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2417,7 +2893,7 @@
         <v>62</v>
       </c>
       <c r="C102" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2428,7 +2904,7 @@
         <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2436,10 +2912,10 @@
         <v>26</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2450,7 +2926,7 @@
         <v>68</v>
       </c>
       <c r="C105" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2461,7 +2937,7 @@
         <v>70</v>
       </c>
       <c r="C106" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2472,7 +2948,7 @@
         <v>72</v>
       </c>
       <c r="C107" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2483,7 +2959,7 @@
         <v>74</v>
       </c>
       <c r="C108" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2494,7 +2970,7 @@
         <v>76</v>
       </c>
       <c r="C109" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2505,7 +2981,7 @@
         <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2516,7 +2992,7 @@
         <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2527,7 +3003,7 @@
         <v>82</v>
       </c>
       <c r="C112" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2535,10 +3011,10 @@
         <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>227</v>
+        <v>282</v>
       </c>
       <c r="C113" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2546,10 +3022,10 @@
         <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="C114" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2560,7 +3036,7 @@
         <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2571,7 +3047,7 @@
         <v>88</v>
       </c>
       <c r="C116" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2582,7 +3058,7 @@
         <v>90</v>
       </c>
       <c r="C117" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2593,7 +3069,7 @@
         <v>92</v>
       </c>
       <c r="C118" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2604,7 +3080,7 @@
         <v>94</v>
       </c>
       <c r="C119" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2615,7 +3091,7 @@
         <v>96</v>
       </c>
       <c r="C120" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2626,7 +3102,7 @@
         <v>98</v>
       </c>
       <c r="C121" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2637,7 +3113,7 @@
         <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2648,7 +3124,7 @@
         <v>102</v>
       </c>
       <c r="C123" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2659,7 +3135,7 @@
         <v>104</v>
       </c>
       <c r="C124" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2670,7 +3146,7 @@
         <v>106</v>
       </c>
       <c r="C125" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2681,7 +3157,7 @@
         <v>108</v>
       </c>
       <c r="C126" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2692,7 +3168,7 @@
         <v>110</v>
       </c>
       <c r="C127" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2703,7 +3179,7 @@
         <v>112</v>
       </c>
       <c r="C128" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2714,7 +3190,7 @@
         <v>114</v>
       </c>
       <c r="C129" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2725,7 +3201,7 @@
         <v>116</v>
       </c>
       <c r="C130" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2736,7 +3212,7 @@
         <v>118</v>
       </c>
       <c r="C131" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2747,7 +3223,7 @@
         <v>120</v>
       </c>
       <c r="C132" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2758,7 +3234,7 @@
         <v>122</v>
       </c>
       <c r="C133" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2769,7 +3245,7 @@
         <v>124</v>
       </c>
       <c r="C134" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2780,7 +3256,7 @@
         <v>126</v>
       </c>
       <c r="C135" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2788,10 +3264,10 @@
         <v>127</v>
       </c>
       <c r="B136" t="s">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="C136" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2802,7 +3278,7 @@
         <v>129</v>
       </c>
       <c r="C137" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2813,7 +3289,7 @@
         <v>131</v>
       </c>
       <c r="C138" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2824,7 +3300,7 @@
         <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2835,7 +3311,7 @@
         <v>135</v>
       </c>
       <c r="C140" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2846,7 +3322,7 @@
         <v>137</v>
       </c>
       <c r="C141" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2857,7 +3333,7 @@
         <v>139</v>
       </c>
       <c r="C142" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2868,7 +3344,7 @@
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2879,7 +3355,7 @@
         <v>143</v>
       </c>
       <c r="C144" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2890,876 +3366,876 @@
         <v>145</v>
       </c>
       <c r="C145" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="B146" t="s">
         <v>135</v>
       </c>
       <c r="C146" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B147" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="C147" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="B148" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="C148" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="C149" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>243</v>
+        <v>299</v>
       </c>
       <c r="B150" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="C150" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="B151" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="B152" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="B153" t="s">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="B154" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="C154" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="B155" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="C155" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="B156" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="B157" t="s">
-        <v>251</v>
+        <v>307</v>
       </c>
       <c r="C157" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B158" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="B159" t="s">
-        <v>277</v>
+        <v>333</v>
       </c>
       <c r="C159" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="B160" t="s">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="C160" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="C161" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="B162" t="s">
-        <v>271</v>
+        <v>327</v>
       </c>
       <c r="C162" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>269</v>
+        <v>325</v>
       </c>
       <c r="C163" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="B164" t="s">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="C164" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="B165" t="s">
-        <v>265</v>
+        <v>321</v>
       </c>
       <c r="C165" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>264</v>
+        <v>320</v>
       </c>
       <c r="B166" t="s">
-        <v>263</v>
+        <v>319</v>
       </c>
       <c r="C166" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>262</v>
+        <v>318</v>
       </c>
       <c r="B167" t="s">
-        <v>261</v>
+        <v>317</v>
       </c>
       <c r="C167" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="B168" t="s">
-        <v>259</v>
+        <v>315</v>
       </c>
       <c r="C168" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="B169" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="C169" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="B170" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="C170" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="B171" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="C171" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="B172" t="s">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="C172" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="B173" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="C173" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="B174" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="C174" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="B175" t="s">
-        <v>294</v>
+        <v>350</v>
       </c>
       <c r="C175" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>295</v>
+        <v>351</v>
       </c>
       <c r="B176" t="s">
-        <v>296</v>
+        <v>352</v>
       </c>
       <c r="C176" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>297</v>
+        <v>353</v>
       </c>
       <c r="B177" t="s">
-        <v>298</v>
+        <v>354</v>
       </c>
       <c r="C177" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="C178" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>301</v>
+        <v>357</v>
       </c>
       <c r="B179" t="s">
-        <v>302</v>
+        <v>358</v>
       </c>
       <c r="C179" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>303</v>
+        <v>359</v>
       </c>
       <c r="B180" t="s">
-        <v>304</v>
+        <v>360</v>
       </c>
       <c r="C180" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>305</v>
+        <v>361</v>
       </c>
       <c r="B181" t="s">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="C181" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>307</v>
+        <v>363</v>
       </c>
       <c r="B182" t="s">
-        <v>308</v>
+        <v>364</v>
       </c>
       <c r="C182" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="B183" t="s">
-        <v>310</v>
+        <v>366</v>
       </c>
       <c r="C183" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="B184" t="s">
-        <v>312</v>
+        <v>368</v>
       </c>
       <c r="C184" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>313</v>
+        <v>369</v>
       </c>
       <c r="B185" t="s">
-        <v>314</v>
+        <v>370</v>
       </c>
       <c r="C185" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="B186" t="s">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="C186" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>317</v>
+        <v>373</v>
       </c>
       <c r="B187" t="s">
-        <v>318</v>
+        <v>374</v>
       </c>
       <c r="C187" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>319</v>
+        <v>375</v>
       </c>
       <c r="B188" t="s">
-        <v>320</v>
+        <v>376</v>
       </c>
       <c r="C188" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>321</v>
+        <v>377</v>
       </c>
       <c r="B189" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="C189" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>323</v>
+        <v>379</v>
       </c>
       <c r="B190" t="s">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="C190" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>325</v>
+        <v>381</v>
       </c>
       <c r="B191" t="s">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="C191" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>327</v>
+        <v>383</v>
       </c>
       <c r="B192" t="s">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="C192" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>329</v>
+        <v>385</v>
       </c>
       <c r="B193" t="s">
-        <v>330</v>
+        <v>386</v>
       </c>
       <c r="C193" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>331</v>
+        <v>387</v>
       </c>
       <c r="B194" t="s">
-        <v>332</v>
+        <v>388</v>
       </c>
       <c r="C194" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>333</v>
+        <v>389</v>
       </c>
       <c r="B195" t="s">
-        <v>334</v>
+        <v>390</v>
       </c>
       <c r="C195" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="B196" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="C196" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="B197" t="s">
-        <v>338</v>
+        <v>394</v>
       </c>
       <c r="C197" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="B198" t="s">
-        <v>340</v>
+        <v>396</v>
       </c>
       <c r="C198" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>341</v>
+        <v>397</v>
       </c>
       <c r="B199" t="s">
-        <v>342</v>
+        <v>398</v>
       </c>
       <c r="C199" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>343</v>
+        <v>399</v>
       </c>
       <c r="B200" t="s">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="C200" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>345</v>
+        <v>401</v>
       </c>
       <c r="B201" t="s">
-        <v>346</v>
+        <v>402</v>
       </c>
       <c r="C201" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>347</v>
+        <v>403</v>
       </c>
       <c r="B202" t="s">
-        <v>348</v>
+        <v>404</v>
       </c>
       <c r="C202" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>349</v>
+        <v>405</v>
       </c>
       <c r="B203" t="s">
-        <v>350</v>
+        <v>406</v>
       </c>
       <c r="C203" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>351</v>
+        <v>407</v>
       </c>
       <c r="B204" t="s">
-        <v>352</v>
+        <v>408</v>
       </c>
       <c r="C204" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>353</v>
+        <v>409</v>
       </c>
       <c r="B205" t="s">
-        <v>354</v>
+        <v>410</v>
       </c>
       <c r="C205" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>355</v>
+        <v>411</v>
       </c>
       <c r="B206" t="s">
-        <v>356</v>
+        <v>412</v>
       </c>
       <c r="C206" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>357</v>
+        <v>413</v>
       </c>
       <c r="B207" t="s">
-        <v>358</v>
+        <v>414</v>
       </c>
       <c r="C207" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>359</v>
+        <v>415</v>
       </c>
       <c r="B208" t="s">
-        <v>360</v>
+        <v>416</v>
       </c>
       <c r="C208" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>361</v>
+        <v>417</v>
       </c>
       <c r="B209" t="s">
-        <v>362</v>
+        <v>418</v>
       </c>
       <c r="C209" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="B210" t="s">
-        <v>364</v>
+        <v>420</v>
       </c>
       <c r="C210" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="B211" t="s">
-        <v>366</v>
+        <v>422</v>
       </c>
       <c r="C211" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>367</v>
+        <v>423</v>
       </c>
       <c r="B212" t="s">
-        <v>368</v>
+        <v>424</v>
       </c>
       <c r="C212" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>369</v>
+        <v>425</v>
       </c>
       <c r="B213" t="s">
-        <v>370</v>
+        <v>426</v>
       </c>
       <c r="C213" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>371</v>
+        <v>427</v>
       </c>
       <c r="B214" t="s">
-        <v>372</v>
+        <v>428</v>
       </c>
       <c r="C214" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>373</v>
+        <v>429</v>
       </c>
       <c r="B215" t="s">
-        <v>374</v>
+        <v>430</v>
       </c>
       <c r="C215" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="B216" t="s">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="C216" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="B217" t="s">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="C217" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="B218" t="s">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="C218" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
       <c r="B219" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="C219" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="B220" t="s">
-        <v>384</v>
+        <v>440</v>
       </c>
       <c r="C220" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="B221" t="s">
-        <v>386</v>
+        <v>442</v>
       </c>
       <c r="C221" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>387</v>
+        <v>443</v>
       </c>
       <c r="B222" t="s">
-        <v>388</v>
+        <v>444</v>
       </c>
       <c r="C222" t="s">
-        <v>215</v>
+        <v>270</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>389</v>
+        <v>445</v>
       </c>
       <c r="B223" t="s">
-        <v>390</v>
+        <v>446</v>
       </c>
       <c r="C223" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>391</v>
+        <v>447</v>
       </c>
       <c r="B224" t="s">
-        <v>392</v>
+        <v>448</v>
       </c>
       <c r="C224" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF68EE7-DA39-4A83-9138-C38E883080C4}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDECF254-402A-40A1-BF0B-54913ABC69B0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/DG-Map/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDECF254-402A-40A1-BF0B-54913ABC69B0}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0163497-7145-42C9-AE76-0A7DA26321C1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="462">
   <si>
     <t>Job</t>
   </si>
@@ -1386,6 +1386,45 @@
   </si>
   <si>
     <t>5 Te Arakura Road, Newbury</t>
+  </si>
+  <si>
+    <t>1085844 - 00035552 - DG Label</t>
+  </si>
+  <si>
+    <t>1085843 - 00063446 - DG Label</t>
+  </si>
+  <si>
+    <t>13 Fantail Avenue, Carterton</t>
+  </si>
+  <si>
+    <t>1085842 - 00059955 - DG Label</t>
+  </si>
+  <si>
+    <t>572 Kelvin Grove Road, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1085841 - 00060910 - DG Label</t>
+  </si>
+  <si>
+    <t>20B Donovans Road, Masterton</t>
+  </si>
+  <si>
+    <t>1085840 - 00062204 - DG Label</t>
+  </si>
+  <si>
+    <t>24 Pokerekere Crescent, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1085839 - 00061211 - DG Label</t>
+  </si>
+  <si>
+    <t>100C Linton Street, West End</t>
+  </si>
+  <si>
+    <t>1085838 - 00058379 - DG Label</t>
+  </si>
+  <si>
+    <t>2E Hogg Crescent, Masterton</t>
   </si>
 </sst>
 </file>
@@ -1447,6 +1486,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1766,7 +1809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C224"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4238,6 +4281,83 @@
         <v>269</v>
       </c>
     </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>449</v>
+      </c>
+      <c r="B225" t="s">
+        <v>398</v>
+      </c>
+      <c r="C225" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>450</v>
+      </c>
+      <c r="B226" t="s">
+        <v>451</v>
+      </c>
+      <c r="C226" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>452</v>
+      </c>
+      <c r="B227" t="s">
+        <v>453</v>
+      </c>
+      <c r="C227" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" t="s">
+        <v>455</v>
+      </c>
+      <c r="C228" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>456</v>
+      </c>
+      <c r="B229" t="s">
+        <v>457</v>
+      </c>
+      <c r="C229" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>458</v>
+      </c>
+      <c r="B230" t="s">
+        <v>459</v>
+      </c>
+      <c r="C230" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>460</v>
+      </c>
+      <c r="B231" t="s">
+        <v>461</v>
+      </c>
+      <c r="C231" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82B78C04-7E2F-44D3-8745-903B049DC371}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B6B855-DCFF-4DFF-B582-FBDD989915CA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="462">
   <si>
     <t>Job</t>
   </si>
@@ -47,6 +47,633 @@
     <t>Site</t>
   </si>
   <si>
+    <t>1084531 - 00060784 - DG Label</t>
+  </si>
+  <si>
+    <t>1084467 - 00055841 - DG Label</t>
+  </si>
+  <si>
+    <t>685 Kairanga Bunnythorpe Road</t>
+  </si>
+  <si>
+    <t>1084466 - 00057025 - DG Label</t>
+  </si>
+  <si>
+    <t>1084464 - 00050442 - DG Label</t>
+  </si>
+  <si>
+    <t>1084462 - 00048230 - DG Label</t>
+  </si>
+  <si>
+    <t>1084461 - 00050984 - DG Label</t>
+  </si>
+  <si>
+    <t>1084307 - 00059085 - DG Label</t>
+  </si>
+  <si>
+    <t>985 Parewanui Road, Bulls</t>
+  </si>
+  <si>
+    <t>1084306 - 00052857 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Kaka Road, Taihape</t>
+  </si>
+  <si>
+    <t>1084171 - 00014163 - DG Label</t>
+  </si>
+  <si>
+    <t>1084156 - 00027186 - DG Label</t>
+  </si>
+  <si>
+    <t>The Lido</t>
+  </si>
+  <si>
+    <t>1084083 - 00057507 - DG Label</t>
+  </si>
+  <si>
+    <t>1084081 - 00056505 - DG Label</t>
+  </si>
+  <si>
+    <t>1084080 - 00054165 - DG Label</t>
+  </si>
+  <si>
+    <t>1084079 - 00059083 - DG Label</t>
+  </si>
+  <si>
+    <t>1084059 - 00051796 - DG Label</t>
+  </si>
+  <si>
+    <t>389a Bluff Rangitumau Road</t>
+  </si>
+  <si>
+    <t>1084058 - 00035372 - DG Label</t>
+  </si>
+  <si>
+    <t>1727 State Highway 2</t>
+  </si>
+  <si>
+    <t>1084056 - 00054197 - DG Label</t>
+  </si>
+  <si>
+    <t>1084055 - 00021842 - DG Label</t>
+  </si>
+  <si>
+    <t>1084053 - 00050380 - DG Label</t>
+  </si>
+  <si>
+    <t>1083913 - 00050014 - DG Label</t>
+  </si>
+  <si>
+    <t>8 Toia Street, Marton</t>
+  </si>
+  <si>
+    <t>1083912 - 00050108 - DG Label</t>
+  </si>
+  <si>
+    <t>49 Weld Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1083909 - 00051891 - DG Label</t>
+  </si>
+  <si>
+    <t>16 Mersey Street, Rongotea</t>
+  </si>
+  <si>
+    <t>1083906 - 00047054 - DG Label</t>
+  </si>
+  <si>
+    <t>10 Malcolm Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1083905 - 00046581 - DG Label</t>
+  </si>
+  <si>
+    <t>43 Taranaki Street, Masterton</t>
+  </si>
+  <si>
+    <t>1083903 - 00049965 - DG Label</t>
+  </si>
+  <si>
+    <t>54 Richmond Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083901 - 00055289 - DG Label</t>
+  </si>
+  <si>
+    <t>353 Kahuterawa Road, Linton</t>
+  </si>
+  <si>
+    <t>1083900 - 00049959 - DG Label</t>
+  </si>
+  <si>
+    <t>290D Dakins Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083715 - 00056130 - DG Label</t>
+  </si>
+  <si>
+    <t>12 Plimsoll Street, Carterton</t>
+  </si>
+  <si>
+    <t>1083714 - 00046993 - DG Label</t>
+  </si>
+  <si>
+    <t>15 John McDonald Mews, Masterton</t>
+  </si>
+  <si>
+    <t>1083713 - 00050713 - DG Label</t>
+  </si>
+  <si>
+    <t>46D Cromarty Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>1083712 - 00046578 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Roger Renall Avenue, Lansdowne</t>
+  </si>
+  <si>
+    <t>1083711 - 00050685 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Wakefield Street, Featherston</t>
+  </si>
+  <si>
+    <t>1083709 - 00042593 - DG Label</t>
+  </si>
+  <si>
+    <t>17 Richmond Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083708 - 00055068 - DG Label</t>
+  </si>
+  <si>
+    <t>215 Calico Line, Marton</t>
+  </si>
+  <si>
+    <t>1083706 - 00039727 - DG Label</t>
+  </si>
+  <si>
+    <t>24 Ardsley Lane, Lansdowne</t>
+  </si>
+  <si>
+    <t>1083705 - 00031383 - DG Label</t>
+  </si>
+  <si>
+    <t>10 Alton Grove, Masterton</t>
+  </si>
+  <si>
+    <t>1083699 - 00059938 - DG Label</t>
+  </si>
+  <si>
+    <t>1009 Taonui Road, Colyton</t>
+  </si>
+  <si>
+    <t>1083697 - 00050711 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Nelsons Road, Martinborough</t>
+  </si>
+  <si>
+    <t>1083694 - 00052240 - DG Label</t>
+  </si>
+  <si>
+    <t>48 Raetihi Ohakune Road, Raetihi</t>
+  </si>
+  <si>
+    <t>1083539 - 00047551 - DG Label</t>
+  </si>
+  <si>
+    <t>Willow Park Drive, Opaki</t>
+  </si>
+  <si>
+    <t>1083538 - 00025313 - DG Label</t>
+  </si>
+  <si>
+    <t>329 Chester Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083537 - 00051885 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Mervyn Brown Place, Solway</t>
+  </si>
+  <si>
+    <t>1083536 - 00051887 - DG Label</t>
+  </si>
+  <si>
+    <t>18 Moore Crescent, Carterton</t>
+  </si>
+  <si>
+    <t>1083533 - 00046992 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Third Street, Masterton</t>
+  </si>
+  <si>
+    <t>1083531 - 00049940 - DG Label</t>
+  </si>
+  <si>
+    <t>82 Brandon Street, Featherston</t>
+  </si>
+  <si>
+    <t>1083530 - 00047843 - DG Label</t>
+  </si>
+  <si>
+    <t>45A Murphys Line, Featherston</t>
+  </si>
+  <si>
+    <t>1083528 - 00046079 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Kākāriki Crescent, Carterton</t>
+  </si>
+  <si>
+    <t>1083527 - 00043587 - DG Label</t>
+  </si>
+  <si>
+    <t>1083524 - 00043172 - DG Label</t>
+  </si>
+  <si>
+    <t>1083521 - 00043163 - DG Label</t>
+  </si>
+  <si>
+    <t>50 Brooklyn Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083520 - 00040965 - DG Label</t>
+  </si>
+  <si>
+    <t>2 Horton Street, Greytown</t>
+  </si>
+  <si>
+    <t>1083519 - 00034917 - DG Label</t>
+  </si>
+  <si>
+    <t>13 Donald Street, Featherston</t>
+  </si>
+  <si>
+    <t>1083517 - 00038450 - DG Label</t>
+  </si>
+  <si>
+    <t>52B Willow Park Drive, Masterton</t>
+  </si>
+  <si>
+    <t>1083516 - 00028358 - DG Label</t>
+  </si>
+  <si>
+    <t>129B Kent Street, Carterton</t>
+  </si>
+  <si>
+    <t>1083515 - 00031167 - DG Label</t>
+  </si>
+  <si>
+    <t>201 Masterton Castlepoint Road, Te Ore Ore</t>
+  </si>
+  <si>
+    <t>1083514 - 00028935 - DG Label</t>
+  </si>
+  <si>
+    <t>78 Lake Domain Road, Featherston</t>
+  </si>
+  <si>
+    <t>1083513 - 00025964 - DG Label</t>
+  </si>
+  <si>
+    <t>21 Feist Street, Carterton</t>
+  </si>
+  <si>
+    <t>1083512 - 00041933 - DG Label</t>
+  </si>
+  <si>
+    <t>117 Chester Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083511 - 00025515 - DG Label</t>
+  </si>
+  <si>
+    <t>20 Carrington Drive, Carterton</t>
+  </si>
+  <si>
+    <t>1083509 - 00031620 - DG Label</t>
+  </si>
+  <si>
+    <t>90E Paierau Road, Masterton</t>
+  </si>
+  <si>
+    <t>1083508 - 00031621 - DG Label</t>
+  </si>
+  <si>
+    <t>26A South Belt, Solway</t>
+  </si>
+  <si>
+    <t>1083507 - 00047943 - DG Label</t>
+  </si>
+  <si>
+    <t>55 Herbert Street, Masterton</t>
+  </si>
+  <si>
+    <t>1083506 - 00047944 - DG Label</t>
+  </si>
+  <si>
+    <t>142A Dublin Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1083503 - 00055234 - DG Label</t>
+  </si>
+  <si>
+    <t>570 Roberts Line, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1083193 - 00058143 - DG Label</t>
+  </si>
+  <si>
+    <t>152 Turitea Road, Turitea</t>
+  </si>
+  <si>
+    <t>1083189 - 00055734 - DG Label</t>
+  </si>
+  <si>
+    <t>101 Upper Manaia Road, Solway</t>
+  </si>
+  <si>
+    <t>1083188 - 00049152 - DG Label</t>
+  </si>
+  <si>
+    <t>16 Parkers Road, Carterton</t>
+  </si>
+  <si>
+    <t>1083186 - 00051708 - DG Label</t>
+  </si>
+  <si>
+    <t>346 State Highway 1, Foxton</t>
+  </si>
+  <si>
+    <t>1083184 - 00055338 - DG Label</t>
+  </si>
+  <si>
+    <t>499 Taikorea Road, Glen Oroua</t>
+  </si>
+  <si>
+    <t>1083182 - 00055894 - DG Label</t>
+  </si>
+  <si>
+    <t>22 South Street, Feilding</t>
+  </si>
+  <si>
+    <t>1083181 - 00049193 - DG Label</t>
+  </si>
+  <si>
+    <t>1083037 - 00042253 - DG Label</t>
+  </si>
+  <si>
+    <t>2 Kaka Street, Masterton</t>
+  </si>
+  <si>
+    <t>1083036 - 00050431 - DG Label</t>
+  </si>
+  <si>
+    <t>722 Upper Plain Road, Masterton</t>
+  </si>
+  <si>
+    <t>1083033 - 00039972 - DG Label</t>
+  </si>
+  <si>
+    <t>20 Langley Avenue, Milson</t>
+  </si>
+  <si>
+    <t>1083023 - 00022620 - DG Label</t>
+  </si>
+  <si>
+    <t>124 Works Road, Longburn</t>
+  </si>
+  <si>
+    <t>1083021 - 00029369 - DG Label</t>
+  </si>
+  <si>
+    <t>43 Fitzherbert Street, Featherston</t>
+  </si>
+  <si>
+    <t>1082897 - 00051235 - DG Label</t>
+  </si>
+  <si>
+    <t>87A Worcester Street, Ashhurst</t>
+  </si>
+  <si>
+    <t>1082873 - 00037497 - DG Label</t>
+  </si>
+  <si>
+    <t>30A McMaster Street, Greytown</t>
+  </si>
+  <si>
+    <t>1082869 - 00043761 - DG Label</t>
+  </si>
+  <si>
+    <t>429A Black Rock Road, Masterton</t>
+  </si>
+  <si>
+    <t>1082793 - 00047634 - DG Label</t>
+  </si>
+  <si>
+    <t>11 Humphries Street, Greytown</t>
+  </si>
+  <si>
+    <t>1082792 - 00051464 - DG Label</t>
+  </si>
+  <si>
+    <t>1082791 - 00042426 - DG Label</t>
+  </si>
+  <si>
+    <t>56 FREDERICK ST, CARTERTON</t>
+  </si>
+  <si>
+    <t>1082789 - 00029633 - DG Label</t>
+  </si>
+  <si>
+    <t>682 ROBERTS LINE, PALMERSTON NORTH</t>
+  </si>
+  <si>
+    <t>1082787 - 00054940 - DG Label</t>
+  </si>
+  <si>
+    <t>69 Duncan Road, Rongotea</t>
+  </si>
+  <si>
+    <t>1082687 - 00058152 - DG Label</t>
+  </si>
+  <si>
+    <t>45 Abraham Crescent, Milson</t>
+  </si>
+  <si>
+    <t>1082684 - 00052888 - DG Label</t>
+  </si>
+  <si>
+    <t>479 Ngaio Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1082681 - 00025645 - DG Label</t>
+  </si>
+  <si>
+    <t>66 Pearce Street, Halcombe</t>
+  </si>
+  <si>
+    <t>1082680 - 00038748 - DG Label</t>
+  </si>
+  <si>
+    <t>2562 Homewood Road, Masterton</t>
+  </si>
+  <si>
+    <t>1082679 - 00027851 - DG Label</t>
+  </si>
+  <si>
+    <t>18 Ataahua Place, Featherston</t>
+  </si>
+  <si>
+    <t>1082675 - 00025196 - DG Label</t>
+  </si>
+  <si>
+    <t>241 Kahuterawa Road, Linton</t>
+  </si>
+  <si>
+    <t>1082671 - 00016526 - DG Label</t>
+  </si>
+  <si>
+    <t>728 Taonui Road</t>
+  </si>
+  <si>
+    <t>1082666 - 00029367 - DG Label</t>
+  </si>
+  <si>
+    <t>769A State Highway 2, Masterton</t>
+  </si>
+  <si>
+    <t>1082663 - 00032564 - DG Label</t>
+  </si>
+  <si>
+    <t>324 Moreton Road, Carterton</t>
+  </si>
+  <si>
+    <t>1082655 - 00052975 - DG Label</t>
+  </si>
+  <si>
+    <t>Junction Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1082641 - 00032322 - DG Label</t>
+  </si>
+  <si>
+    <t>1082309 - 00027982 - DG Label</t>
+  </si>
+  <si>
+    <t>881C Norfolk Road, Carterton</t>
+  </si>
+  <si>
+    <t>1082308 - 00036363 - DG Label</t>
+  </si>
+  <si>
+    <t>60E Skeets Road, Masterton</t>
+  </si>
+  <si>
+    <t>1082303 - 00046835 - DG Label</t>
+  </si>
+  <si>
+    <t>23 Fry Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1082300 - 00046363 - DG Label</t>
+  </si>
+  <si>
+    <t>1082166 - 00052136 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Bristow Street, Saint Johns Hill</t>
+  </si>
+  <si>
+    <t>1082165 - 00046105 - DG Label</t>
+  </si>
+  <si>
+    <t>95 Mingaroa Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1082157 - 00045590 - DG Label</t>
+  </si>
+  <si>
+    <t>83 Ngahere Park Road, Palmerston North</t>
+  </si>
+  <si>
+    <t>1082153 - 00045468 - DG Label</t>
+  </si>
+  <si>
+    <t>48 Woodward Street East, Featherston</t>
+  </si>
+  <si>
+    <t>1082152 - 00039772 - DG Label</t>
+  </si>
+  <si>
+    <t>94 Lake Domain Road, Featherston</t>
+  </si>
+  <si>
+    <t>1082150 - 00043307 - DG Label</t>
+  </si>
+  <si>
+    <t>68 London Street, Kimbolton</t>
+  </si>
+  <si>
+    <t>1082148 - 00049360 - DG Label</t>
+  </si>
+  <si>
+    <t>11 Moore Street, Featherston</t>
+  </si>
+  <si>
+    <t>1081142 - 00042583 - DG Label</t>
+  </si>
+  <si>
+    <t>6B Prendiville Lane, Greytown</t>
+  </si>
+  <si>
+    <t>1081138 - 00037296 - DG Label</t>
+  </si>
+  <si>
+    <t>67 Naples Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1081088 - 00032869 - DG Label</t>
+  </si>
+  <si>
+    <t>73A Reading Street, Greytown</t>
+  </si>
+  <si>
+    <t>1080323 - 00040962 - DG Label</t>
+  </si>
+  <si>
+    <t>19 McMaster Street, Greytown</t>
+  </si>
+  <si>
+    <t>1080313 - 00036332 - DG Label</t>
+  </si>
+  <si>
+    <t>621 Lake Ferry Road, Martinborough</t>
+  </si>
+  <si>
+    <t>1080299 - 00047942 - DG Label</t>
+  </si>
+  <si>
+    <t>2 Churchill Crescent, Featherston</t>
+  </si>
+  <si>
+    <t>1080270 - 00041117 - DG Label</t>
+  </si>
+  <si>
+    <t>38 Cologne Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1080268 - 00034177 - DG Label</t>
+  </si>
+  <si>
+    <t>34 Jellicoe Street, Martinborough</t>
+  </si>
+  <si>
     <t>1082613 - 00037301  - DG Label - 0068841000WR999</t>
   </si>
   <si>
@@ -89,23 +716,732 @@
     <t>274 HIGH STREET NORTH , CARTERTON, 5713</t>
   </si>
   <si>
+    <t>1082585 - 00035668 - DG Label - 0666003845PCD5A</t>
+  </si>
+  <si>
+    <t>433B WAIOHINE GORGE ROAD , CARTERTON, 5791</t>
+  </si>
+  <si>
+    <t>1082584 - 00034018 - DG Label - 0052489000WRDDE</t>
+  </si>
+  <si>
+    <t>1 TAMARISK DR , MASTERTON</t>
+  </si>
+  <si>
+    <t>1082582 - 00034014  - DG Label -0070568100WR40F</t>
+  </si>
+  <si>
+    <t>17 HOMESTEAD LANE , GREYTOWN, GREYTOWN, 5712</t>
+  </si>
+  <si>
+    <t>1082576 - 00031683  - DG Label -0666003622PC96B</t>
+  </si>
+  <si>
+    <t>70B DUBLIN STREET , MARTINBOROUGH, 5711</t>
+  </si>
+  <si>
+    <t>1082574 - 00014488  - DG Label -0037559000WRE8B</t>
+  </si>
+  <si>
+    <t>64 CORNWALL STREET , MASTERTON, 5810</t>
+  </si>
+  <si>
+    <t>1082571 - 00039316 - DG Label - 0000068226CP3F0</t>
+  </si>
+  <si>
+    <t>2 VISCOUNT PLACE, WEST END, PALMERSTON NORTH, 4412</t>
+  </si>
+  <si>
+    <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
+  </si>
+  <si>
+    <t>69 KERERU DRIVE, TURITEA, PALMERSTON NORTH, 4472</t>
+  </si>
+  <si>
+    <t>1082560 - 00052590 - DG Label - 0000048858CP6F1</t>
+  </si>
+  <si>
+    <t>9 HEATHCOTE PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
+    <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
+  </si>
+  <si>
+    <t>180B PHARAZYN ROAD, FEILDING, 4777</t>
+  </si>
+  <si>
+    <t>1082526 - 00044306 - DG Label - 1000605858PCC99</t>
+  </si>
+  <si>
+    <t>1 Cotterville Crescent, Greytown, 5712</t>
+  </si>
+  <si>
+    <t>1082525 - 00042914 - DG Label - 1000574372PC7FE</t>
+  </si>
+  <si>
+    <t>13 MERVYN BROWN PLACE, SOLWAY, MASTERTON, 5810</t>
+  </si>
+  <si>
+    <t>1082504 - 00050338 - DG Label - 1000579124PCE5E</t>
+  </si>
+  <si>
+    <t>4 HUFFINGTON PLACE, FEILDING, FEILDING, 4702</t>
+  </si>
+  <si>
+    <t>1082503 - 00050326 - DG Label - 0900086275PCEC2</t>
+  </si>
+  <si>
+    <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
+    <t>1082492 - 00055639 - DG Label - 0000037890CP0D3</t>
+  </si>
+  <si>
+    <t>41 ESCORT GROVE, AWAPUNI, PALMERSTON NORTH, 4412</t>
+  </si>
+  <si>
+    <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
+  </si>
+  <si>
+    <t>221B State Highway 2, Opaki, Masterton, 5871</t>
+  </si>
+  <si>
+    <t>1082487 - 00042599 - DG Label - 0070237600WR412</t>
+  </si>
+  <si>
+    <t>16 PAPAWAI ROAD, GREYTOWN</t>
+  </si>
+  <si>
+    <t>1082485 - 00052302 - DG Label - 1000615865PCCDB</t>
+  </si>
+  <si>
+    <t>8 GRATITUDE WAY, KELVIN GROVE, PALMERSTON NORTH, 4470</t>
+  </si>
+  <si>
+    <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
+  </si>
+  <si>
+    <t>1082458 - 00054943 - DG Label - 1000624687PC063</t>
+  </si>
+  <si>
+    <t>8 Sardinia Grove, Fitzherbert, Palmerston North</t>
+  </si>
+  <si>
+    <t>1082455 - 00044025 - DG Label - 1000621883PC042</t>
+  </si>
+  <si>
+    <t>6 CASTLEBRIDGE LANE, AOKAUTERE, PALMERSTON NORTH, 4471</t>
+  </si>
+  <si>
+    <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
+  </si>
+  <si>
+    <t>43 COUTTS WAY, FITZHERBERT, PALMERSTON NORTH, 4410</t>
+  </si>
+  <si>
+    <t>1077616 - 00029329  - DG Label</t>
+  </si>
+  <si>
+    <t>39 Craigmillar Street, Solway, Masterton</t>
+  </si>
+  <si>
+    <t>1077614 - 00023887 - DG Label</t>
+  </si>
+  <si>
     <t>OH</t>
   </si>
   <si>
     <t>UG</t>
   </si>
   <si>
+    <t>143 Watershed Road, Bunnythorpe</t>
+  </si>
+  <si>
     <t>Type</t>
+  </si>
+  <si>
+    <t>231 Valley Views, Palmerston North</t>
+  </si>
+  <si>
+    <t>99A Lees Pakaraka Road, Masterton</t>
+  </si>
+  <si>
+    <t>67A Perry Street, Masterton</t>
+  </si>
+  <si>
+    <t>80 West Street, Greytown</t>
+  </si>
+  <si>
+    <t>89 Dublin Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1853 Rongotea Road, Rongotea</t>
+  </si>
+  <si>
+    <t>4 Wake Place, Aokautere</t>
+  </si>
+  <si>
+    <t>5 Castlebridge Lane, Aokautere</t>
+  </si>
+  <si>
+    <t>208 Smiths Road, Ohakune</t>
+  </si>
+  <si>
+    <t>46A Main Street, Greytown</t>
+  </si>
+  <si>
+    <t>95 Pyke Road, Rangitou</t>
+  </si>
+  <si>
+    <t>431C Te Kopi Road, Te Whiti</t>
+  </si>
+  <si>
+    <t>57 White Rock Road, Martinborough</t>
+  </si>
+  <si>
+    <t>16 Madden Place, Masterton</t>
+  </si>
+  <si>
+    <t>3 Paterson Lane, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>Nga Waka Winery, Martinborough</t>
+  </si>
+  <si>
+    <t>506 Longbush Road, Hinakura</t>
+  </si>
+  <si>
+    <t>688 Aranui Road, Kairanga</t>
+  </si>
+  <si>
+    <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
+  </si>
+  <si>
+    <t>45D Brandon Street, Featherston</t>
+  </si>
+  <si>
+    <t>1084698 - 00058929 - DG Label</t>
+  </si>
+  <si>
+    <t>122 Hewitts Road, Linton</t>
+  </si>
+  <si>
+    <t>1084699 - 00053230 - DG Label</t>
+  </si>
+  <si>
+    <t>84 North Street, Ashhurst</t>
+  </si>
+  <si>
+    <t>1084701 - 00054540 - DG Label</t>
+  </si>
+  <si>
+    <t>296 Cambridge Avenue, Ashhurst</t>
+  </si>
+  <si>
+    <t>1084702 - 00052539 - DG Label</t>
+  </si>
+  <si>
+    <t>29 Rexwood Street, Carterton</t>
+  </si>
+  <si>
+    <t>1084703 - 00056419 - DG Label</t>
+  </si>
+  <si>
+    <t>37 Pukenaua Road, Taihape</t>
+  </si>
+  <si>
+    <t>1084705 - 00045442 - DG Label</t>
+  </si>
+  <si>
+    <t>513 Raetihi Ohakune Road, Raetihi</t>
+  </si>
+  <si>
+    <t>1084707 - 00046224 - DG Label</t>
+  </si>
+  <si>
+    <t>1084709 - 00022620 - DG Label</t>
+  </si>
+  <si>
+    <t>37 Fry Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1084770 - 00055238 - DG Label</t>
+  </si>
+  <si>
+    <t>338E Leedstown Road, Hunterville</t>
+  </si>
+  <si>
+    <t>1084772 - 00060405 - DG Label</t>
+  </si>
+  <si>
+    <t>74 Cambridge Avenue, Ashhurst</t>
+  </si>
+  <si>
+    <t>1084779 - 00048369 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Pukeko Place, Riversdale Beach</t>
+  </si>
+  <si>
+    <t>1084781 - 00059954 - DG Label</t>
+  </si>
+  <si>
+    <t>1244A Rangitikei Line, Kauwhata</t>
+  </si>
+  <si>
+    <t>1085276 - 00054364 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Millennium Way, Feilding</t>
+  </si>
+  <si>
+    <t>1085277 - 00061586 - DG Label</t>
+  </si>
+  <si>
+    <t>64A Thomas Road, Carrington</t>
+  </si>
+  <si>
+    <t>1085279 - 00063713 - DG Label</t>
+  </si>
+  <si>
+    <t>220 Somerset Road, Carterton</t>
+  </si>
+  <si>
+    <t>1085281 - 00063711 - DG Label</t>
+  </si>
+  <si>
+    <t>788 Tangimoana Road, Ōhakea</t>
+  </si>
+  <si>
+    <t>1085282 - 00063388 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Tangaroa View, Otamatea</t>
+  </si>
+  <si>
+    <t>1085283 - 00062392 - DG Label</t>
+  </si>
+  <si>
+    <t>142 West Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085285 - 00054784 - DG Label</t>
+  </si>
+  <si>
+    <t>5B Blennerville Close, Marton</t>
+  </si>
+  <si>
+    <t>1085287 - 00056035 - DG Label</t>
+  </si>
+  <si>
+    <t>40 Campbell Place, Marton</t>
+  </si>
+  <si>
+    <t>1085288 - 00052613 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Barracks Avenue, Solway</t>
+  </si>
+  <si>
+    <t>1085290 - 00059953 - DG Label</t>
+  </si>
+  <si>
+    <t>1965B State Highway 2, Greytown</t>
+  </si>
+  <si>
+    <t>1085291 - 00059958 - DG Label</t>
+  </si>
+  <si>
+    <t>1085378 - 00050724 - DG Label</t>
+  </si>
+  <si>
+    <t>51A Southdown Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>1085377 - 00052076 - DG Label</t>
+  </si>
+  <si>
+    <t>8C Michael Street, Masterton</t>
+  </si>
+  <si>
+    <t>1085376 - 00064756 - DG Label</t>
+  </si>
+  <si>
+    <t>6A Garrity Lane, Greytown</t>
+  </si>
+  <si>
+    <t>1085373 - 00037564 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Kowhai Street, Castelcliff</t>
+  </si>
+  <si>
+    <t>1085371 - 00053149 - DG Label</t>
+  </si>
+  <si>
+    <t>56 Willoughby Street, Halcombe</t>
+  </si>
+  <si>
+    <t>1085370 - 00061230 - DG Label</t>
+  </si>
+  <si>
+    <t>130 Mount Biggs Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1085369 - 00053697 - DG Label</t>
+  </si>
+  <si>
+    <t>121 Taikorea Road, Glen Oroua</t>
+  </si>
+  <si>
+    <t>1085457 - 00055046 - DG Label</t>
+  </si>
+  <si>
+    <t>63 Otawa Drive, Carterton</t>
+  </si>
+  <si>
+    <t>1085460 - 00026995 - DG Label</t>
+  </si>
+  <si>
+    <t>73 Young Street, Whanganui East</t>
+  </si>
+  <si>
+    <t>1085458 - 00044870 - DG Label</t>
+  </si>
+  <si>
+    <t>70B Duddings Lane, Featherson</t>
+  </si>
+  <si>
+    <t>1085533 - 00050342 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Whisky Way, Aokautere</t>
+  </si>
+  <si>
+    <t>1085531 - 00056810 - DG Label</t>
+  </si>
+  <si>
+    <t>289A Fabians Road, Greytown</t>
+  </si>
+  <si>
+    <t>1085529 - 00052073 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Valkyrie Close, Carterton</t>
+  </si>
+  <si>
+    <t>1085528 - 00052070 - DG Label</t>
+  </si>
+  <si>
+    <t>72 Jellicoe Street, Greytown</t>
+  </si>
+  <si>
+    <t>1085526 - 00052065 - DG Label</t>
+  </si>
+  <si>
+    <t>966 Kahutara Road, Kahutara</t>
+  </si>
+  <si>
+    <t>1085525 - 00050727 - DG Label</t>
+  </si>
+  <si>
+    <t>138 Loop Line, Opaki</t>
+  </si>
+  <si>
+    <t>1085524 - 00050503 - DG Label</t>
+  </si>
+  <si>
+    <t>29 Harrison Street West, Featherston</t>
+  </si>
+  <si>
+    <t>1085522 - 00050476 - DG Label</t>
+  </si>
+  <si>
+    <t>194 Kiriwhakapapa Road, Masterton</t>
+  </si>
+  <si>
+    <t>1085521 - 00048180 - DG Label</t>
+  </si>
+  <si>
+    <t>49 Wards Line, Greytown</t>
+  </si>
+  <si>
+    <t>1085554 - 00062941 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Boydfield Street, Whanganui East</t>
+  </si>
+  <si>
+    <t>1085553 - 00057633 - DG Label</t>
+  </si>
+  <si>
+    <t>2a Buxton Road, Westmere</t>
+  </si>
+  <si>
+    <t>1085551 - 00062161 - DG Label</t>
+  </si>
+  <si>
+    <t>72 Watt Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085550 - 00061611 - DG Label</t>
+  </si>
+  <si>
+    <t>180A Manchester Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085549 - 00061578 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Rothesay Place, Highbury</t>
+  </si>
+  <si>
+    <t>1085548 - 00061326 - DG Label</t>
+  </si>
+  <si>
+    <t>19 Mill Grove, Clareville</t>
+  </si>
+  <si>
+    <t>1085628 - 00042760 - DG Label</t>
+  </si>
+  <si>
+    <t>286 Central Mangaone Road, Eketahuna</t>
+  </si>
+  <si>
+    <t>1085627 - 00060729 - DG Label</t>
+  </si>
+  <si>
+    <t>1294 Turakina Valley Road, Turakina</t>
+  </si>
+  <si>
+    <t>1085626 - 00058779 - DG Label</t>
+  </si>
+  <si>
+    <t>154 Watershed Road, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085625 - 00059698 - DG Label</t>
+  </si>
+  <si>
+    <t>19 Bengston Street, Eketahuna</t>
+  </si>
+  <si>
+    <t>1085624 - 00045886 - DG Label</t>
+  </si>
+  <si>
+    <t>17 Pickwick Road, Otamatea</t>
+  </si>
+  <si>
+    <t>1085623 - 00035552 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Tangimoana Road, Ohakea</t>
+  </si>
+  <si>
+    <t>1085622 - 00055340 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Tayforth Road, Whanganui</t>
+  </si>
+  <si>
+    <t>1085621 - 00052867 - DG Label</t>
+  </si>
+  <si>
+    <t>8 Aotea Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085620 - 00053518 - DG Label</t>
+  </si>
+  <si>
+    <t>295 Dalefield Road, Dalefield</t>
+  </si>
+  <si>
+    <t>1085619 - 00054760 - DG Label</t>
+  </si>
+  <si>
+    <t>42 Johnstone Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085737 - 00064071 - DG Label</t>
+  </si>
+  <si>
+    <t>471 Lees Road, Feilding</t>
+  </si>
+  <si>
+    <t>1085735 - 00061413 - DG Label</t>
+  </si>
+  <si>
+    <t>85 Watt Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085734 - 00025403 - DG Label</t>
+  </si>
+  <si>
+    <t>7B Brassey Road, Saint Johns Hill</t>
+  </si>
+  <si>
+    <t>1085733 - 00031648 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Fox Road, Springvale</t>
+  </si>
+  <si>
+    <t>1085732 - 00030245 - DG Label</t>
+  </si>
+  <si>
+    <t>47 Kowhai Street, Castlecliff</t>
+  </si>
+  <si>
+    <t>1085731 - 00029753 - DG Label</t>
+  </si>
+  <si>
+    <t>119 Pharazyn Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085730 - 00038535 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Waicola Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085727 - 00046515 - DG Label</t>
+  </si>
+  <si>
+    <t>6 Hayward Street, Featherston</t>
+  </si>
+  <si>
+    <t>1085726 - 00038396 - DG Label</t>
+  </si>
+  <si>
+    <t>182 Kimbolton Road, Feilding</t>
+  </si>
+  <si>
+    <t>1085725 - 00025168 - DG Label</t>
+  </si>
+  <si>
+    <t>388 Ruakokoputuna Road, Martinborough</t>
+  </si>
+  <si>
+    <t>1085724 - 00032739 - DG Label</t>
+  </si>
+  <si>
+    <t>2187 State Highway 3, Sanson</t>
+  </si>
+  <si>
+    <t>1085722 - 00047186 - DG Label</t>
+  </si>
+  <si>
+    <t>36 Cloverlea Road, Westbrook</t>
+  </si>
+  <si>
+    <t>1085721 - 00054363 - DG Label</t>
+  </si>
+  <si>
+    <t>71 Wightman Road, Sanson</t>
+  </si>
+  <si>
+    <t>1085720 - 00051231 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Spelman Court, Ashhurst</t>
+  </si>
+  <si>
+    <t>1085718 - 00025360 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Hartwell Drive, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085717 - 00057960 - DG Label</t>
+  </si>
+  <si>
+    <t>32 Harrison Street West, Featherston</t>
+  </si>
+  <si>
+    <t>1085716 - 00055342 - DG Label</t>
+  </si>
+  <si>
+    <t>52 Surrey Road, Springvale</t>
+  </si>
+  <si>
+    <t>1085715 - 00030535 - DG Label</t>
+  </si>
+  <si>
+    <t>2/31 Moore Street, Tawhero</t>
+  </si>
+  <si>
+    <t>1085714 - 00048298 - DG Label</t>
+  </si>
+  <si>
+    <t>6 Monmouth Street, Feilding</t>
+  </si>
+  <si>
+    <t>1085712 - 00055446 - DG Label</t>
+  </si>
+  <si>
+    <t>262 Campbell Road, Brunswick</t>
+  </si>
+  <si>
+    <t>1085711 - 00060489 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Te Arakura Road, Newbury</t>
+  </si>
+  <si>
+    <t>1085844 - 00035552 - DG Label</t>
+  </si>
+  <si>
+    <t>1085843 - 00063446 - DG Label</t>
+  </si>
+  <si>
+    <t>13 Fantail Avenue, Carterton</t>
+  </si>
+  <si>
+    <t>1085842 - 00059955 - DG Label</t>
+  </si>
+  <si>
+    <t>572 Kelvin Grove Road, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1085841 - 00060910 - DG Label</t>
+  </si>
+  <si>
+    <t>20B Donovans Road, Masterton</t>
+  </si>
+  <si>
+    <t>1085840 - 00062204 - DG Label</t>
+  </si>
+  <si>
+    <t>24 Pokerekere Crescent, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1085839 - 00061211 - DG Label</t>
+  </si>
+  <si>
+    <t>100C Linton Street, West End</t>
+  </si>
+  <si>
+    <t>1085838 - 00058379 - DG Label</t>
+  </si>
+  <si>
+    <t>2E Hogg Crescent, Masterton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -131,8 +1467,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -483,84 +1821,2537 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>211</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>219</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" t="s">
+        <v>248</v>
+      </c>
+      <c r="C20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>249</v>
+      </c>
+      <c r="B21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>253</v>
+      </c>
+      <c r="B23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>257</v>
+      </c>
+      <c r="B25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>259</v>
+      </c>
+      <c r="B26" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>265</v>
+      </c>
+      <c r="C29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" t="s">
+        <v>267</v>
+      </c>
+      <c r="C30" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" t="s">
+        <v>290</v>
+      </c>
+      <c r="C31" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C32" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C34" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C36" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" t="s">
+        <v>160</v>
+      </c>
+      <c r="C39" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B40" t="s">
+        <v>162</v>
+      </c>
+      <c r="C40" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>171</v>
+      </c>
+      <c r="B45" t="s">
+        <v>172</v>
+      </c>
+      <c r="C45" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" t="s">
+        <v>288</v>
+      </c>
+      <c r="C46" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>176</v>
+      </c>
+      <c r="B48" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>178</v>
+      </c>
+      <c r="B49" t="s">
+        <v>179</v>
+      </c>
+      <c r="C49" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" t="s">
+        <v>179</v>
+      </c>
+      <c r="C50" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" t="s">
+        <v>182</v>
+      </c>
+      <c r="C51" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>183</v>
+      </c>
+      <c r="B52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>187</v>
+      </c>
+      <c r="B54" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>193</v>
+      </c>
+      <c r="B57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C57" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>195</v>
+      </c>
+      <c r="B58" t="s">
+        <v>196</v>
+      </c>
+      <c r="C58" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>197</v>
+      </c>
+      <c r="B59" t="s">
+        <v>198</v>
+      </c>
+      <c r="C59" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>203</v>
+      </c>
+      <c r="B62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>205</v>
+      </c>
+      <c r="B63" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>207</v>
+      </c>
+      <c r="B64" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>209</v>
+      </c>
+      <c r="B65" t="s">
+        <v>210</v>
+      </c>
+      <c r="C65" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>273</v>
+      </c>
+      <c r="C68" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>274</v>
+      </c>
+      <c r="C69" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>275</v>
+      </c>
+      <c r="C70" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71" t="s">
+        <v>276</v>
+      </c>
+      <c r="C71" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" t="s">
+        <v>277</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B75" t="s">
         <v>15</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C75" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" t="s">
+        <v>287</v>
+      </c>
+      <c r="C76" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>17</v>
+      </c>
+      <c r="B77" t="s">
+        <v>278</v>
+      </c>
+      <c r="C77" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s">
+        <v>280</v>
+      </c>
+      <c r="C79" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" t="s">
+        <v>23</v>
+      </c>
+      <c r="C81" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B82" t="s">
+        <v>285</v>
+      </c>
+      <c r="C82" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>286</v>
+      </c>
+      <c r="C83" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>65</v>
+      </c>
+      <c r="B84" t="s">
+        <v>66</v>
+      </c>
+      <c r="C84" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" t="s">
+        <v>32</v>
+      </c>
+      <c r="C87" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B88" t="s">
+        <v>34</v>
+      </c>
+      <c r="C88" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>35</v>
+      </c>
+      <c r="B89" t="s">
+        <v>36</v>
+      </c>
+      <c r="C89" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" t="s">
+        <v>38</v>
+      </c>
+      <c r="C90" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C91" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" t="s">
+        <v>44</v>
+      </c>
+      <c r="C93" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C94" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>47</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" t="s">
+        <v>50</v>
+      </c>
+      <c r="C96" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>51</v>
+      </c>
+      <c r="B97" t="s">
+        <v>52</v>
+      </c>
+      <c r="C97" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>53</v>
+      </c>
+      <c r="B98" t="s">
+        <v>54</v>
+      </c>
+      <c r="C98" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>56</v>
+      </c>
+      <c r="C99" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" t="s">
+        <v>58</v>
+      </c>
+      <c r="C100" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>59</v>
+      </c>
+      <c r="B101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>61</v>
+      </c>
+      <c r="B102" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>63</v>
+      </c>
+      <c r="B103" t="s">
+        <v>64</v>
+      </c>
+      <c r="C103" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>67</v>
+      </c>
+      <c r="B105" t="s">
+        <v>68</v>
+      </c>
+      <c r="C105" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>71</v>
+      </c>
+      <c r="B107" t="s">
+        <v>72</v>
+      </c>
+      <c r="C107" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>73</v>
+      </c>
+      <c r="B108" t="s">
+        <v>74</v>
+      </c>
+      <c r="C108" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>75</v>
+      </c>
+      <c r="B109" t="s">
+        <v>76</v>
+      </c>
+      <c r="C109" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>77</v>
+      </c>
+      <c r="B110" t="s">
+        <v>78</v>
+      </c>
+      <c r="C110" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>79</v>
+      </c>
+      <c r="B111" t="s">
+        <v>80</v>
+      </c>
+      <c r="C111" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>81</v>
+      </c>
+      <c r="B112" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>83</v>
+      </c>
+      <c r="B113" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>84</v>
+      </c>
+      <c r="B114" t="s">
+        <v>284</v>
+      </c>
+      <c r="C114" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>85</v>
+      </c>
+      <c r="B115" t="s">
+        <v>86</v>
+      </c>
+      <c r="C115" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>87</v>
+      </c>
+      <c r="B116" t="s">
+        <v>88</v>
+      </c>
+      <c r="C116" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>89</v>
+      </c>
+      <c r="B117" t="s">
+        <v>90</v>
+      </c>
+      <c r="C117" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>91</v>
+      </c>
+      <c r="B118" t="s">
+        <v>92</v>
+      </c>
+      <c r="C118" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>93</v>
+      </c>
+      <c r="B119" t="s">
+        <v>94</v>
+      </c>
+      <c r="C119" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>95</v>
+      </c>
+      <c r="B120" t="s">
+        <v>96</v>
+      </c>
+      <c r="C120" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>97</v>
+      </c>
+      <c r="B121" t="s">
+        <v>98</v>
+      </c>
+      <c r="C121" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>99</v>
+      </c>
+      <c r="B122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C122" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>101</v>
+      </c>
+      <c r="B123" t="s">
+        <v>102</v>
+      </c>
+      <c r="C123" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>103</v>
+      </c>
+      <c r="B124" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>105</v>
+      </c>
+      <c r="B125" t="s">
+        <v>106</v>
+      </c>
+      <c r="C125" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" t="s">
+        <v>108</v>
+      </c>
+      <c r="C126" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>109</v>
+      </c>
+      <c r="B127" t="s">
+        <v>110</v>
+      </c>
+      <c r="C127" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>111</v>
+      </c>
+      <c r="B128" t="s">
+        <v>112</v>
+      </c>
+      <c r="C128" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>113</v>
+      </c>
+      <c r="B129" t="s">
+        <v>114</v>
+      </c>
+      <c r="C129" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>115</v>
+      </c>
+      <c r="B130" t="s">
+        <v>116</v>
+      </c>
+      <c r="C130" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>117</v>
+      </c>
+      <c r="B131" t="s">
+        <v>118</v>
+      </c>
+      <c r="C131" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>119</v>
+      </c>
+      <c r="B132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C132" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>121</v>
+      </c>
+      <c r="B133" t="s">
+        <v>122</v>
+      </c>
+      <c r="C133" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>123</v>
+      </c>
+      <c r="B134" t="s">
+        <v>124</v>
+      </c>
+      <c r="C134" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>125</v>
+      </c>
+      <c r="B135" t="s">
+        <v>126</v>
+      </c>
+      <c r="C135" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>127</v>
+      </c>
+      <c r="B136" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>128</v>
+      </c>
+      <c r="B137" t="s">
+        <v>129</v>
+      </c>
+      <c r="C137" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>130</v>
+      </c>
+      <c r="B138" t="s">
+        <v>131</v>
+      </c>
+      <c r="C138" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>132</v>
+      </c>
+      <c r="B139" t="s">
+        <v>133</v>
+      </c>
+      <c r="C139" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>134</v>
+      </c>
+      <c r="B140" t="s">
+        <v>135</v>
+      </c>
+      <c r="C140" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>136</v>
+      </c>
+      <c r="B141" t="s">
+        <v>137</v>
+      </c>
+      <c r="C141" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>138</v>
+      </c>
+      <c r="B142" t="s">
+        <v>139</v>
+      </c>
+      <c r="C142" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>140</v>
+      </c>
+      <c r="B143" t="s">
+        <v>141</v>
+      </c>
+      <c r="C143" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>142</v>
+      </c>
+      <c r="B144" t="s">
+        <v>143</v>
+      </c>
+      <c r="C144" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>306</v>
+      </c>
+      <c r="B146" t="s">
+        <v>135</v>
+      </c>
+      <c r="C146" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>305</v>
+      </c>
+      <c r="B147" t="s">
+        <v>304</v>
+      </c>
+      <c r="C147" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>303</v>
+      </c>
+      <c r="B148" t="s">
+        <v>302</v>
+      </c>
+      <c r="C148" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>301</v>
+      </c>
+      <c r="B149" t="s">
+        <v>300</v>
+      </c>
+      <c r="C149" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>299</v>
+      </c>
+      <c r="B150" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>297</v>
+      </c>
+      <c r="B151" t="s">
+        <v>296</v>
+      </c>
+      <c r="C151" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>295</v>
+      </c>
+      <c r="B152" t="s">
+        <v>294</v>
+      </c>
+      <c r="C152" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>293</v>
+      </c>
+      <c r="B153" t="s">
+        <v>292</v>
+      </c>
+      <c r="C153" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>314</v>
+      </c>
+      <c r="B154" t="s">
+        <v>313</v>
+      </c>
+      <c r="C154" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+      <c r="B155" t="s">
+        <v>311</v>
+      </c>
+      <c r="C155" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" t="s">
+        <v>309</v>
+      </c>
+      <c r="C156" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>308</v>
+      </c>
+      <c r="B157" t="s">
+        <v>307</v>
+      </c>
+      <c r="C157" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>336</v>
+      </c>
+      <c r="B158" t="s">
+        <v>335</v>
+      </c>
+      <c r="C158" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>334</v>
+      </c>
+      <c r="B159" t="s">
+        <v>333</v>
+      </c>
+      <c r="C159" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>332</v>
+      </c>
+      <c r="B160" t="s">
+        <v>331</v>
+      </c>
+      <c r="C160" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>330</v>
+      </c>
+      <c r="B161" t="s">
+        <v>329</v>
+      </c>
+      <c r="C161" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>328</v>
+      </c>
+      <c r="B162" t="s">
+        <v>327</v>
+      </c>
+      <c r="C162" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>326</v>
+      </c>
+      <c r="B163" t="s">
+        <v>325</v>
+      </c>
+      <c r="C163" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>324</v>
+      </c>
+      <c r="B164" t="s">
+        <v>323</v>
+      </c>
+      <c r="C164" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>322</v>
+      </c>
+      <c r="B165" t="s">
+        <v>321</v>
+      </c>
+      <c r="C165" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>320</v>
+      </c>
+      <c r="B166" t="s">
+        <v>319</v>
+      </c>
+      <c r="C166" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>318</v>
+      </c>
+      <c r="B167" t="s">
+        <v>317</v>
+      </c>
+      <c r="C167" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>316</v>
+      </c>
+      <c r="B168" t="s">
+        <v>315</v>
+      </c>
+      <c r="C168" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>337</v>
+      </c>
+      <c r="B169" t="s">
+        <v>338</v>
+      </c>
+      <c r="C169" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>339</v>
+      </c>
+      <c r="B170" t="s">
+        <v>340</v>
+      </c>
+      <c r="C170" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>341</v>
+      </c>
+      <c r="B171" t="s">
+        <v>342</v>
+      </c>
+      <c r="C171" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>343</v>
+      </c>
+      <c r="B172" t="s">
+        <v>344</v>
+      </c>
+      <c r="C172" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>345</v>
+      </c>
+      <c r="B173" t="s">
+        <v>346</v>
+      </c>
+      <c r="C173" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>347</v>
+      </c>
+      <c r="B174" t="s">
+        <v>348</v>
+      </c>
+      <c r="C174" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>349</v>
+      </c>
+      <c r="B175" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>351</v>
+      </c>
+      <c r="B176" t="s">
+        <v>352</v>
+      </c>
+      <c r="C176" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>353</v>
+      </c>
+      <c r="B177" t="s">
+        <v>354</v>
+      </c>
+      <c r="C177" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>355</v>
+      </c>
+      <c r="B178" t="s">
+        <v>356</v>
+      </c>
+      <c r="C178" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>357</v>
+      </c>
+      <c r="B179" t="s">
+        <v>358</v>
+      </c>
+      <c r="C179" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>359</v>
+      </c>
+      <c r="B180" t="s">
+        <v>360</v>
+      </c>
+      <c r="C180" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>361</v>
+      </c>
+      <c r="B181" t="s">
+        <v>362</v>
+      </c>
+      <c r="C181" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>363</v>
+      </c>
+      <c r="B182" t="s">
+        <v>364</v>
+      </c>
+      <c r="C182" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>365</v>
+      </c>
+      <c r="B183" t="s">
+        <v>366</v>
+      </c>
+      <c r="C183" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>367</v>
+      </c>
+      <c r="B184" t="s">
+        <v>368</v>
+      </c>
+      <c r="C184" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>369</v>
+      </c>
+      <c r="B185" t="s">
+        <v>370</v>
+      </c>
+      <c r="C185" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>371</v>
+      </c>
+      <c r="B186" t="s">
+        <v>372</v>
+      </c>
+      <c r="C186" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>373</v>
+      </c>
+      <c r="B187" t="s">
+        <v>374</v>
+      </c>
+      <c r="C187" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>375</v>
+      </c>
+      <c r="B188" t="s">
+        <v>376</v>
+      </c>
+      <c r="C188" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" t="s">
+        <v>378</v>
+      </c>
+      <c r="C189" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>379</v>
+      </c>
+      <c r="B190" t="s">
+        <v>380</v>
+      </c>
+      <c r="C190" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>381</v>
+      </c>
+      <c r="B191" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>383</v>
+      </c>
+      <c r="B192" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>385</v>
+      </c>
+      <c r="B193" t="s">
+        <v>386</v>
+      </c>
+      <c r="C193" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" t="s">
+        <v>388</v>
+      </c>
+      <c r="C194" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>389</v>
+      </c>
+      <c r="B195" t="s">
+        <v>390</v>
+      </c>
+      <c r="C195" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>391</v>
+      </c>
+      <c r="B196" t="s">
+        <v>392</v>
+      </c>
+      <c r="C196" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>393</v>
+      </c>
+      <c r="B197" t="s">
+        <v>394</v>
+      </c>
+      <c r="C197" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>395</v>
+      </c>
+      <c r="B198" t="s">
+        <v>396</v>
+      </c>
+      <c r="C198" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>397</v>
+      </c>
+      <c r="B199" t="s">
+        <v>398</v>
+      </c>
+      <c r="C199" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>399</v>
+      </c>
+      <c r="B200" t="s">
+        <v>400</v>
+      </c>
+      <c r="C200" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>401</v>
+      </c>
+      <c r="B201" t="s">
+        <v>402</v>
+      </c>
+      <c r="C201" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>403</v>
+      </c>
+      <c r="B202" t="s">
+        <v>404</v>
+      </c>
+      <c r="C202" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>405</v>
+      </c>
+      <c r="B203" t="s">
+        <v>406</v>
+      </c>
+      <c r="C203" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>407</v>
+      </c>
+      <c r="B204" t="s">
+        <v>408</v>
+      </c>
+      <c r="C204" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>409</v>
+      </c>
+      <c r="B205" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>411</v>
+      </c>
+      <c r="B206" t="s">
+        <v>412</v>
+      </c>
+      <c r="C206" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>413</v>
+      </c>
+      <c r="B207" t="s">
+        <v>414</v>
+      </c>
+      <c r="C207" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>415</v>
+      </c>
+      <c r="B208" t="s">
+        <v>416</v>
+      </c>
+      <c r="C208" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>417</v>
+      </c>
+      <c r="B209" t="s">
+        <v>418</v>
+      </c>
+      <c r="C209" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>419</v>
+      </c>
+      <c r="B210" t="s">
+        <v>420</v>
+      </c>
+      <c r="C210" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>421</v>
+      </c>
+      <c r="B211" t="s">
+        <v>422</v>
+      </c>
+      <c r="C211" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>423</v>
+      </c>
+      <c r="B212" t="s">
+        <v>424</v>
+      </c>
+      <c r="C212" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>425</v>
+      </c>
+      <c r="B213" t="s">
+        <v>426</v>
+      </c>
+      <c r="C213" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>427</v>
+      </c>
+      <c r="B214" t="s">
+        <v>428</v>
+      </c>
+      <c r="C214" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>429</v>
+      </c>
+      <c r="B215" t="s">
+        <v>430</v>
+      </c>
+      <c r="C215" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>431</v>
+      </c>
+      <c r="B216" t="s">
+        <v>432</v>
+      </c>
+      <c r="C216" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>433</v>
+      </c>
+      <c r="B217" t="s">
+        <v>434</v>
+      </c>
+      <c r="C217" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>435</v>
+      </c>
+      <c r="B218" t="s">
+        <v>436</v>
+      </c>
+      <c r="C218" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>437</v>
+      </c>
+      <c r="B219" t="s">
+        <v>438</v>
+      </c>
+      <c r="C219" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>439</v>
+      </c>
+      <c r="B220" t="s">
+        <v>440</v>
+      </c>
+      <c r="C220" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>441</v>
+      </c>
+      <c r="B221" t="s">
+        <v>442</v>
+      </c>
+      <c r="C221" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>443</v>
+      </c>
+      <c r="B222" t="s">
+        <v>444</v>
+      </c>
+      <c r="C222" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>445</v>
+      </c>
+      <c r="B223" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>447</v>
+      </c>
+      <c r="B224" t="s">
+        <v>448</v>
+      </c>
+      <c r="C224" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>449</v>
+      </c>
+      <c r="B225" t="s">
+        <v>398</v>
+      </c>
+      <c r="C225" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>450</v>
+      </c>
+      <c r="B226" t="s">
+        <v>451</v>
+      </c>
+      <c r="C226" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>452</v>
+      </c>
+      <c r="B227" t="s">
+        <v>453</v>
+      </c>
+      <c r="C227" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" t="s">
+        <v>455</v>
+      </c>
+      <c r="C228" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>456</v>
+      </c>
+      <c r="B229" t="s">
+        <v>457</v>
+      </c>
+      <c r="C229" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>458</v>
+      </c>
+      <c r="B230" t="s">
+        <v>459</v>
+      </c>
+      <c r="C230" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>460</v>
+      </c>
+      <c r="B231" t="s">
+        <v>461</v>
+      </c>
+      <c r="C231" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/GW-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF0C6ACD-FCC6-4AF5-8D2E-2B18ED29C396}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EF3A7E-19D3-4CFF-ADB9-0D5EDBD7EAE6}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Job</t>
   </si>
@@ -57,6 +57,78 @@
   </si>
   <si>
     <t>12 Winchester Street, Awapuni</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Any time</t>
+  </si>
+  <si>
+    <t>18 Dahlia Street, Palmy</t>
+  </si>
+  <si>
+    <t>8 Margaret Street, Solway</t>
+  </si>
+  <si>
+    <t>824 Waitawhiti Road, Tinui</t>
+  </si>
+  <si>
+    <t>217 Chester Road, Clareville</t>
+  </si>
+  <si>
+    <t>5 Balrickard Way, Milson</t>
+  </si>
+  <si>
+    <t>87 Old West Road, Linton</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>50566661 - 00056252</t>
+  </si>
+  <si>
+    <t>11 Betts Avenue, Solway</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>50578497 - 00062289</t>
+  </si>
+  <si>
+    <t>16 Russell Street, Palmerston North</t>
+  </si>
+  <si>
+    <t>58 James Line, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>50566945 - 00056455</t>
+  </si>
+  <si>
+    <t>318 Aorangi Road, Aorangi</t>
+  </si>
+  <si>
+    <t>50532186 - 00037647</t>
+  </si>
+  <si>
+    <t>6 South Street, Palmerston North</t>
+  </si>
+  <si>
+    <t>50565367 - 00055454 + 2x NR</t>
+  </si>
+  <si>
+    <t>14 Vaucluse Heights, Fitzherbert, Palmerston North 4410</t>
+  </si>
+  <si>
+    <t>Raetihi</t>
+  </si>
+  <si>
+    <t>50570658 - 00058451 - 16 Mt View Street</t>
   </si>
 </sst>
 </file>
@@ -99,10 +171,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,65 +510,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>50553745</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>50562878</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>50576619</v>
       </c>
       <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="1"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>50590478</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46245</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>50573924</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>50581840</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>50566584</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>50589941</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>50580303</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>50572435</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46246</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46247</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46248</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46251</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46251</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46252</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D74" s="1"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/GW-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EF3A7E-19D3-4CFF-ADB9-0D5EDBD7EAE6}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E517E4A-AE29-4E8A-8BA1-4DFC4C313E4D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
     <t>Job</t>
   </si>
@@ -80,12 +80,6 @@
     <t>5 Balrickard Way, Milson</t>
   </si>
   <si>
-    <t>87 Old West Road, Linton</t>
-  </si>
-  <si>
-    <t>both</t>
-  </si>
-  <si>
     <t>50566661 - 00056252</t>
   </si>
   <si>
@@ -102,9 +96,6 @@
   </si>
   <si>
     <t>58 James Line, Kelvin Grove</t>
-  </si>
-  <si>
-    <t>Both</t>
   </si>
   <si>
     <t>50566945 - 00056455</t>
@@ -510,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -625,7 +616,7 @@
         <v>46248</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -647,77 +638,77 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>50580303</v>
+        <v>50572435</v>
       </c>
       <c r="B10" s="3">
         <v>46248</v>
       </c>
       <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B11" s="3">
+        <v>46246</v>
+      </c>
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>50572435</v>
-      </c>
-      <c r="B11" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46247</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" s="3">
-        <v>46246</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46251</v>
+      </c>
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3">
-        <v>46248</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B15" s="3">
         <v>46251</v>
@@ -726,45 +717,31 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46252</v>
+      </c>
+      <c r="C16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="3">
-        <v>46251</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
       <c r="D16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="3">
-        <v>46252</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D74" s="1"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D73" s="1"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1B6B855-DCFF-4DFF-B582-FBDD989915CA}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B3A2DD-F93B-4876-94A5-C5DD075FDB14}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="474">
   <si>
     <t>Job</t>
   </si>
@@ -1425,6 +1425,42 @@
   </si>
   <si>
     <t>2E Hogg Crescent, Masterton</t>
+  </si>
+  <si>
+    <t>1085917 - 00056807 - DG Label</t>
+  </si>
+  <si>
+    <t>33 Hughes Line, Clareville</t>
+  </si>
+  <si>
+    <t>1085916 - 00050209 - DG Label</t>
+  </si>
+  <si>
+    <t>587 Rapanui Road, Kai Iwi</t>
+  </si>
+  <si>
+    <t>1085915 - 00061776 - DG Label</t>
+  </si>
+  <si>
+    <t>62 Hartwell Drive, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1085914 - 00062074 - DG Label</t>
+  </si>
+  <si>
+    <t>12 Edenmore Terrace, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1085912 - 00061647 - DG Label</t>
+  </si>
+  <si>
+    <t>427C Ruahine Street, Terrace End</t>
+  </si>
+  <si>
+    <t>1085910 - 00061603 - DG Label</t>
+  </si>
+  <si>
+    <t>43 Tirimoana Place, Otamatea</t>
   </si>
 </sst>
 </file>
@@ -1805,7 +1841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C237"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4354,6 +4390,72 @@
         <v>270</v>
       </c>
     </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>462</v>
+      </c>
+      <c r="B232" t="s">
+        <v>463</v>
+      </c>
+      <c r="C232" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>464</v>
+      </c>
+      <c r="B233" t="s">
+        <v>465</v>
+      </c>
+      <c r="C233" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>466</v>
+      </c>
+      <c r="B234" t="s">
+        <v>467</v>
+      </c>
+      <c r="C234" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>468</v>
+      </c>
+      <c r="B235" t="s">
+        <v>469</v>
+      </c>
+      <c r="C235" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>470</v>
+      </c>
+      <c r="B236" t="s">
+        <v>471</v>
+      </c>
+      <c r="C236" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>472</v>
+      </c>
+      <c r="B237" t="s">
+        <v>473</v>
+      </c>
+      <c r="C237" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B3A2DD-F93B-4876-94A5-C5DD075FDB14}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253ED763-9A09-4D28-9D57-A1A4F18FFAD5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-330" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="496">
   <si>
     <t>Job</t>
   </si>
@@ -1461,6 +1461,72 @@
   </si>
   <si>
     <t>43 Tirimoana Place, Otamatea</t>
+  </si>
+  <si>
+    <t>3 Riverstone Grove, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086010 - 00059961 - DG Label</t>
+  </si>
+  <si>
+    <t>1132 Pohangina Valley East Road, Pohangina</t>
+  </si>
+  <si>
+    <t>1086011 - 00060978 - DG Label</t>
+  </si>
+  <si>
+    <t>3 Lyttle Way, Featherston</t>
+  </si>
+  <si>
+    <t>1086012 - 00048206 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Jellicoe Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1086014 - 00062883 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Cracroft Drive, Putiki</t>
+  </si>
+  <si>
+    <t>1086015 - 00056955 - DG Label</t>
+  </si>
+  <si>
+    <t>2 Crawford Street, Featherston</t>
+  </si>
+  <si>
+    <t>1086016 - 00062446 - DG Label</t>
+  </si>
+  <si>
+    <t>41 Watt Street, Featherston</t>
+  </si>
+  <si>
+    <t>1086017 - 00064085 - DG Label</t>
+  </si>
+  <si>
+    <t>2623 Pohangina Road, Pohangina</t>
+  </si>
+  <si>
+    <t>1086018 - 00060571 - DG Label</t>
+  </si>
+  <si>
+    <t>33 Monty's Lane, Woodside</t>
+  </si>
+  <si>
+    <t>1086019 - 00051506 - DG Label</t>
+  </si>
+  <si>
+    <t>22 Tukere Crescent, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1086020 - 00052189 - DG Label</t>
+  </si>
+  <si>
+    <t>21 Sandown Avenue, Himatangi Beach</t>
+  </si>
+  <si>
+    <t>1086021 - 00056665 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4456,6 +4522,127 @@
         <v>270</v>
       </c>
     </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>495</v>
+      </c>
+      <c r="B238" t="s">
+        <v>494</v>
+      </c>
+      <c r="C238" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>493</v>
+      </c>
+      <c r="B239" t="s">
+        <v>492</v>
+      </c>
+      <c r="C239" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>491</v>
+      </c>
+      <c r="B240" t="s">
+        <v>490</v>
+      </c>
+      <c r="C240" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>489</v>
+      </c>
+      <c r="B241" t="s">
+        <v>488</v>
+      </c>
+      <c r="C241" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>487</v>
+      </c>
+      <c r="B242" t="s">
+        <v>486</v>
+      </c>
+      <c r="C242" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>485</v>
+      </c>
+      <c r="B243" t="s">
+        <v>484</v>
+      </c>
+      <c r="C243" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>483</v>
+      </c>
+      <c r="B244" t="s">
+        <v>482</v>
+      </c>
+      <c r="C244" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>481</v>
+      </c>
+      <c r="B245" t="s">
+        <v>480</v>
+      </c>
+      <c r="C245" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>479</v>
+      </c>
+      <c r="B246" t="s">
+        <v>478</v>
+      </c>
+      <c r="C246" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>477</v>
+      </c>
+      <c r="B247" t="s">
+        <v>476</v>
+      </c>
+      <c r="C247" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>475</v>
+      </c>
+      <c r="B248" t="s">
+        <v>474</v>
+      </c>
+      <c r="C248" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253ED763-9A09-4D28-9D57-A1A4F18FFAD5}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E2F1AA-07D2-4A5B-8D50-11E9F0151AD1}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="494">
   <si>
     <t>Job</t>
   </si>
@@ -746,12 +746,6 @@
     <t>64 CORNWALL STREET , MASTERTON, 5810</t>
   </si>
   <si>
-    <t>1082571 - 00039316 - DG Label - 0000068226CP3F0</t>
-  </si>
-  <si>
-    <t>2 VISCOUNT PLACE, WEST END, PALMERSTON NORTH, 4412</t>
-  </si>
-  <si>
     <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
   </si>
   <si>
@@ -794,12 +788,6 @@
     <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
   </si>
   <si>
-    <t>1082492 - 00055639 - DG Label - 0000037890CP0D3</t>
-  </si>
-  <si>
-    <t>41 ESCORT GROVE, AWAPUNI, PALMERSTON NORTH, 4412</t>
-  </si>
-  <si>
     <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
   </si>
   <si>
@@ -890,9 +878,6 @@
     <t>46A Main Street, Greytown</t>
   </si>
   <si>
-    <t>95 Pyke Road, Rangitou</t>
-  </si>
-  <si>
     <t>431C Te Kopi Road, Te Whiti</t>
   </si>
   <si>
@@ -1034,9 +1019,6 @@
     <t>1085287 - 00056035 - DG Label</t>
   </si>
   <si>
-    <t>40 Campbell Place, Marton</t>
-  </si>
-  <si>
     <t>1085288 - 00052613 - DG Label</t>
   </si>
   <si>
@@ -1055,9 +1037,6 @@
     <t>1085378 - 00050724 - DG Label</t>
   </si>
   <si>
-    <t>51A Southdown Drive, Martinborough</t>
-  </si>
-  <si>
     <t>1085377 - 00052076 - DG Label</t>
   </si>
   <si>
@@ -1073,9 +1052,6 @@
     <t>1085373 - 00037564 - DG Label</t>
   </si>
   <si>
-    <t>41 Kowhai Street, Castelcliff</t>
-  </si>
-  <si>
     <t>1085371 - 00053149 - DG Label</t>
   </si>
   <si>
@@ -1109,9 +1085,6 @@
     <t>1085458 - 00044870 - DG Label</t>
   </si>
   <si>
-    <t>70B Duddings Lane, Featherson</t>
-  </si>
-  <si>
     <t>1085533 - 00050342 - DG Label</t>
   </si>
   <si>
@@ -1190,12 +1163,6 @@
     <t>180A Manchester Street, Feilding</t>
   </si>
   <si>
-    <t>1085549 - 00061578 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Rothesay Place, Highbury</t>
-  </si>
-  <si>
     <t>1085548 - 00061326 - DG Label</t>
   </si>
   <si>
@@ -1415,12 +1382,6 @@
     <t>24 Pokerekere Crescent, Kelvin Grove</t>
   </si>
   <si>
-    <t>1085839 - 00061211 - DG Label</t>
-  </si>
-  <si>
-    <t>100C Linton Street, West End</t>
-  </si>
-  <si>
     <t>1085838 - 00058379 - DG Label</t>
   </si>
   <si>
@@ -1527,6 +1488,39 @@
   </si>
   <si>
     <t>1086021 - 00056665 - DG Label</t>
+  </si>
+  <si>
+    <t>1086114 - 00058005 - DG Label</t>
+  </si>
+  <si>
+    <t>329 Kahuterawa Road, Linton</t>
+  </si>
+  <si>
+    <t>1086113 - 00061650 - DG Label</t>
+  </si>
+  <si>
+    <t>1086116 - 00052128 - DG Label</t>
+  </si>
+  <si>
+    <t>93 Chester Road, Clareville</t>
+  </si>
+  <si>
+    <t>95 Pyke Road, Manawatu</t>
+  </si>
+  <si>
+    <t>40 Campbell Place, Marton, 4710</t>
+  </si>
+  <si>
+    <t>51 Southdown Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>41 Kowhai Street, Castelcliff, Whanganui, 4501</t>
+  </si>
+  <si>
+    <t>70 Duddings Lane, Featherson</t>
+  </si>
+  <si>
+    <t>178 Kilkern Road, Marton</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -1923,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1934,7 +1928,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1945,7 +1939,7 @@
         <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1956,7 +1950,7 @@
         <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1967,7 +1961,7 @@
         <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1978,7 +1972,7 @@
         <v>220</v>
       </c>
       <c r="C6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1989,7 +1983,7 @@
         <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2000,7 +1994,7 @@
         <v>224</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2011,7 +2005,7 @@
         <v>226</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2022,7 +2016,7 @@
         <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2033,7 +2027,7 @@
         <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2044,7 +2038,7 @@
         <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2055,7 +2049,7 @@
         <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2066,7 +2060,7 @@
         <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2077,7 +2071,7 @@
         <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2088,7 +2082,7 @@
         <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,7 +2093,7 @@
         <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2110,7 +2104,7 @@
         <v>244</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,7 +2115,7 @@
         <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2132,7 +2126,7 @@
         <v>248</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2143,7 +2137,7 @@
         <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2154,7 +2148,7 @@
         <v>252</v>
       </c>
       <c r="C22" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2165,7 +2159,7 @@
         <v>254</v>
       </c>
       <c r="C23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2173,32 +2167,32 @@
         <v>255</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C24" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" t="s">
         <v>257</v>
       </c>
-      <c r="B25" t="s">
-        <v>258</v>
-      </c>
       <c r="C25" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" t="s">
         <v>259</v>
       </c>
-      <c r="B26" t="s">
-        <v>291</v>
-      </c>
       <c r="C26" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2209,7 +2203,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2220,7 +2214,7 @@
         <v>263</v>
       </c>
       <c r="C28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2228,2419 +2222,2408 @@
         <v>264</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="B30" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C39" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B44" t="s">
-        <v>170</v>
+        <v>283</v>
       </c>
       <c r="C44" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>288</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C47" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C52" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B54" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C54" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C55" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B56" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C56" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B57" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B58" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C59" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C61" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B62" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="C64" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>209</v>
+        <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>270</v>
       </c>
       <c r="C67" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C68" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C69" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>275</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>276</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" t="s">
-        <v>270</v>
+        <v>273</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C73" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>270</v>
+        <v>282</v>
+      </c>
+      <c r="C74" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="C75" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C76" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C77" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>280</v>
+        <v>23</v>
       </c>
       <c r="C79" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="C80" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>281</v>
       </c>
       <c r="C81" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>285</v>
+        <v>66</v>
       </c>
       <c r="C82" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>286</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C84" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C85" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C87" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C88" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C89" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B91" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C91" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C92" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C93" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C95" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B96" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C96" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C97" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C99" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B100" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C100" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C101" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>61</v>
-      </c>
-      <c r="B102" t="s">
-        <v>62</v>
-      </c>
-      <c r="C102" t="s">
-        <v>270</v>
+      <c r="A102" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C103" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>269</v>
+      <c r="A104" t="s">
+        <v>69</v>
+      </c>
+      <c r="B104" t="s">
+        <v>70</v>
+      </c>
+      <c r="C104" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B105" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C105" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B106" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C106" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C107" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C108" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B109" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C109" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B110" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C110" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="C111" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B112" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="C112" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B113" t="s">
-        <v>282</v>
+        <v>86</v>
       </c>
       <c r="C113" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B114" t="s">
-        <v>284</v>
+        <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B115" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C115" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C116" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B117" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C117" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C118" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B119" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B120" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C120" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B121" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C121" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B122" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C122" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B123" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C123" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B124" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C124" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B125" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C125" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B126" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C126" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C127" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B128" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C128" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B129" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C129" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B130" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C130" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B131" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C131" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B132" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C132" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B133" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C133" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B134" t="s">
-        <v>124</v>
+        <v>488</v>
       </c>
       <c r="C134" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B135" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C135" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B136" t="s">
-        <v>283</v>
+        <v>131</v>
       </c>
       <c r="C136" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B137" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C137" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C138" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C140" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C142" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C143" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>301</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B146" t="s">
-        <v>135</v>
+        <v>297</v>
       </c>
       <c r="C146" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B147" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B149" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C150" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B153" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B154" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C154" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="B156" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B157" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="C157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B158" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="C158" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B159" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C159" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="C160" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B161" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C161" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B162" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C162" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B163" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C163" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B164" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B165" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B166" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C166" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B167" t="s">
-        <v>317</v>
+        <v>490</v>
       </c>
       <c r="C167" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="B168" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B169" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B170" t="s">
-        <v>340</v>
+        <v>491</v>
       </c>
       <c r="C170" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C172" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B173" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C173" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B174" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C174" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B175" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C175" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>492</v>
       </c>
       <c r="C176" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B177" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B178" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B179" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B180" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C180" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B181" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C181" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B182" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B183" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C183" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B184" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C184" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B185" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C185" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B186" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C186" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B187" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C187" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B188" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C188" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B189" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C189" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C190" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B191" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C191" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B192" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C192" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B193" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B194" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C194" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B195" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B196" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C196" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B197" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C197" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B198" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B199" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C199" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B200" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B201" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B202" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B203" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B204" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B205" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B208" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B210" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C210" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B211" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C212" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B213" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C213" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C214" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C215" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B216" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C216" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C217" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B218" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C218" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B219" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C219" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B220" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B221" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C221" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B222" t="s">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="C222" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C223" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C224" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B225" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="C225" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B226" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C226" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B227" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C227" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B228" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C228" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B229" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C229" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B230" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C230" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B231" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C231" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B232" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B233" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C233" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B234" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="C234" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B235" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="C235" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B236" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C236" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B237" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C237" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="B238" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="C238" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="B239" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="C239" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="B240" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="C240" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="B241" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
       <c r="C241" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="B242" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C242" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="B243" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="C243" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="B244" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="C244" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B245" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="C245" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B246" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C246" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B247" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C247" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>475</v>
-      </c>
-      <c r="B248" t="s">
-        <v>474</v>
-      </c>
-      <c r="C248" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94E2F1AA-07D2-4A5B-8D50-11E9F0151AD1}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D222AA-DCBB-4B2C-A489-9582ECB384A3}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="504">
   <si>
     <t>Job</t>
   </si>
@@ -1521,6 +1521,36 @@
   </si>
   <si>
     <t>178 Kilkern Road, Marton</t>
+  </si>
+  <si>
+    <t>1086148 - 00064275 - DG Label</t>
+  </si>
+  <si>
+    <t>15B Aitken Street, Bulls</t>
+  </si>
+  <si>
+    <t>1086155 - 00059130 - DG Label</t>
+  </si>
+  <si>
+    <t>284 Cambridge Avenue, Ashhurst</t>
+  </si>
+  <si>
+    <t>1086153 - 00059404 - DG Label</t>
+  </si>
+  <si>
+    <t>38C Grove Road, Ashhurst</t>
+  </si>
+  <si>
+    <t>1086152 - 00063160 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Twiss Road, Bulls</t>
+  </si>
+  <si>
+    <t>633 Turakina Valley Road, Turakina</t>
+  </si>
+  <si>
+    <t>1086149 - 00062569 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +1931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C252"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4626,6 +4656,61 @@
         <v>265</v>
       </c>
     </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>494</v>
+      </c>
+      <c r="B248" t="s">
+        <v>495</v>
+      </c>
+      <c r="C248" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>496</v>
+      </c>
+      <c r="B249" t="s">
+        <v>497</v>
+      </c>
+      <c r="C249" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>498</v>
+      </c>
+      <c r="B250" t="s">
+        <v>499</v>
+      </c>
+      <c r="C250" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>500</v>
+      </c>
+      <c r="B251" t="s">
+        <v>501</v>
+      </c>
+      <c r="C251" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>503</v>
+      </c>
+      <c r="B252" t="s">
+        <v>502</v>
+      </c>
+      <c r="C252" t="s">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4D222AA-DCBB-4B2C-A489-9582ECB384A3}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{261EA6E9-5989-4189-A8C2-A9DA9022EF85}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="514">
   <si>
     <t>Job</t>
   </si>
@@ -1551,6 +1551,36 @@
   </si>
   <si>
     <t>1086149 - 00062569 - DG Label</t>
+  </si>
+  <si>
+    <t>1086200 - 00055582 - DG Label</t>
+  </si>
+  <si>
+    <t>281F Lees Pakaraka Road, Te Ore Ore</t>
+  </si>
+  <si>
+    <t>1086199 - 00024419 - DG Label</t>
+  </si>
+  <si>
+    <t>27 Jellicoe Street, Martinborough</t>
+  </si>
+  <si>
+    <t>1086197 - 00066902 - DG Label</t>
+  </si>
+  <si>
+    <t>69 Tararua Drive, Masterton</t>
+  </si>
+  <si>
+    <t>1086196 - 00061643 - DG Label</t>
+  </si>
+  <si>
+    <t>88 Oxford Street, Ashhurst</t>
+  </si>
+  <si>
+    <t>1086195 - 00062723 - DG Label</t>
+  </si>
+  <si>
+    <t>44b James Line, Kelvin Grove</t>
   </si>
 </sst>
 </file>
@@ -1931,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4711,6 +4741,61 @@
         <v>265</v>
       </c>
     </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>504</v>
+      </c>
+      <c r="B253" t="s">
+        <v>505</v>
+      </c>
+      <c r="C253" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>506</v>
+      </c>
+      <c r="B254" t="s">
+        <v>507</v>
+      </c>
+      <c r="C254" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>508</v>
+      </c>
+      <c r="B255" t="s">
+        <v>509</v>
+      </c>
+      <c r="C255" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>510</v>
+      </c>
+      <c r="B256" t="s">
+        <v>511</v>
+      </c>
+      <c r="C256" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>512</v>
+      </c>
+      <c r="B257" t="s">
+        <v>513</v>
+      </c>
+      <c r="C257" t="s">
+        <v>266</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{261EA6E9-5989-4189-A8C2-A9DA9022EF85}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046BC157-6172-441A-8BE6-E68C242D5651}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="512">
   <si>
     <t>Job</t>
   </si>
@@ -236,12 +236,6 @@
     <t>1 Nelsons Road, Martinborough</t>
   </si>
   <si>
-    <t>1083694 - 00052240 - DG Label</t>
-  </si>
-  <si>
-    <t>48 Raetihi Ohakune Road, Raetihi</t>
-  </si>
-  <si>
     <t>1083539 - 00047551 - DG Label</t>
   </si>
   <si>
@@ -746,18 +740,6 @@
     <t>64 CORNWALL STREET , MASTERTON, 5810</t>
   </si>
   <si>
-    <t>1082562 - 00052452 - DG Label - 0000080600CP356</t>
-  </si>
-  <si>
-    <t>69 KERERU DRIVE, TURITEA, PALMERSTON NORTH, 4472</t>
-  </si>
-  <si>
-    <t>1082560 - 00052590 - DG Label - 0000048858CP6F1</t>
-  </si>
-  <si>
-    <t>9 HEATHCOTE PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
-  </si>
-  <si>
     <t>1082527 - 00052277 - DG Label - 0000065056CP68A</t>
   </si>
   <si>
@@ -776,18 +758,6 @@
     <t>13 MERVYN BROWN PLACE, SOLWAY, MASTERTON, 5810</t>
   </si>
   <si>
-    <t>1082504 - 00050338 - DG Label - 1000579124PCE5E</t>
-  </si>
-  <si>
-    <t>4 HUFFINGTON PLACE, FEILDING, FEILDING, 4702</t>
-  </si>
-  <si>
-    <t>1082503 - 00050326 - DG Label - 0900086275PCEC2</t>
-  </si>
-  <si>
-    <t>15 RON PLACE, FITZHERBERT, PALMERSTON NORTH, 4410</t>
-  </si>
-  <si>
     <t>1082489 - 00042252 - DG Label - 0666001531PCF45</t>
   </si>
   <si>
@@ -809,18 +779,6 @@
     <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
   </si>
   <si>
-    <t>1082458 - 00054943 - DG Label - 1000624687PC063</t>
-  </si>
-  <si>
-    <t>8 Sardinia Grove, Fitzherbert, Palmerston North</t>
-  </si>
-  <si>
-    <t>1082455 - 00044025 - DG Label - 1000621883PC042</t>
-  </si>
-  <si>
-    <t>6 CASTLEBRIDGE LANE, AOKAUTERE, PALMERSTON NORTH, 4471</t>
-  </si>
-  <si>
     <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
   </si>
   <si>
@@ -833,9 +791,6 @@
     <t>39 Craigmillar Street, Solway, Masterton</t>
   </si>
   <si>
-    <t>1077614 - 00023887 - DG Label</t>
-  </si>
-  <si>
     <t>OH</t>
   </si>
   <si>
@@ -896,9 +851,6 @@
     <t>506 Longbush Road, Hinakura</t>
   </si>
   <si>
-    <t>688 Aranui Road, Kairanga</t>
-  </si>
-  <si>
     <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
   </si>
   <si>
@@ -1581,6 +1533,48 @@
   </si>
   <si>
     <t>44b James Line, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1086288 - 00059442 - DG Label</t>
+  </si>
+  <si>
+    <t>38 Marybank Road, Marybank</t>
+  </si>
+  <si>
+    <t>1086286 - 00054776 - DG Label</t>
+  </si>
+  <si>
+    <t>10 Browning Place, Roslyn</t>
+  </si>
+  <si>
+    <t>1086285 - 00067399 - DG Label</t>
+  </si>
+  <si>
+    <t>24 Feist Street, Carterton</t>
+  </si>
+  <si>
+    <t>1086240 - 00052127 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Oates Place, Greytown</t>
+  </si>
+  <si>
+    <t>1086239 - 00052061 - DG Label</t>
+  </si>
+  <si>
+    <t>26 Feist Street, Carterton</t>
+  </si>
+  <si>
+    <t>1086237 - 00052158 - DG Label</t>
+  </si>
+  <si>
+    <t>105 Ahiaruhe Road, Ahiaruhe</t>
+  </si>
+  <si>
+    <t>1086236 - 00063154 - DG Label</t>
+  </si>
+  <si>
+    <t>397D Pohangina Valley East Road, Pohangina</t>
   </si>
 </sst>
 </file>
@@ -1961,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C257"/>
+  <dimension ref="A1:C256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -1977,1932 +1971,1932 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C13" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C15" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C20" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C21" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>253</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>255</v>
+        <v>145</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="C25" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="C27" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>155</v>
       </c>
       <c r="B29" t="s">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>284</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C33" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>160</v>
+        <v>268</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B38" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C38" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C40" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C43" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="B44" t="s">
-        <v>283</v>
+        <v>184</v>
       </c>
       <c r="C44" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C46" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C47" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B49" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C51" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C52" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C53" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B54" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B55" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C55" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B56" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C56" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>197</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="C57" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>199</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>201</v>
+        <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="C59" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="C60" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>205</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="C62" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
-        <v>266</v>
+        <v>258</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>269</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C67" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C68" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C69" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B70" t="s">
-        <v>10</v>
+        <v>261</v>
       </c>
       <c r="C70" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>273</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>266</v>
+        <v>23</v>
+      </c>
+      <c r="C72" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
       <c r="C73" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C74" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>274</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>275</v>
+        <v>30</v>
       </c>
       <c r="C76" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B77" t="s">
-        <v>276</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B79" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>280</v>
+        <v>38</v>
       </c>
       <c r="C80" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>281</v>
+        <v>40</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C84" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C85" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C87" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C89" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C91" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="B92" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="C93" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>49</v>
-      </c>
-      <c r="B94" t="s">
-        <v>50</v>
-      </c>
-      <c r="C94" t="s">
-        <v>266</v>
+      <c r="A94" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B95" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C95" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="C96" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C97" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B98" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C98" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="C99" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B101" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C101" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>265</v>
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102" t="s">
+        <v>80</v>
+      </c>
+      <c r="C102" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>263</v>
       </c>
       <c r="C103" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B104" t="s">
-        <v>70</v>
+        <v>264</v>
       </c>
       <c r="C104" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B106" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B107" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C108" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B109" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C109" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B110" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C110" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B111" t="s">
-        <v>278</v>
+        <v>96</v>
       </c>
       <c r="C111" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B112" t="s">
-        <v>279</v>
+        <v>98</v>
       </c>
       <c r="C112" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="B113" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C113" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C114" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B117" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C117" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B118" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C118" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B119" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C119" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B120" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C120" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B121" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B122" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C123" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>472</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C127" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B128" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B129" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C129" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B130" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B131" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B133" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>488</v>
+        <v>141</v>
       </c>
       <c r="C134" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C135" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C136" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>132</v>
+        <v>284</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>283</v>
       </c>
       <c r="C137" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>281</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>136</v>
+        <v>280</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>278</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="C140" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>140</v>
+        <v>276</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>275</v>
       </c>
       <c r="C141" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="B142" t="s">
-        <v>143</v>
+        <v>273</v>
       </c>
       <c r="C142" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>272</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="C143" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B144" t="s">
-        <v>135</v>
+        <v>292</v>
       </c>
       <c r="C144" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="B145" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C145" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C146" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B147" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C147" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="B148" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="C148" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="B149" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="C149" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="B150" t="s">
-        <v>289</v>
+        <v>473</v>
       </c>
       <c r="C150" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="B151" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C151" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B152" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C152" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B153" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C153" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B154" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C154" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B155" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C155" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="B156" t="s">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="B157" t="s">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="C157" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="B158" t="s">
-        <v>489</v>
+        <v>294</v>
       </c>
       <c r="C158" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="B159" t="s">
-        <v>324</v>
+        <v>474</v>
       </c>
       <c r="C159" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B160" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C160" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C161" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>318</v>
+        <v>475</v>
       </c>
       <c r="C162" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B163" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>490</v>
+        <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>476</v>
       </c>
       <c r="C168" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B169" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C169" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B170" t="s">
-        <v>491</v>
+        <v>335</v>
       </c>
       <c r="C170" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>336</v>
+      </c>
+      <c r="B171" t="s">
         <v>337</v>
       </c>
-      <c r="B171" t="s">
-        <v>338</v>
-      </c>
       <c r="C171" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>338</v>
+      </c>
+      <c r="B172" t="s">
         <v>339</v>
       </c>
-      <c r="B172" t="s">
-        <v>340</v>
-      </c>
       <c r="C172" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
+        <v>340</v>
+      </c>
+      <c r="B173" t="s">
         <v>341</v>
       </c>
-      <c r="B173" t="s">
-        <v>342</v>
-      </c>
       <c r="C173" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>342</v>
+      </c>
+      <c r="B174" t="s">
         <v>343</v>
       </c>
-      <c r="B174" t="s">
-        <v>344</v>
-      </c>
       <c r="C174" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>344</v>
+      </c>
+      <c r="B175" t="s">
         <v>345</v>
       </c>
-      <c r="B175" t="s">
-        <v>346</v>
-      </c>
       <c r="C175" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>346</v>
+      </c>
+      <c r="B176" t="s">
         <v>347</v>
       </c>
-      <c r="B176" t="s">
-        <v>492</v>
-      </c>
       <c r="C176" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3913,7 +3907,7 @@
         <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3924,7 +3918,7 @@
         <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3935,7 +3929,7 @@
         <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3946,7 +3940,7 @@
         <v>355</v>
       </c>
       <c r="C180" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3957,7 +3951,7 @@
         <v>357</v>
       </c>
       <c r="C181" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3968,7 +3962,7 @@
         <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3979,7 +3973,7 @@
         <v>361</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -3990,7 +3984,7 @@
         <v>363</v>
       </c>
       <c r="C184" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4001,7 +3995,7 @@
         <v>365</v>
       </c>
       <c r="C185" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4012,7 +4006,7 @@
         <v>367</v>
       </c>
       <c r="C186" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4023,7 +4017,7 @@
         <v>369</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4034,7 +4028,7 @@
         <v>371</v>
       </c>
       <c r="C188" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4045,7 +4039,7 @@
         <v>373</v>
       </c>
       <c r="C189" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4056,7 +4050,7 @@
         <v>375</v>
       </c>
       <c r="C190" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4067,7 +4061,7 @@
         <v>377</v>
       </c>
       <c r="C191" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4078,7 +4072,7 @@
         <v>379</v>
       </c>
       <c r="C192" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4089,7 +4083,7 @@
         <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4100,7 +4094,7 @@
         <v>383</v>
       </c>
       <c r="C194" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4111,7 +4105,7 @@
         <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4122,7 +4116,7 @@
         <v>387</v>
       </c>
       <c r="C196" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4133,7 +4127,7 @@
         <v>389</v>
       </c>
       <c r="C197" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4144,7 +4138,7 @@
         <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4155,7 +4149,7 @@
         <v>393</v>
       </c>
       <c r="C199" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4166,7 +4160,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4177,7 +4171,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4188,7 +4182,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4199,7 +4193,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4210,7 +4204,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4221,7 +4215,7 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4232,7 +4226,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4243,7 +4237,7 @@
         <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4254,7 +4248,7 @@
         <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4265,7 +4259,7 @@
         <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4276,7 +4270,7 @@
         <v>415</v>
       </c>
       <c r="C210" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4287,7 +4281,7 @@
         <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4298,7 +4292,7 @@
         <v>419</v>
       </c>
       <c r="C212" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4309,7 +4303,7 @@
         <v>421</v>
       </c>
       <c r="C213" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4317,98 +4311,98 @@
         <v>422</v>
       </c>
       <c r="B214" t="s">
-        <v>423</v>
+        <v>371</v>
       </c>
       <c r="C214" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>423</v>
+      </c>
+      <c r="B215" t="s">
         <v>424</v>
       </c>
-      <c r="B215" t="s">
-        <v>425</v>
-      </c>
       <c r="C215" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>425</v>
+      </c>
+      <c r="B216" t="s">
         <v>426</v>
       </c>
-      <c r="B216" t="s">
-        <v>427</v>
-      </c>
       <c r="C216" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>427</v>
+      </c>
+      <c r="B217" t="s">
         <v>428</v>
       </c>
-      <c r="B217" t="s">
-        <v>429</v>
-      </c>
       <c r="C217" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>429</v>
+      </c>
+      <c r="B218" t="s">
         <v>430</v>
       </c>
-      <c r="B218" t="s">
-        <v>431</v>
-      </c>
       <c r="C218" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>431</v>
+      </c>
+      <c r="B219" t="s">
         <v>432</v>
       </c>
-      <c r="B219" t="s">
-        <v>433</v>
-      </c>
       <c r="C219" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>433</v>
+      </c>
+      <c r="B220" t="s">
         <v>434</v>
       </c>
-      <c r="B220" t="s">
-        <v>435</v>
-      </c>
       <c r="C220" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>435</v>
+      </c>
+      <c r="B221" t="s">
         <v>436</v>
       </c>
-      <c r="B221" t="s">
-        <v>437</v>
-      </c>
       <c r="C221" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>437</v>
+      </c>
+      <c r="B222" t="s">
         <v>438</v>
       </c>
-      <c r="B222" t="s">
-        <v>387</v>
-      </c>
       <c r="C222" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4419,7 +4413,7 @@
         <v>440</v>
       </c>
       <c r="C223" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4430,7 +4424,7 @@
         <v>442</v>
       </c>
       <c r="C224" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4441,249 +4435,249 @@
         <v>444</v>
       </c>
       <c r="C225" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="B226" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="C226" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="B227" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B228" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="C228" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="B229" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B230" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>456</v>
+      </c>
+      <c r="B231" t="s">
         <v>455</v>
       </c>
-      <c r="B231" t="s">
-        <v>456</v>
-      </c>
       <c r="C231" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B232" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C232" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="B233" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C233" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>482</v>
+        <v>450</v>
       </c>
       <c r="B234" t="s">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="C234" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="B235" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="C235" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>478</v>
+        <v>446</v>
       </c>
       <c r="B236" t="s">
-        <v>477</v>
+        <v>445</v>
       </c>
       <c r="C236" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B237" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C237" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B238" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C238" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B239" t="s">
         <v>471</v>
       </c>
       <c r="C239" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="B240" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="C240" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="B241" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="C241" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B242" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C242" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="B243" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="C243" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="B244" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B245" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B246" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C246" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="B247" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="C247" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4694,7 +4688,7 @@
         <v>495</v>
       </c>
       <c r="C248" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4705,7 +4699,7 @@
         <v>497</v>
       </c>
       <c r="C249" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4716,7 +4710,7 @@
         <v>499</v>
       </c>
       <c r="C250" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4727,18 +4721,18 @@
         <v>501</v>
       </c>
       <c r="C251" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>502</v>
+      </c>
+      <c r="B252" t="s">
         <v>503</v>
       </c>
-      <c r="B252" t="s">
-        <v>502</v>
-      </c>
       <c r="C252" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -4749,7 +4743,7 @@
         <v>505</v>
       </c>
       <c r="C253" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -4760,7 +4754,7 @@
         <v>507</v>
       </c>
       <c r="C254" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -4771,7 +4765,7 @@
         <v>509</v>
       </c>
       <c r="C255" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -4782,18 +4776,7 @@
         <v>511</v>
       </c>
       <c r="C256" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>512</v>
-      </c>
-      <c r="B257" t="s">
-        <v>513</v>
-      </c>
-      <c r="C257" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046BC157-6172-441A-8BE6-E68C242D5651}"/>
+  <xr:revisionPtr revIDLastSave="313" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D62A42C-5CAA-4D6C-8631-6D72057D6526}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="522">
   <si>
     <t>Job</t>
   </si>
@@ -74,12 +74,6 @@
     <t>985 Parewanui Road, Bulls</t>
   </si>
   <si>
-    <t>1084306 - 00052857 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Kaka Road, Taihape</t>
-  </si>
-  <si>
     <t>1084171 - 00014163 - DG Label</t>
   </si>
   <si>
@@ -1575,6 +1569,42 @@
   </si>
   <si>
     <t>397D Pohangina Valley East Road, Pohangina</t>
+  </si>
+  <si>
+    <t>1085966 - 00024933 - DG Label</t>
+  </si>
+  <si>
+    <t>1085965 - 00039615 - DG Label</t>
+  </si>
+  <si>
+    <t>1085964 - 00038228 - DG Label</t>
+  </si>
+  <si>
+    <t>1078484 - DG Labelling request - 00022542</t>
+  </si>
+  <si>
+    <t>1078481 - DG Labelling request - 00037578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1085967 - 00038230 - DG Label </t>
+  </si>
+  <si>
+    <t>258 High Street South, Carterton</t>
+  </si>
+  <si>
+    <t>58 Burgundy Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>58 Gimson Street, Solway</t>
+  </si>
+  <si>
+    <t>260 High Street South, Carterton</t>
+  </si>
+  <si>
+    <t>613 Lake Ferry Road</t>
+  </si>
+  <si>
+    <t>574 Masterton Castlepoint Road, Masterton</t>
   </si>
 </sst>
 </file>
@@ -1625,7 +1655,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1955,12 +1993,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1971,612 +2010,612 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C15" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B26" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C27" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B28" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C28" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C36" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C40" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C41" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C42" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C45" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C46" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B48" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C48" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C49" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C50" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C51" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C52" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B53" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B55" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C55" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C56" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2584,10 +2623,10 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C57" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,7 +2637,7 @@
         <v>4</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2606,10 +2645,10 @@
         <v>5</v>
       </c>
       <c r="B59" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2617,10 +2656,10 @@
         <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2628,10 +2667,10 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C61" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2639,10 +2678,10 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2661,21 +2700,21 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
-      </c>
-      <c r="C64" t="s">
-        <v>250</v>
+        <v>256</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
         <v>13</v>
       </c>
-      <c r="B65" t="s">
-        <v>258</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>251</v>
+      <c r="C65" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2683,54 +2722,54 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>265</v>
       </c>
       <c r="C66" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B67" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C68" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C69" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70" t="s">
         <v>19</v>
       </c>
-      <c r="B70" t="s">
-        <v>261</v>
-      </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,7 +2780,7 @@
         <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2749,21 +2788,21 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>263</v>
       </c>
       <c r="C72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +2810,10 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>266</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,7 +2824,7 @@
         <v>28</v>
       </c>
       <c r="C75" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,7 +2835,7 @@
         <v>30</v>
       </c>
       <c r="C76" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,7 +2846,7 @@
         <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2818,7 +2857,7 @@
         <v>34</v>
       </c>
       <c r="C78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2829,7 +2868,7 @@
         <v>36</v>
       </c>
       <c r="C79" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2840,7 +2879,7 @@
         <v>38</v>
       </c>
       <c r="C80" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2851,7 +2890,7 @@
         <v>40</v>
       </c>
       <c r="C81" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2862,7 +2901,7 @@
         <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2873,7 +2912,7 @@
         <v>44</v>
       </c>
       <c r="C83" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,7 +2923,7 @@
         <v>46</v>
       </c>
       <c r="C84" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2895,7 +2934,7 @@
         <v>48</v>
       </c>
       <c r="C85" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2906,7 +2945,7 @@
         <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2917,7 +2956,7 @@
         <v>52</v>
       </c>
       <c r="C87" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2928,7 +2967,7 @@
         <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2939,7 +2978,7 @@
         <v>56</v>
       </c>
       <c r="C89" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2950,7 +2989,7 @@
         <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2961,7 +3000,7 @@
         <v>60</v>
       </c>
       <c r="C91" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2972,29 +3011,29 @@
         <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>63</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>64</v>
       </c>
-      <c r="C93" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>250</v>
+      <c r="C94" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3005,7 +3044,7 @@
         <v>66</v>
       </c>
       <c r="C95" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3016,7 +3055,7 @@
         <v>68</v>
       </c>
       <c r="C96" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,7 +3066,7 @@
         <v>70</v>
       </c>
       <c r="C97" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3038,7 +3077,7 @@
         <v>72</v>
       </c>
       <c r="C98" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3049,7 +3088,7 @@
         <v>74</v>
       </c>
       <c r="C99" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3060,7 +3099,7 @@
         <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,7 +3110,7 @@
         <v>78</v>
       </c>
       <c r="C101" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3079,32 +3118,32 @@
         <v>79</v>
       </c>
       <c r="B102" t="s">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="C102" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B103" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C103" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104" t="s">
         <v>82</v>
       </c>
-      <c r="B104" t="s">
-        <v>264</v>
-      </c>
       <c r="C104" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,7 +3154,7 @@
         <v>84</v>
       </c>
       <c r="C105" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,7 +3165,7 @@
         <v>86</v>
       </c>
       <c r="C106" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3137,7 +3176,7 @@
         <v>88</v>
       </c>
       <c r="C107" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3148,7 +3187,7 @@
         <v>90</v>
       </c>
       <c r="C108" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,7 +3198,7 @@
         <v>92</v>
       </c>
       <c r="C109" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3170,7 +3209,7 @@
         <v>94</v>
       </c>
       <c r="C110" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3181,7 +3220,7 @@
         <v>96</v>
       </c>
       <c r="C111" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3192,7 +3231,7 @@
         <v>98</v>
       </c>
       <c r="C112" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3203,7 +3242,7 @@
         <v>100</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3214,7 +3253,7 @@
         <v>102</v>
       </c>
       <c r="C114" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,7 +3264,7 @@
         <v>104</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,7 +3275,7 @@
         <v>106</v>
       </c>
       <c r="C116" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3247,7 +3286,7 @@
         <v>108</v>
       </c>
       <c r="C117" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3258,7 +3297,7 @@
         <v>110</v>
       </c>
       <c r="C118" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3269,7 +3308,7 @@
         <v>112</v>
       </c>
       <c r="C119" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3280,7 +3319,7 @@
         <v>114</v>
       </c>
       <c r="C120" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3291,7 +3330,7 @@
         <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3302,7 +3341,7 @@
         <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,7 +3352,7 @@
         <v>120</v>
       </c>
       <c r="C123" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3324,7 +3363,7 @@
         <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,21 +3371,21 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>124</v>
+        <v>470</v>
       </c>
       <c r="C125" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
-        <v>472</v>
-      </c>
       <c r="C126" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3357,7 +3396,7 @@
         <v>127</v>
       </c>
       <c r="C127" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3368,7 +3407,7 @@
         <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3379,7 +3418,7 @@
         <v>131</v>
       </c>
       <c r="C129" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3390,7 +3429,7 @@
         <v>133</v>
       </c>
       <c r="C130" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3401,7 +3440,7 @@
         <v>135</v>
       </c>
       <c r="C131" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,7 +3451,7 @@
         <v>137</v>
       </c>
       <c r="C132" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,7 +3462,7 @@
         <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3434,282 +3473,282 @@
         <v>141</v>
       </c>
       <c r="C134" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>142</v>
+        <v>283</v>
       </c>
       <c r="B135" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C135" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="C136" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B137" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C137" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B138" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C138" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B139" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C139" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C140" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C141" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B142" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C142" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="B143" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C143" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B144" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C144" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B145" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C145" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C146" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="B147" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="C147" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B148" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C148" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B149" t="s">
-        <v>311</v>
+        <v>471</v>
       </c>
       <c r="C149" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B150" t="s">
-        <v>473</v>
+        <v>306</v>
       </c>
       <c r="C150" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B151" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C151" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B152" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C152" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B153" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C153" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B154" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C154" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B155" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C155" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B156" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C156" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B157" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C157" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B158" t="s">
-        <v>294</v>
+        <v>472</v>
       </c>
       <c r="C158" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>314</v>
+      </c>
+      <c r="B159" t="s">
         <v>315</v>
       </c>
-      <c r="B159" t="s">
-        <v>474</v>
-      </c>
       <c r="C159" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3720,7 +3759,7 @@
         <v>317</v>
       </c>
       <c r="C160" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3728,21 +3767,21 @@
         <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>319</v>
+        <v>473</v>
       </c>
       <c r="C161" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>319</v>
+      </c>
+      <c r="B162" t="s">
         <v>320</v>
       </c>
-      <c r="B162" t="s">
-        <v>475</v>
-      </c>
       <c r="C162" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3753,7 +3792,7 @@
         <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -3764,7 +3803,7 @@
         <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -3775,7 +3814,7 @@
         <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -3786,7 +3825,7 @@
         <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -3794,21 +3833,21 @@
         <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>330</v>
+        <v>474</v>
       </c>
       <c r="C167" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>330</v>
+      </c>
+      <c r="B168" t="s">
         <v>331</v>
       </c>
-      <c r="B168" t="s">
-        <v>476</v>
-      </c>
       <c r="C168" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -3819,7 +3858,7 @@
         <v>333</v>
       </c>
       <c r="C169" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -3830,7 +3869,7 @@
         <v>335</v>
       </c>
       <c r="C170" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -3841,7 +3880,7 @@
         <v>337</v>
       </c>
       <c r="C171" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3852,7 +3891,7 @@
         <v>339</v>
       </c>
       <c r="C172" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3863,7 +3902,7 @@
         <v>341</v>
       </c>
       <c r="C173" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3874,7 +3913,7 @@
         <v>343</v>
       </c>
       <c r="C174" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3885,7 +3924,7 @@
         <v>345</v>
       </c>
       <c r="C175" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3896,7 +3935,7 @@
         <v>347</v>
       </c>
       <c r="C176" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3907,7 +3946,7 @@
         <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3918,7 +3957,7 @@
         <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3929,7 +3968,7 @@
         <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3940,7 +3979,7 @@
         <v>355</v>
       </c>
       <c r="C180" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,7 +3990,7 @@
         <v>357</v>
       </c>
       <c r="C181" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,7 +4001,7 @@
         <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,7 +4012,7 @@
         <v>361</v>
       </c>
       <c r="C183" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,7 +4023,7 @@
         <v>363</v>
       </c>
       <c r="C184" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,7 +4034,7 @@
         <v>365</v>
       </c>
       <c r="C185" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,7 +4045,7 @@
         <v>367</v>
       </c>
       <c r="C186" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4017,7 +4056,7 @@
         <v>369</v>
       </c>
       <c r="C187" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4028,7 +4067,7 @@
         <v>371</v>
       </c>
       <c r="C188" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4039,7 +4078,7 @@
         <v>373</v>
       </c>
       <c r="C189" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,7 +4089,7 @@
         <v>375</v>
       </c>
       <c r="C190" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,7 +4100,7 @@
         <v>377</v>
       </c>
       <c r="C191" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,7 +4111,7 @@
         <v>379</v>
       </c>
       <c r="C192" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,7 +4122,7 @@
         <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,7 +4133,7 @@
         <v>383</v>
       </c>
       <c r="C194" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,7 +4144,7 @@
         <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,7 +4155,7 @@
         <v>387</v>
       </c>
       <c r="C196" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,7 +4166,7 @@
         <v>389</v>
       </c>
       <c r="C197" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,7 +4177,7 @@
         <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,7 +4188,7 @@
         <v>393</v>
       </c>
       <c r="C199" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,7 +4199,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,7 +4210,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,7 +4221,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,7 +4232,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,7 +4243,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,7 +4254,7 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,7 +4265,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,7 +4276,7 @@
         <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4248,7 +4287,7 @@
         <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,7 +4298,7 @@
         <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4270,7 +4309,7 @@
         <v>415</v>
       </c>
       <c r="C210" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4281,7 +4320,7 @@
         <v>417</v>
       </c>
       <c r="C211" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,7 +4331,7 @@
         <v>419</v>
       </c>
       <c r="C212" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4300,21 +4339,21 @@
         <v>420</v>
       </c>
       <c r="B213" t="s">
-        <v>421</v>
+        <v>369</v>
       </c>
       <c r="C213" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>421</v>
+      </c>
+      <c r="B214" t="s">
         <v>422</v>
       </c>
-      <c r="B214" t="s">
-        <v>371</v>
-      </c>
       <c r="C214" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4325,7 +4364,7 @@
         <v>424</v>
       </c>
       <c r="C215" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4336,7 +4375,7 @@
         <v>426</v>
       </c>
       <c r="C216" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4347,7 +4386,7 @@
         <v>428</v>
       </c>
       <c r="C217" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4358,7 +4397,7 @@
         <v>430</v>
       </c>
       <c r="C218" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4369,7 +4408,7 @@
         <v>432</v>
       </c>
       <c r="C219" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4380,7 +4419,7 @@
         <v>434</v>
       </c>
       <c r="C220" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4391,7 +4430,7 @@
         <v>436</v>
       </c>
       <c r="C221" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4402,7 +4441,7 @@
         <v>438</v>
       </c>
       <c r="C222" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4413,7 +4452,7 @@
         <v>440</v>
       </c>
       <c r="C223" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,172 +4463,172 @@
         <v>442</v>
       </c>
       <c r="C224" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="B225" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="C225" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B226" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C226" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B227" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C227" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B228" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C228" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B229" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C229" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B230" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C230" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B231" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C231" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B232" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C232" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B233" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C233" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B234" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C234" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B235" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C235" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B236" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="C236" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B237" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C237" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B238" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C238" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B239" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="C239" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,7 +4639,7 @@
         <v>479</v>
       </c>
       <c r="C240" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,7 +4650,7 @@
         <v>481</v>
       </c>
       <c r="C241" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,29 +4661,29 @@
         <v>483</v>
       </c>
       <c r="C242" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>485</v>
+      </c>
+      <c r="B243" t="s">
         <v>484</v>
       </c>
-      <c r="B243" t="s">
-        <v>485</v>
-      </c>
       <c r="C243" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>486</v>
+      </c>
+      <c r="B244" t="s">
         <v>487</v>
       </c>
-      <c r="B244" t="s">
-        <v>486</v>
-      </c>
       <c r="C244" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,7 +4694,7 @@
         <v>489</v>
       </c>
       <c r="C245" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,7 +4705,7 @@
         <v>491</v>
       </c>
       <c r="C246" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,7 +4716,7 @@
         <v>493</v>
       </c>
       <c r="C247" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,7 +4727,7 @@
         <v>495</v>
       </c>
       <c r="C248" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,7 +4738,7 @@
         <v>497</v>
       </c>
       <c r="C249" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4710,7 +4749,7 @@
         <v>499</v>
       </c>
       <c r="C250" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,7 +4760,7 @@
         <v>501</v>
       </c>
       <c r="C251" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4732,7 +4771,7 @@
         <v>503</v>
       </c>
       <c r="C252" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,7 +4782,7 @@
         <v>505</v>
       </c>
       <c r="C253" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,7 +4793,7 @@
         <v>507</v>
       </c>
       <c r="C254" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,21 +4804,81 @@
         <v>509</v>
       </c>
       <c r="C255" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
+        <v>515</v>
+      </c>
+      <c r="B256" t="s">
+        <v>516</v>
+      </c>
+      <c r="C256" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
         <v>510</v>
       </c>
-      <c r="B256" t="s">
+      <c r="B257" t="s">
+        <v>517</v>
+      </c>
+      <c r="C257" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
         <v>511</v>
       </c>
-      <c r="C256" t="s">
-        <v>251</v>
+      <c r="B258" t="s">
+        <v>518</v>
+      </c>
+      <c r="C258" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>512</v>
+      </c>
+      <c r="B259" t="s">
+        <v>519</v>
+      </c>
+      <c r="C259" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>513</v>
+      </c>
+      <c r="B260" t="s">
+        <v>520</v>
+      </c>
+      <c r="C260" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>514</v>
+      </c>
+      <c r="B261" t="s">
+        <v>521</v>
+      </c>
+      <c r="C261" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>COUNTIF($A:$A, E2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="313" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D62A42C-5CAA-4D6C-8631-6D72057D6526}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2BCD421-D7B3-4972-A2D8-9193264D1A08}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="518">
   <si>
     <t>Job</t>
   </si>
@@ -113,9 +113,6 @@
     <t>1084055 - 00021842 - DG Label</t>
   </si>
   <si>
-    <t>1084053 - 00050380 - DG Label</t>
-  </si>
-  <si>
     <t>1083913 - 00050014 - DG Label</t>
   </si>
   <si>
@@ -770,9 +767,6 @@
     <t>8 GRATITUDE WAY, KELVIN GROVE, PALMERSTON NORTH, 4470</t>
   </si>
   <si>
-    <t>1082477 - 00052899 - DG Label- 1000594314PC4FC</t>
-  </si>
-  <si>
     <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
   </si>
   <si>
@@ -821,9 +815,6 @@
     <t>5 Castlebridge Lane, Aokautere</t>
   </si>
   <si>
-    <t>208 Smiths Road, Ohakune</t>
-  </si>
-  <si>
     <t>46A Main Street, Greytown</t>
   </si>
   <si>
@@ -843,9 +834,6 @@
   </si>
   <si>
     <t>506 Longbush Road, Hinakura</t>
-  </si>
-  <si>
-    <t>26 MAKOPUA ROAD, TAOROA JUNCTION</t>
   </si>
   <si>
     <t>45D Brandon Street, Featherston</t>
@@ -1611,17 +1599,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1647,15 +1628,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1993,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:C259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2010,216 +2004,216 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" t="s">
         <v>207</v>
       </c>
-      <c r="B2" t="s">
-        <v>208</v>
-      </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" t="s">
         <v>209</v>
       </c>
-      <c r="B3" t="s">
-        <v>210</v>
-      </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" t="s">
         <v>211</v>
       </c>
-      <c r="B4" t="s">
-        <v>212</v>
-      </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" t="s">
         <v>213</v>
       </c>
-      <c r="B5" t="s">
-        <v>214</v>
-      </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" t="s">
         <v>215</v>
       </c>
-      <c r="B6" t="s">
-        <v>216</v>
-      </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" t="s">
         <v>217</v>
       </c>
-      <c r="B7" t="s">
-        <v>218</v>
-      </c>
       <c r="C7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" t="s">
         <v>219</v>
       </c>
-      <c r="B8" t="s">
-        <v>220</v>
-      </c>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" t="s">
         <v>221</v>
       </c>
-      <c r="B9" t="s">
-        <v>222</v>
-      </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" t="s">
         <v>223</v>
       </c>
-      <c r="B10" t="s">
-        <v>224</v>
-      </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B11" t="s">
         <v>225</v>
       </c>
-      <c r="B11" t="s">
-        <v>226</v>
-      </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="s">
         <v>227</v>
       </c>
-      <c r="B12" t="s">
-        <v>228</v>
-      </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" t="s">
         <v>229</v>
       </c>
-      <c r="B13" t="s">
-        <v>230</v>
-      </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" t="s">
         <v>231</v>
       </c>
-      <c r="B14" t="s">
-        <v>232</v>
-      </c>
       <c r="C14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B15" t="s">
         <v>233</v>
       </c>
-      <c r="B15" t="s">
-        <v>234</v>
-      </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" t="s">
         <v>235</v>
       </c>
-      <c r="B16" t="s">
-        <v>236</v>
-      </c>
       <c r="C16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
         <v>237</v>
       </c>
-      <c r="B17" t="s">
-        <v>238</v>
-      </c>
       <c r="C17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18" t="s">
         <v>239</v>
       </c>
-      <c r="B18" t="s">
-        <v>240</v>
-      </c>
       <c r="C18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="B19" t="s">
-        <v>242</v>
-      </c>
       <c r="C19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" t="s">
         <v>243</v>
       </c>
-      <c r="B20" t="s">
-        <v>268</v>
-      </c>
       <c r="C20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2230,18 +2224,18 @@
         <v>245</v>
       </c>
       <c r="C21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>246</v>
+        <v>141</v>
       </c>
       <c r="B22" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2249,153 +2243,153 @@
         <v>142</v>
       </c>
       <c r="B23" t="s">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C35" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="C36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2403,43 +2397,43 @@
         <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>266</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s">
         <v>174</v>
       </c>
-      <c r="B40" t="s">
-        <v>175</v>
-      </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2447,1297 +2441,1297 @@
         <v>176</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B45" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C47" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B48" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B49" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C49" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C54" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C55" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>250</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>250</v>
       </c>
       <c r="C58" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>255</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>249</v>
+        <v>254</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>256</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>249</v>
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>262</v>
       </c>
       <c r="C65" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C66" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C68" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B69" t="s">
-        <v>259</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C78" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C81" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B82" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C82" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C83" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C84" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C85" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C86" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B87" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C87" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C89" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B90" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B92" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>248</v>
+      <c r="A93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B93" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C94" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C95" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C96" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C97" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B98" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C98" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B99" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C99" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B100" t="s">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="C100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B102" t="s">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c r="C102" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B103" t="s">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="C103" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B104" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C104" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B106" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C106" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B107" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C107" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B108" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C108" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C109" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C110" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B111" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C111" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B113" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C113" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B114" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B115" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C115" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C116" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C117" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C118" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B119" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C120" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C122" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>466</v>
       </c>
       <c r="C123" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B125" t="s">
-        <v>470</v>
+        <v>126</v>
       </c>
       <c r="C125" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B126" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C126" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C127" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B128" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C128" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C129" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C131" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C132" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>138</v>
+        <v>279</v>
       </c>
       <c r="B133" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C133" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>140</v>
+        <v>278</v>
       </c>
       <c r="B134" t="s">
-        <v>141</v>
+        <v>277</v>
       </c>
       <c r="C134" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B135" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="C135" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B136" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C136" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B137" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C137" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="C138" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B139" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C139" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B140" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C140" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="B141" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="B142" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C142" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="B143" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C143" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B144" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C144" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B145" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="B146" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C146" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B147" t="s">
-        <v>311</v>
+        <v>467</v>
       </c>
       <c r="C147" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B148" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C148" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B149" t="s">
-        <v>471</v>
+        <v>300</v>
       </c>
       <c r="C149" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="B150" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C150" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B151" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C151" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="B152" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="C152" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B153" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B154" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C154" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B155" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="C155" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B156" t="s">
-        <v>294</v>
+        <v>468</v>
       </c>
       <c r="C156" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>312</v>
+      </c>
+      <c r="B158" t="s">
         <v>313</v>
       </c>
-      <c r="B158" t="s">
-        <v>472</v>
-      </c>
       <c r="C158" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3745,32 +3739,32 @@
         <v>314</v>
       </c>
       <c r="B159" t="s">
-        <v>315</v>
+        <v>469</v>
       </c>
       <c r="C159" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>315</v>
+      </c>
+      <c r="B160" t="s">
         <v>316</v>
       </c>
-      <c r="B160" t="s">
-        <v>317</v>
-      </c>
       <c r="C160" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>317</v>
+      </c>
+      <c r="B161" t="s">
         <v>318</v>
       </c>
-      <c r="B161" t="s">
-        <v>473</v>
-      </c>
       <c r="C161" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3781,7 +3775,7 @@
         <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3792,7 +3786,7 @@
         <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -3803,7 +3797,7 @@
         <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -3811,32 +3805,32 @@
         <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>326</v>
+        <v>470</v>
       </c>
       <c r="C165" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
+        <v>326</v>
+      </c>
+      <c r="B166" t="s">
         <v>327</v>
       </c>
-      <c r="B166" t="s">
-        <v>328</v>
-      </c>
       <c r="C166" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>328</v>
+      </c>
+      <c r="B167" t="s">
         <v>329</v>
       </c>
-      <c r="B167" t="s">
-        <v>474</v>
-      </c>
       <c r="C167" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -3847,7 +3841,7 @@
         <v>331</v>
       </c>
       <c r="C168" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -3858,7 +3852,7 @@
         <v>333</v>
       </c>
       <c r="C169" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -3869,7 +3863,7 @@
         <v>335</v>
       </c>
       <c r="C170" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -3880,7 +3874,7 @@
         <v>337</v>
       </c>
       <c r="C171" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3891,7 +3885,7 @@
         <v>339</v>
       </c>
       <c r="C172" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3902,7 +3896,7 @@
         <v>341</v>
       </c>
       <c r="C173" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3913,7 +3907,7 @@
         <v>343</v>
       </c>
       <c r="C174" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3924,7 +3918,7 @@
         <v>345</v>
       </c>
       <c r="C175" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3935,7 +3929,7 @@
         <v>347</v>
       </c>
       <c r="C176" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3946,7 +3940,7 @@
         <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3957,7 +3951,7 @@
         <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3968,7 +3962,7 @@
         <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3979,7 +3973,7 @@
         <v>355</v>
       </c>
       <c r="C180" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3990,7 +3984,7 @@
         <v>357</v>
       </c>
       <c r="C181" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4001,7 +3995,7 @@
         <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4012,7 +4006,7 @@
         <v>361</v>
       </c>
       <c r="C183" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4023,7 +4017,7 @@
         <v>363</v>
       </c>
       <c r="C184" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4034,7 +4028,7 @@
         <v>365</v>
       </c>
       <c r="C185" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4045,7 +4039,7 @@
         <v>367</v>
       </c>
       <c r="C186" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4056,7 +4050,7 @@
         <v>369</v>
       </c>
       <c r="C187" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4067,7 +4061,7 @@
         <v>371</v>
       </c>
       <c r="C188" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4078,7 +4072,7 @@
         <v>373</v>
       </c>
       <c r="C189" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4089,7 +4083,7 @@
         <v>375</v>
       </c>
       <c r="C190" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4100,7 +4094,7 @@
         <v>377</v>
       </c>
       <c r="C191" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4111,7 +4105,7 @@
         <v>379</v>
       </c>
       <c r="C192" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4122,7 +4116,7 @@
         <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4133,7 +4127,7 @@
         <v>383</v>
       </c>
       <c r="C194" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4144,7 +4138,7 @@
         <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4155,7 +4149,7 @@
         <v>387</v>
       </c>
       <c r="C196" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4166,7 +4160,7 @@
         <v>389</v>
       </c>
       <c r="C197" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4177,7 +4171,7 @@
         <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4188,7 +4182,7 @@
         <v>393</v>
       </c>
       <c r="C199" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4199,7 +4193,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4210,7 +4204,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4221,7 +4215,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4232,7 +4226,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4243,7 +4237,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4254,7 +4248,7 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4265,7 +4259,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4276,7 +4270,7 @@
         <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4287,7 +4281,7 @@
         <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4298,7 +4292,7 @@
         <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4309,7 +4303,7 @@
         <v>415</v>
       </c>
       <c r="C210" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4317,32 +4311,32 @@
         <v>416</v>
       </c>
       <c r="B211" t="s">
-        <v>417</v>
+        <v>365</v>
       </c>
       <c r="C211" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>417</v>
+      </c>
+      <c r="B212" t="s">
         <v>418</v>
       </c>
-      <c r="B212" t="s">
-        <v>419</v>
-      </c>
       <c r="C212" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>419</v>
+      </c>
+      <c r="B213" t="s">
         <v>420</v>
       </c>
-      <c r="B213" t="s">
-        <v>369</v>
-      </c>
       <c r="C213" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4353,7 +4347,7 @@
         <v>422</v>
       </c>
       <c r="C214" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4364,7 +4358,7 @@
         <v>424</v>
       </c>
       <c r="C215" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4375,7 +4369,7 @@
         <v>426</v>
       </c>
       <c r="C216" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4386,7 +4380,7 @@
         <v>428</v>
       </c>
       <c r="C217" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4397,7 +4391,7 @@
         <v>430</v>
       </c>
       <c r="C218" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4408,7 +4402,7 @@
         <v>432</v>
       </c>
       <c r="C219" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4419,7 +4413,7 @@
         <v>434</v>
       </c>
       <c r="C220" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4430,7 +4424,7 @@
         <v>436</v>
       </c>
       <c r="C221" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4441,183 +4435,183 @@
         <v>438</v>
       </c>
       <c r="C222" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="B223" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="C223" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="B224" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C224" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B225" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C225" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B226" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C226" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B227" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C227" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B228" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C228" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B229" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="C229" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B230" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="C230" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C231" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B232" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C232" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B233" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C233" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="B234" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="C234" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B235" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="C235" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B236" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C236" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="B237" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C237" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B238" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C238" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4628,7 +4622,7 @@
         <v>477</v>
       </c>
       <c r="C239" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -4639,18 +4633,18 @@
         <v>479</v>
       </c>
       <c r="C240" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>481</v>
+      </c>
+      <c r="B241" t="s">
         <v>480</v>
       </c>
-      <c r="B241" t="s">
-        <v>481</v>
-      </c>
       <c r="C241" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -4661,18 +4655,18 @@
         <v>483</v>
       </c>
       <c r="C242" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>484</v>
+      </c>
+      <c r="B243" t="s">
         <v>485</v>
       </c>
-      <c r="B243" t="s">
-        <v>484</v>
-      </c>
       <c r="C243" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -4683,7 +4677,7 @@
         <v>487</v>
       </c>
       <c r="C244" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -4694,7 +4688,7 @@
         <v>489</v>
       </c>
       <c r="C245" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -4705,7 +4699,7 @@
         <v>491</v>
       </c>
       <c r="C246" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -4716,7 +4710,7 @@
         <v>493</v>
       </c>
       <c r="C247" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -4727,7 +4721,7 @@
         <v>495</v>
       </c>
       <c r="C248" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -4738,7 +4732,7 @@
         <v>497</v>
       </c>
       <c r="C249" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -4749,7 +4743,7 @@
         <v>499</v>
       </c>
       <c r="C250" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -4760,7 +4754,7 @@
         <v>501</v>
       </c>
       <c r="C251" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -4771,7 +4765,7 @@
         <v>503</v>
       </c>
       <c r="C252" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -4782,101 +4776,89 @@
         <v>505</v>
       </c>
       <c r="C253" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B254" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="C254" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B255" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C255" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B256" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C256" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B257" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C257" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B258" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C258" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B259" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C259" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>513</v>
-      </c>
-      <c r="B260" t="s">
-        <v>520</v>
-      </c>
-      <c r="C260" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>514</v>
-      </c>
-      <c r="B261" t="s">
-        <v>521</v>
-      </c>
-      <c r="C261" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="E1:E18 E20:E90 E92:E1048573">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>COUNTIF($A:$A, E2)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1048574:E1048576">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>COUNTIF($A:$A, E1)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E91 E19">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>COUNTIF($A:$A, #REF!)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2BCD421-D7B3-4972-A2D8-9193264D1A08}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA1962D-C75F-4527-87C7-D5D6B09536EB}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="526">
   <si>
     <t>Job</t>
   </si>
@@ -1593,6 +1593,30 @@
   </si>
   <si>
     <t>574 Masterton Castlepoint Road, Masterton</t>
+  </si>
+  <si>
+    <t>1086425 - 00067416 - DG Label</t>
+  </si>
+  <si>
+    <t>49 Mt Biggs Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1086424 - 00065363 - DG Label</t>
+  </si>
+  <si>
+    <t>377 Gillespies Line, Kairanga</t>
+  </si>
+  <si>
+    <t>1086423 - 00065064 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Cleveland Heights, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1086422 - 00065066 - DG Label</t>
+  </si>
+  <si>
+    <t>49 Parnell Heights Drive, Kelvin Grove</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C259"/>
+  <dimension ref="A1:C263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4845,20 +4869,64 @@
         <v>247</v>
       </c>
     </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>518</v>
+      </c>
+      <c r="B260" t="s">
+        <v>519</v>
+      </c>
+      <c r="C260" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>520</v>
+      </c>
+      <c r="B261" t="s">
+        <v>521</v>
+      </c>
+      <c r="C261" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>522</v>
+      </c>
+      <c r="B262" t="s">
+        <v>523</v>
+      </c>
+      <c r="C262" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>524</v>
+      </c>
+      <c r="B263" t="s">
+        <v>525</v>
+      </c>
+      <c r="C263" t="s">
+        <v>247</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E18 E20:E90 E92:E1048573">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>COUNTIF($A:$A, E2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1048574:E1048576">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>COUNTIF($A:$A, E1)=0</formula>
+  <conditionalFormatting sqref="E19 E91">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>COUNTIF($A:$A, #REF!)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E91 E19">
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>COUNTIF($A:$A, #REF!)=0</formula>
+  <conditionalFormatting sqref="E1048574:E1048576">
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>COUNTIF($A:$A, E1)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA1962D-C75F-4527-87C7-D5D6B09536EB}"/>
+  <xr:revisionPtr revIDLastSave="329" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B142447-0F80-4476-9A99-7CE97CC9EC5A}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="542">
   <si>
     <t>Job</t>
   </si>
@@ -1617,6 +1617,54 @@
   </si>
   <si>
     <t>49 Parnell Heights Drive, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>33 Harvest Lane, Newbury</t>
+  </si>
+  <si>
+    <t>1086475 - 00064074 - DG Label</t>
+  </si>
+  <si>
+    <t>29 Balmoral Drive, Terrace End</t>
+  </si>
+  <si>
+    <t>1086476 - 00062189 - DG Label</t>
+  </si>
+  <si>
+    <t>91 Managhs Road, Halcombe</t>
+  </si>
+  <si>
+    <t>1086478 - 00060479 - DG Label</t>
+  </si>
+  <si>
+    <t>60 Purnell Street, College Estate</t>
+  </si>
+  <si>
+    <t>1086482 - 00061638 - DG Label</t>
+  </si>
+  <si>
+    <t>1065 Rongotea Road, Rongotea</t>
+  </si>
+  <si>
+    <t>1086483 - 00063913 - DG Label</t>
+  </si>
+  <si>
+    <t>297 Fitzherbert East Road, Aokautere</t>
+  </si>
+  <si>
+    <t>1086484 - 00065455 - DG Label</t>
+  </si>
+  <si>
+    <t>291 Kahuterawa Road, Linton</t>
+  </si>
+  <si>
+    <t>1086485 - 00066284 - DG Label</t>
+  </si>
+  <si>
+    <t>508 Ballance Valley Road, Ballance</t>
+  </si>
+  <si>
+    <t>1086486 - 00058615 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -2011,7 +2059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C263"/>
+  <dimension ref="A1:C271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -4910,6 +4958,94 @@
         <v>525</v>
       </c>
       <c r="C263" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>541</v>
+      </c>
+      <c r="B264" t="s">
+        <v>540</v>
+      </c>
+      <c r="C264" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>539</v>
+      </c>
+      <c r="B265" t="s">
+        <v>538</v>
+      </c>
+      <c r="C265" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>537</v>
+      </c>
+      <c r="B266" t="s">
+        <v>536</v>
+      </c>
+      <c r="C266" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>535</v>
+      </c>
+      <c r="B267" t="s">
+        <v>534</v>
+      </c>
+      <c r="C267" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>533</v>
+      </c>
+      <c r="B268" t="s">
+        <v>532</v>
+      </c>
+      <c r="C268" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>531</v>
+      </c>
+      <c r="B269" t="s">
+        <v>530</v>
+      </c>
+      <c r="C269" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>529</v>
+      </c>
+      <c r="B270" t="s">
+        <v>528</v>
+      </c>
+      <c r="C270" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>527</v>
+      </c>
+      <c r="B271" t="s">
+        <v>526</v>
+      </c>
+      <c r="C271" t="s">
         <v>247</v>
       </c>
     </row>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B142447-0F80-4476-9A99-7CE97CC9EC5A}"/>
+  <xr:revisionPtr revIDLastSave="655" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE298BC4-002C-484B-9B7F-CE86351B51F8}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="546">
   <si>
     <t>Job</t>
   </si>
@@ -761,12 +761,6 @@
     <t>16 PAPAWAI ROAD, GREYTOWN</t>
   </si>
   <si>
-    <t>1082485 - 00052302 - DG Label - 1000615865PCCDB</t>
-  </si>
-  <si>
-    <t>8 GRATITUDE WAY, KELVIN GROVE, PALMERSTON NORTH, 4470</t>
-  </si>
-  <si>
     <t>1082446 - 00050624 - DG Label - 1000580901PC775</t>
   </si>
   <si>
@@ -1451,9 +1445,6 @@
     <t>41 Kowhai Street, Castelcliff, Whanganui, 4501</t>
   </si>
   <si>
-    <t>70 Duddings Lane, Featherson</t>
-  </si>
-  <si>
     <t>178 Kilkern Road, Marton</t>
   </si>
   <si>
@@ -1466,9 +1457,6 @@
     <t>1086155 - 00059130 - DG Label</t>
   </si>
   <si>
-    <t>284 Cambridge Avenue, Ashhurst</t>
-  </si>
-  <si>
     <t>1086153 - 00059404 - DG Label</t>
   </si>
   <si>
@@ -1665,6 +1653,30 @@
   </si>
   <si>
     <t>1086486 - 00058615 - DG Label</t>
+  </si>
+  <si>
+    <t>283 Cambridge Avenue, Ashhurst</t>
+  </si>
+  <si>
+    <t>628 Pukepapa Road, Marton</t>
+  </si>
+  <si>
+    <t>43 Tennyson Avenue, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>70 Duddings Line, Featherson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4a wellesley st </t>
+  </si>
+  <si>
+    <t>1085892 - 00053352 - DG Label</t>
+  </si>
+  <si>
+    <t>1078322 - DG Labelling request - 00038395</t>
+  </si>
+  <si>
+    <t>1085963 - 00057948 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -1700,14 +1712,148 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2059,13 +2205,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C271"/>
+  <dimension ref="A1:E273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2076,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2087,7 +2233,7 @@
         <v>207</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2098,7 +2244,7 @@
         <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2109,7 +2255,7 @@
         <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2120,7 +2266,7 @@
         <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2131,7 +2277,7 @@
         <v>215</v>
       </c>
       <c r="C6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2142,7 +2288,7 @@
         <v>217</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2153,7 +2299,7 @@
         <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2164,7 +2310,7 @@
         <v>221</v>
       </c>
       <c r="C9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2175,7 +2321,7 @@
         <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2186,7 +2332,7 @@
         <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2197,7 +2343,7 @@
         <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2208,7 +2354,7 @@
         <v>229</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2219,7 +2365,7 @@
         <v>231</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2230,7 +2376,7 @@
         <v>233</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2241,7 +2387,7 @@
         <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2252,7 +2398,7 @@
         <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2263,7 +2409,7 @@
         <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2274,7 +2420,7 @@
         <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2285,1503 +2431,1503 @@
         <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s">
-        <v>264</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B24" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C26" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C31" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="C35" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>263</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B39" t="s">
         <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C40" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C42" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C43" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C44" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C45" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C46" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C48" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B51" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C51" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C52" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C53" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B54" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C54" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="C55" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>248</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>248</v>
       </c>
       <c r="C57" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C58" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C59" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C60" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>253</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>247</v>
+        <v>252</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>254</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>247</v>
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C66" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C71" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B72" t="s">
-        <v>261</v>
+        <v>25</v>
       </c>
       <c r="C72" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B75" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C75" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C76" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C80" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B81" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C81" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C82" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C83" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B84" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C85" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C86" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B87" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C88" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C89" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B93" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C93" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C94" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B95" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C95" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C96" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B97" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B98" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="C99" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B100" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C100" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B101" t="s">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="C101" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B103" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B104" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C104" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B105" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C105" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B106" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C106" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B107" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C107" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C108" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B109" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C109" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B110" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C110" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B111" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C111" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B112" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C112" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B113" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B114" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C114" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B115" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C115" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B116" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C117" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>464</v>
       </c>
       <c r="C122" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>466</v>
+        <v>124</v>
       </c>
       <c r="C123" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C124" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C125" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B126" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C126" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C129" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C130" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B131" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C131" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="C133" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B134" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C134" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B135" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C135" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B136" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C136" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B137" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C137" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B138" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C138" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B139" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C139" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B140" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C140" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B141" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C141" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C142" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B143" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C143" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="B144" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="C144" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B145" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B146" t="s">
-        <v>305</v>
+        <v>465</v>
       </c>
       <c r="C146" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B147" t="s">
-        <v>467</v>
+        <v>300</v>
       </c>
       <c r="C147" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B148" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C148" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B149" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C149" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C150" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B151" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C151" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B152" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C152" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B153" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C153" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B154" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C154" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B155" t="s">
-        <v>288</v>
+        <v>466</v>
       </c>
       <c r="C155" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>308</v>
+      </c>
+      <c r="B156" t="s">
         <v>309</v>
       </c>
-      <c r="B156" t="s">
-        <v>468</v>
-      </c>
       <c r="C156" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3792,7 +3938,7 @@
         <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3800,21 +3946,21 @@
         <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>467</v>
       </c>
       <c r="C158" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>313</v>
+      </c>
+      <c r="B159" t="s">
         <v>314</v>
       </c>
-      <c r="B159" t="s">
-        <v>469</v>
-      </c>
       <c r="C159" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3825,7 +3971,7 @@
         <v>316</v>
       </c>
       <c r="C160" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3836,7 +3982,7 @@
         <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -3847,7 +3993,7 @@
         <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3858,7 +4004,7 @@
         <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -3866,21 +4012,21 @@
         <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>324</v>
+        <v>541</v>
       </c>
       <c r="C164" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>324</v>
+      </c>
+      <c r="B165" t="s">
         <v>325</v>
       </c>
-      <c r="B165" t="s">
-        <v>470</v>
-      </c>
       <c r="C165" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -3891,7 +4037,7 @@
         <v>327</v>
       </c>
       <c r="C166" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -3902,7 +4048,7 @@
         <v>329</v>
       </c>
       <c r="C167" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -3913,7 +4059,7 @@
         <v>331</v>
       </c>
       <c r="C168" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -3924,7 +4070,7 @@
         <v>333</v>
       </c>
       <c r="C169" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -3935,7 +4081,7 @@
         <v>335</v>
       </c>
       <c r="C170" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -3946,7 +4092,7 @@
         <v>337</v>
       </c>
       <c r="C171" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3957,7 +4103,7 @@
         <v>339</v>
       </c>
       <c r="C172" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -3968,7 +4114,7 @@
         <v>341</v>
       </c>
       <c r="C173" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -3979,7 +4125,7 @@
         <v>343</v>
       </c>
       <c r="C174" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -3990,7 +4136,7 @@
         <v>345</v>
       </c>
       <c r="C175" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4001,7 +4147,7 @@
         <v>347</v>
       </c>
       <c r="C176" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4012,7 +4158,7 @@
         <v>349</v>
       </c>
       <c r="C177" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4023,7 +4169,7 @@
         <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4034,7 +4180,7 @@
         <v>353</v>
       </c>
       <c r="C179" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4045,7 +4191,7 @@
         <v>355</v>
       </c>
       <c r="C180" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4056,7 +4202,7 @@
         <v>357</v>
       </c>
       <c r="C181" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4067,7 +4213,7 @@
         <v>359</v>
       </c>
       <c r="C182" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4078,7 +4224,7 @@
         <v>361</v>
       </c>
       <c r="C183" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4089,7 +4235,7 @@
         <v>363</v>
       </c>
       <c r="C184" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4100,7 +4246,7 @@
         <v>365</v>
       </c>
       <c r="C185" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4111,7 +4257,7 @@
         <v>367</v>
       </c>
       <c r="C186" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4122,7 +4268,7 @@
         <v>369</v>
       </c>
       <c r="C187" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4133,7 +4279,7 @@
         <v>371</v>
       </c>
       <c r="C188" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4144,7 +4290,7 @@
         <v>373</v>
       </c>
       <c r="C189" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4155,7 +4301,7 @@
         <v>375</v>
       </c>
       <c r="C190" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4166,7 +4312,7 @@
         <v>377</v>
       </c>
       <c r="C191" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4177,7 +4323,7 @@
         <v>379</v>
       </c>
       <c r="C192" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4188,7 +4334,7 @@
         <v>381</v>
       </c>
       <c r="C193" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4199,7 +4345,7 @@
         <v>383</v>
       </c>
       <c r="C194" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4210,7 +4356,7 @@
         <v>385</v>
       </c>
       <c r="C195" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4221,7 +4367,7 @@
         <v>387</v>
       </c>
       <c r="C196" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4232,7 +4378,7 @@
         <v>389</v>
       </c>
       <c r="C197" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4243,7 +4389,7 @@
         <v>391</v>
       </c>
       <c r="C198" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4254,7 +4400,7 @@
         <v>393</v>
       </c>
       <c r="C199" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4265,7 +4411,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4276,7 +4422,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4287,7 +4433,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4298,7 +4444,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4309,7 +4455,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4320,7 +4466,7 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4331,7 +4477,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4342,7 +4488,7 @@
         <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4353,7 +4499,7 @@
         <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4364,7 +4510,7 @@
         <v>413</v>
       </c>
       <c r="C209" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4372,21 +4518,21 @@
         <v>414</v>
       </c>
       <c r="B210" t="s">
-        <v>415</v>
+        <v>363</v>
       </c>
       <c r="C210" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>415</v>
+      </c>
+      <c r="B211" t="s">
         <v>416</v>
       </c>
-      <c r="B211" t="s">
-        <v>365</v>
-      </c>
       <c r="C211" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4397,7 +4543,7 @@
         <v>418</v>
       </c>
       <c r="C212" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4408,7 +4554,7 @@
         <v>420</v>
       </c>
       <c r="C213" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4419,7 +4565,7 @@
         <v>422</v>
       </c>
       <c r="C214" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4430,7 +4576,7 @@
         <v>424</v>
       </c>
       <c r="C215" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4441,7 +4587,7 @@
         <v>426</v>
       </c>
       <c r="C216" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4452,7 +4598,7 @@
         <v>428</v>
       </c>
       <c r="C217" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4463,7 +4609,7 @@
         <v>430</v>
       </c>
       <c r="C218" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4474,7 +4620,7 @@
         <v>432</v>
       </c>
       <c r="C219" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4485,7 +4631,7 @@
         <v>434</v>
       </c>
       <c r="C220" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4496,575 +4642,582 @@
         <v>436</v>
       </c>
       <c r="C221" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="B222" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="C222" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B223" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C223" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B224" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C224" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B225" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C225" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B226" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C226" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B227" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C227" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B228" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C228" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B229" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C229" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B230" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C230" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B231" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C231" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B232" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C232" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="B233" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="C233" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B234" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C234" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B235" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C235" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B236" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C236" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B237" t="s">
-        <v>473</v>
+        <v>538</v>
       </c>
       <c r="C237" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B238" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C238" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B239" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C239" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B240" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C240" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B241" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C241" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B242" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C242" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B243" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C243" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B244" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C244" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B245" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C245" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B246" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C246" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B247" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C247" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B248" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C248" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B249" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C249" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B250" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C250" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B251" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C251" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B252" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C252" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B253" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C253" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="B254" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C254" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B255" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C255" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B256" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C256" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B257" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C257" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B258" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C258" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B259" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C259" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B260" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C260" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B261" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C261" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B262" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C262" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="B263" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C263" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="B264" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C264" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="B265" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C265" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B266" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="C266" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B267" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C267" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B268" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C268" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B269" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C269" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="B270" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C270" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B271" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="C271" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>544</v>
+      </c>
+      <c r="B272" t="s">
+        <v>542</v>
+      </c>
+      <c r="C272" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>545</v>
+      </c>
+      <c r="B273" t="s">
+        <v>539</v>
+      </c>
+      <c r="C273" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E18 E20:E90 E92:E1048573">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>COUNTIF($A:$A, E2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19 E91">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>COUNTIF($A:$A, #REF!)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E1048574:E1048576">
-    <cfRule type="expression" dxfId="0" priority="3">
-      <formula>COUNTIF($A:$A, E1)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="655" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE298BC4-002C-484B-9B7F-CE86351B51F8}"/>
+  <xr:revisionPtr revIDLastSave="684" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB4F4B6-35AD-466D-AA77-08DD0A65F4A7}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="602">
   <si>
     <t>Job</t>
   </si>
@@ -1677,6 +1677,174 @@
   </si>
   <si>
     <t>1085963 - 00057948 - DG Label</t>
+  </si>
+  <si>
+    <t>1086655 - 00064086 - DG Label</t>
+  </si>
+  <si>
+    <t>300 Ahiaruhe Road, Ahiaruhe</t>
+  </si>
+  <si>
+    <t>1086654 - 00067847 - DG Label</t>
+  </si>
+  <si>
+    <t>35 Shelton Place, Feilding</t>
+  </si>
+  <si>
+    <t>1086653 - 00061609 - DG Label</t>
+  </si>
+  <si>
+    <t>1119A Camerons Line, Aorangi</t>
+  </si>
+  <si>
+    <t>1086652 - 00059021 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Pastoral Lane, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086651 - 00058544 - DG Label</t>
+  </si>
+  <si>
+    <t>3 Tutakarae Road, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1086650 - 00063059 - DG Label</t>
+  </si>
+  <si>
+    <t>35 Horseshoe Lane, Pahiatua</t>
+  </si>
+  <si>
+    <t>1086649 - 00056472 - DG Label</t>
+  </si>
+  <si>
+    <t>156 Polson Hill Drive, Aokautere</t>
+  </si>
+  <si>
+    <t>1086648 - 00056476 - DG Label</t>
+  </si>
+  <si>
+    <t>455A Taonui Road, Colyton</t>
+  </si>
+  <si>
+    <t>1086647 - 00056580 - DG Label</t>
+  </si>
+  <si>
+    <t>714 Waimutu Road, Turakina</t>
+  </si>
+  <si>
+    <t>1086645 - 00055182 - DG Label</t>
+  </si>
+  <si>
+    <t>31 Kennedy Avenue, Feilding</t>
+  </si>
+  <si>
+    <t>1086644 - 00055190 - DG Label</t>
+  </si>
+  <si>
+    <t>182 North Street, Feilding</t>
+  </si>
+  <si>
+    <t>1086643 - 00055174 - DG Label</t>
+  </si>
+  <si>
+    <t>146 Mill Road, Rongotea</t>
+  </si>
+  <si>
+    <t>1086642 - 00057023 - DG Label</t>
+  </si>
+  <si>
+    <t>23 Liberty Grove, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1086641 - 00057011 - DG Label</t>
+  </si>
+  <si>
+    <t>18 La Lena Grove, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1086640 - 00056786 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Ake Ake Avenue, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086639 - 00056782 - DG Label</t>
+  </si>
+  <si>
+    <t>173 Valley Views, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1086638 - 00056767 - DG Label</t>
+  </si>
+  <si>
+    <t>45 Pahiatua Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086637 - 00056454 - DG Label</t>
+  </si>
+  <si>
+    <t>1580 State Highway 3, Awahuri</t>
+  </si>
+  <si>
+    <t>1086635 - 00056022 - DG Label</t>
+  </si>
+  <si>
+    <t>992 Tremaine Avenue, Roslyn</t>
+  </si>
+  <si>
+    <t>1086634 - 00056019 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Sharon Place, Awapuni</t>
+  </si>
+  <si>
+    <t>1086633 - 00053622 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Montgomery Terrace, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086632 - 00048393 - DG Label</t>
+  </si>
+  <si>
+    <t>47 Newcastle Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1086631 - 00050566 - DG Label</t>
+  </si>
+  <si>
+    <t>4 Whio Avenue, Feilding</t>
+  </si>
+  <si>
+    <t>1086618 - 00053389 - DG Label</t>
+  </si>
+  <si>
+    <t>58B London Street, Kimbolton</t>
+  </si>
+  <si>
+    <t>1086617 - 00050999 - DG Label</t>
+  </si>
+  <si>
+    <t>26 Tirimoana Place, Otamatea</t>
+  </si>
+  <si>
+    <t>1086616 - 00061593 - DG Label</t>
+  </si>
+  <si>
+    <t>66 Wikitoria Road, Putiki</t>
+  </si>
+  <si>
+    <t>1086615 - 00053909 - DG Label</t>
+  </si>
+  <si>
+    <t>4A Prendiville Lane, Greytown</t>
+  </si>
+  <si>
+    <t>1086613 - 00052969 - DG Label</t>
+  </si>
+  <si>
+    <t>80 Jellicoe Street, Greytown</t>
   </si>
 </sst>
 </file>
@@ -1712,170 +1880,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2205,13 +2217,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -5217,6 +5229,314 @@
         <v>244</v>
       </c>
     </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>546</v>
+      </c>
+      <c r="B274" t="s">
+        <v>547</v>
+      </c>
+      <c r="C274" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>548</v>
+      </c>
+      <c r="B275" t="s">
+        <v>549</v>
+      </c>
+      <c r="C275" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>550</v>
+      </c>
+      <c r="B276" t="s">
+        <v>551</v>
+      </c>
+      <c r="C276" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>552</v>
+      </c>
+      <c r="B277" t="s">
+        <v>553</v>
+      </c>
+      <c r="C277" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>554</v>
+      </c>
+      <c r="B278" t="s">
+        <v>555</v>
+      </c>
+      <c r="C278" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>556</v>
+      </c>
+      <c r="B279" t="s">
+        <v>557</v>
+      </c>
+      <c r="C279" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>558</v>
+      </c>
+      <c r="B280" t="s">
+        <v>559</v>
+      </c>
+      <c r="C280" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>560</v>
+      </c>
+      <c r="B281" t="s">
+        <v>561</v>
+      </c>
+      <c r="C281" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>562</v>
+      </c>
+      <c r="B282" t="s">
+        <v>563</v>
+      </c>
+      <c r="C282" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>564</v>
+      </c>
+      <c r="B283" t="s">
+        <v>565</v>
+      </c>
+      <c r="C283" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>566</v>
+      </c>
+      <c r="B284" t="s">
+        <v>567</v>
+      </c>
+      <c r="C284" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>568</v>
+      </c>
+      <c r="B285" t="s">
+        <v>569</v>
+      </c>
+      <c r="C285" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>570</v>
+      </c>
+      <c r="B286" t="s">
+        <v>571</v>
+      </c>
+      <c r="C286" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>572</v>
+      </c>
+      <c r="B287" t="s">
+        <v>573</v>
+      </c>
+      <c r="C287" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>574</v>
+      </c>
+      <c r="B288" t="s">
+        <v>575</v>
+      </c>
+      <c r="C288" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>576</v>
+      </c>
+      <c r="B289" t="s">
+        <v>577</v>
+      </c>
+      <c r="C289" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>578</v>
+      </c>
+      <c r="B290" t="s">
+        <v>579</v>
+      </c>
+      <c r="C290" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>580</v>
+      </c>
+      <c r="B291" t="s">
+        <v>581</v>
+      </c>
+      <c r="C291" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>582</v>
+      </c>
+      <c r="B292" t="s">
+        <v>583</v>
+      </c>
+      <c r="C292" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>584</v>
+      </c>
+      <c r="B293" t="s">
+        <v>585</v>
+      </c>
+      <c r="C293" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>586</v>
+      </c>
+      <c r="B294" t="s">
+        <v>587</v>
+      </c>
+      <c r="C294" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>588</v>
+      </c>
+      <c r="B295" t="s">
+        <v>589</v>
+      </c>
+      <c r="C295" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>590</v>
+      </c>
+      <c r="B296" t="s">
+        <v>591</v>
+      </c>
+      <c r="C296" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>592</v>
+      </c>
+      <c r="B297" t="s">
+        <v>593</v>
+      </c>
+      <c r="C297" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>594</v>
+      </c>
+      <c r="B298" t="s">
+        <v>595</v>
+      </c>
+      <c r="C298" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>596</v>
+      </c>
+      <c r="B299" t="s">
+        <v>597</v>
+      </c>
+      <c r="C299" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>598</v>
+      </c>
+      <c r="B300" t="s">
+        <v>599</v>
+      </c>
+      <c r="C300" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>600</v>
+      </c>
+      <c r="B301" t="s">
+        <v>601</v>
+      </c>
+      <c r="C301" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="684" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB4F4B6-35AD-466D-AA77-08DD0A65F4A7}"/>
+  <xr:revisionPtr revIDLastSave="692" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC431518-4B3C-4F6E-9EA3-C4E580A93287}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="614">
   <si>
     <t>Job</t>
   </si>
@@ -1845,6 +1845,42 @@
   </si>
   <si>
     <t>80 Jellicoe Street, Greytown</t>
+  </si>
+  <si>
+    <t>1 Kawau Place, Otamatea</t>
+  </si>
+  <si>
+    <t>1086965 - 00061608 - DG Label</t>
+  </si>
+  <si>
+    <t>31 Koromiko Road, Gonville</t>
+  </si>
+  <si>
+    <t>1086967 - 00057376 - DG Label</t>
+  </si>
+  <si>
+    <t>2738 Masterton Castlepoint Road, Mangapakeha</t>
+  </si>
+  <si>
+    <t>1086968 - 00064506 - DG Label</t>
+  </si>
+  <si>
+    <t>110 Fitzroy Street, Terrace End</t>
+  </si>
+  <si>
+    <t>1086969 - 00045408 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Bunny Street, Masterton</t>
+  </si>
+  <si>
+    <t>1086970 - 00057969 - DG Label</t>
+  </si>
+  <si>
+    <t>271 Scotts Road, Linton</t>
+  </si>
+  <si>
+    <t>1086971 - 00048813 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -2217,16 +2253,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C301"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C307"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="64.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2237,7 +2273,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>206</v>
       </c>
@@ -2248,7 +2284,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>208</v>
       </c>
@@ -2259,7 +2295,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>210</v>
       </c>
@@ -2270,7 +2306,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>212</v>
       </c>
@@ -2281,7 +2317,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>214</v>
       </c>
@@ -2292,7 +2328,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>216</v>
       </c>
@@ -2303,7 +2339,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>218</v>
       </c>
@@ -2314,7 +2350,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>220</v>
       </c>
@@ -2325,7 +2361,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>222</v>
       </c>
@@ -2336,7 +2372,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>224</v>
       </c>
@@ -2347,7 +2383,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>226</v>
       </c>
@@ -2358,7 +2394,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>228</v>
       </c>
@@ -2369,7 +2405,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>230</v>
       </c>
@@ -2380,7 +2416,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>232</v>
       </c>
@@ -2391,7 +2427,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>234</v>
       </c>
@@ -2402,7 +2438,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>236</v>
       </c>
@@ -2413,7 +2449,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>238</v>
       </c>
@@ -2424,7 +2460,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>240</v>
       </c>
@@ -2435,7 +2471,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>242</v>
       </c>
@@ -2446,7 +2482,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>141</v>
       </c>
@@ -2457,7 +2493,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>142</v>
       </c>
@@ -2468,7 +2504,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>144</v>
       </c>
@@ -2479,7 +2515,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>146</v>
       </c>
@@ -2490,7 +2526,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>148</v>
       </c>
@@ -2501,7 +2537,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>150</v>
       </c>
@@ -2512,7 +2548,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>152</v>
       </c>
@@ -2523,7 +2559,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>154</v>
       </c>
@@ -2534,7 +2570,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>156</v>
       </c>
@@ -2545,7 +2581,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>158</v>
       </c>
@@ -2556,7 +2592,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>160</v>
       </c>
@@ -2567,7 +2603,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>162</v>
       </c>
@@ -2578,7 +2614,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -2589,7 +2625,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>166</v>
       </c>
@@ -2600,7 +2636,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>168</v>
       </c>
@@ -2611,7 +2647,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>169</v>
       </c>
@@ -2622,7 +2658,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -2633,7 +2669,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>173</v>
       </c>
@@ -2644,7 +2680,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>175</v>
       </c>
@@ -2655,7 +2691,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>176</v>
       </c>
@@ -2666,7 +2702,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>178</v>
       </c>
@@ -2677,7 +2713,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>180</v>
       </c>
@@ -2688,7 +2724,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -2699,7 +2735,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>184</v>
       </c>
@@ -2710,7 +2746,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>186</v>
       </c>
@@ -2721,7 +2757,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>188</v>
       </c>
@@ -2732,7 +2768,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>190</v>
       </c>
@@ -2743,7 +2779,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>192</v>
       </c>
@@ -2754,7 +2790,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>194</v>
       </c>
@@ -2765,7 +2801,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>196</v>
       </c>
@@ -2776,7 +2812,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>198</v>
       </c>
@@ -2787,7 +2823,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>200</v>
       </c>
@@ -2798,7 +2834,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>202</v>
       </c>
@@ -2809,7 +2845,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>204</v>
       </c>
@@ -2820,7 +2856,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2</v>
       </c>
@@ -2831,7 +2867,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -2842,7 +2878,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -2853,7 +2889,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -2864,7 +2900,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>7</v>
       </c>
@@ -2875,7 +2911,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -2886,7 +2922,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -2897,7 +2933,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -2908,7 +2944,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -2919,7 +2955,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -2930,7 +2966,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>15</v>
       </c>
@@ -2941,7 +2977,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -2952,7 +2988,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2963,7 +2999,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -2974,7 +3010,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>20</v>
       </c>
@@ -2985,7 +3021,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -2996,7 +3032,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -3007,7 +3043,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -3018,7 +3054,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>26</v>
       </c>
@@ -3029,7 +3065,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -3040,7 +3076,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>30</v>
       </c>
@@ -3051,7 +3087,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>32</v>
       </c>
@@ -3062,7 +3098,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -3073,7 +3109,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>36</v>
       </c>
@@ -3084,7 +3120,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>38</v>
       </c>
@@ -3095,7 +3131,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -3106,7 +3142,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>42</v>
       </c>
@@ -3117,7 +3153,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>44</v>
       </c>
@@ -3128,7 +3164,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>46</v>
       </c>
@@ -3139,7 +3175,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>48</v>
       </c>
@@ -3150,7 +3186,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>50</v>
       </c>
@@ -3161,7 +3197,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>52</v>
       </c>
@@ -3172,7 +3208,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>54</v>
       </c>
@@ -3183,7 +3219,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>56</v>
       </c>
@@ -3194,7 +3230,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>58</v>
       </c>
@@ -3205,7 +3241,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>60</v>
       </c>
@@ -3216,7 +3252,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>62</v>
       </c>
@@ -3227,7 +3263,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>64</v>
       </c>
@@ -3238,7 +3274,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>66</v>
       </c>
@@ -3249,7 +3285,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>68</v>
       </c>
@@ -3260,7 +3296,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>70</v>
       </c>
@@ -3271,7 +3307,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>72</v>
       </c>
@@ -3282,7 +3318,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>74</v>
       </c>
@@ -3293,7 +3329,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>76</v>
       </c>
@@ -3304,7 +3340,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>78</v>
       </c>
@@ -3315,7 +3351,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>79</v>
       </c>
@@ -3326,7 +3362,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>80</v>
       </c>
@@ -3337,7 +3373,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>82</v>
       </c>
@@ -3348,7 +3384,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>84</v>
       </c>
@@ -3359,7 +3395,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>86</v>
       </c>
@@ -3370,7 +3406,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>88</v>
       </c>
@@ -3381,7 +3417,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>90</v>
       </c>
@@ -3392,7 +3428,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>92</v>
       </c>
@@ -3403,7 +3439,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>94</v>
       </c>
@@ -3414,7 +3450,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>96</v>
       </c>
@@ -3425,7 +3461,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>98</v>
       </c>
@@ -3436,7 +3472,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>100</v>
       </c>
@@ -3447,7 +3483,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>102</v>
       </c>
@@ -3458,7 +3494,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>104</v>
       </c>
@@ -3469,7 +3505,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>106</v>
       </c>
@@ -3480,7 +3516,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>108</v>
       </c>
@@ -3491,7 +3527,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>110</v>
       </c>
@@ -3502,7 +3538,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>112</v>
       </c>
@@ -3513,7 +3549,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>114</v>
       </c>
@@ -3524,7 +3560,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>116</v>
       </c>
@@ -3535,7 +3571,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -3546,7 +3582,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -3557,7 +3593,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -3568,7 +3604,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -3579,7 +3615,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>125</v>
       </c>
@@ -3590,7 +3626,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -3601,7 +3637,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>129</v>
       </c>
@@ -3612,7 +3648,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -3623,7 +3659,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>133</v>
       </c>
@@ -3634,7 +3670,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>135</v>
       </c>
@@ -3645,7 +3681,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -3656,7 +3692,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>139</v>
       </c>
@@ -3667,7 +3703,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>277</v>
       </c>
@@ -3678,7 +3714,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>276</v>
       </c>
@@ -3689,7 +3725,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>274</v>
       </c>
@@ -3700,7 +3736,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>272</v>
       </c>
@@ -3711,7 +3747,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>270</v>
       </c>
@@ -3722,7 +3758,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>268</v>
       </c>
@@ -3733,7 +3769,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>266</v>
       </c>
@@ -3744,7 +3780,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>264</v>
       </c>
@@ -3755,7 +3791,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>285</v>
       </c>
@@ -3766,7 +3802,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>283</v>
       </c>
@@ -3777,7 +3813,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>281</v>
       </c>
@@ -3788,7 +3824,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>279</v>
       </c>
@@ -3799,7 +3835,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>306</v>
       </c>
@@ -3810,7 +3846,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>304</v>
       </c>
@@ -3821,7 +3857,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>302</v>
       </c>
@@ -3832,7 +3868,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>301</v>
       </c>
@@ -3843,7 +3879,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>299</v>
       </c>
@@ -3854,7 +3890,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>297</v>
       </c>
@@ -3865,7 +3901,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>295</v>
       </c>
@@ -3876,7 +3912,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>293</v>
       </c>
@@ -3887,7 +3923,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>291</v>
       </c>
@@ -3898,7 +3934,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>289</v>
       </c>
@@ -3909,7 +3945,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>287</v>
       </c>
@@ -3920,7 +3956,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>307</v>
       </c>
@@ -3931,7 +3967,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>308</v>
       </c>
@@ -3942,7 +3978,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>310</v>
       </c>
@@ -3953,7 +3989,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>312</v>
       </c>
@@ -3964,7 +4000,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>313</v>
       </c>
@@ -3975,7 +4011,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>315</v>
       </c>
@@ -3986,7 +4022,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>317</v>
       </c>
@@ -3997,7 +4033,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>319</v>
       </c>
@@ -4008,7 +4044,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>321</v>
       </c>
@@ -4019,7 +4055,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>323</v>
       </c>
@@ -4030,7 +4066,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>324</v>
       </c>
@@ -4041,7 +4077,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>326</v>
       </c>
@@ -4052,7 +4088,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>328</v>
       </c>
@@ -4063,7 +4099,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>330</v>
       </c>
@@ -4074,7 +4110,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>332</v>
       </c>
@@ -4085,7 +4121,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>334</v>
       </c>
@@ -4096,7 +4132,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>336</v>
       </c>
@@ -4107,7 +4143,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>338</v>
       </c>
@@ -4118,7 +4154,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>340</v>
       </c>
@@ -4129,7 +4165,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>342</v>
       </c>
@@ -4140,7 +4176,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>344</v>
       </c>
@@ -4151,7 +4187,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>346</v>
       </c>
@@ -4162,7 +4198,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>348</v>
       </c>
@@ -4173,7 +4209,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>350</v>
       </c>
@@ -4184,7 +4220,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>352</v>
       </c>
@@ -4195,7 +4231,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>354</v>
       </c>
@@ -4206,7 +4242,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>356</v>
       </c>
@@ -4217,7 +4253,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>358</v>
       </c>
@@ -4228,7 +4264,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>360</v>
       </c>
@@ -4239,7 +4275,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>362</v>
       </c>
@@ -4250,7 +4286,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>364</v>
       </c>
@@ -4261,7 +4297,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>366</v>
       </c>
@@ -4272,7 +4308,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>368</v>
       </c>
@@ -4283,7 +4319,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>370</v>
       </c>
@@ -4294,7 +4330,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>372</v>
       </c>
@@ -4305,7 +4341,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>374</v>
       </c>
@@ -4316,7 +4352,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>376</v>
       </c>
@@ -4327,7 +4363,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>378</v>
       </c>
@@ -4338,7 +4374,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>380</v>
       </c>
@@ -4349,7 +4385,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>382</v>
       </c>
@@ -4360,7 +4396,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>384</v>
       </c>
@@ -4371,7 +4407,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>386</v>
       </c>
@@ -4382,7 +4418,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>388</v>
       </c>
@@ -4393,7 +4429,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>390</v>
       </c>
@@ -4404,7 +4440,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>392</v>
       </c>
@@ -4415,7 +4451,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>394</v>
       </c>
@@ -4426,7 +4462,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>396</v>
       </c>
@@ -4437,7 +4473,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>398</v>
       </c>
@@ -4448,7 +4484,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>400</v>
       </c>
@@ -4459,7 +4495,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>402</v>
       </c>
@@ -4470,7 +4506,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>404</v>
       </c>
@@ -4481,7 +4517,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>406</v>
       </c>
@@ -4492,7 +4528,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>408</v>
       </c>
@@ -4503,7 +4539,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>410</v>
       </c>
@@ -4514,7 +4550,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>412</v>
       </c>
@@ -4525,7 +4561,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>414</v>
       </c>
@@ -4536,7 +4572,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>415</v>
       </c>
@@ -4547,7 +4583,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>417</v>
       </c>
@@ -4558,7 +4594,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>419</v>
       </c>
@@ -4569,7 +4605,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>421</v>
       </c>
@@ -4580,7 +4616,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>423</v>
       </c>
@@ -4591,7 +4627,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>425</v>
       </c>
@@ -4602,7 +4638,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>427</v>
       </c>
@@ -4613,7 +4649,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>429</v>
       </c>
@@ -4624,7 +4660,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>431</v>
       </c>
@@ -4635,7 +4671,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>433</v>
       </c>
@@ -4646,7 +4682,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>435</v>
       </c>
@@ -4657,7 +4693,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>458</v>
       </c>
@@ -4668,7 +4704,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>456</v>
       </c>
@@ -4679,7 +4715,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>454</v>
       </c>
@@ -4690,7 +4726,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>452</v>
       </c>
@@ -4701,7 +4737,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>450</v>
       </c>
@@ -4712,7 +4748,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>448</v>
       </c>
@@ -4723,7 +4759,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>446</v>
       </c>
@@ -4734,7 +4770,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>444</v>
       </c>
@@ -4745,7 +4781,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>442</v>
       </c>
@@ -4756,7 +4792,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>440</v>
       </c>
@@ -4767,7 +4803,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>438</v>
       </c>
@@ -4778,7 +4814,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>461</v>
       </c>
@@ -4789,7 +4825,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>459</v>
       </c>
@@ -4800,7 +4836,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>462</v>
       </c>
@@ -4811,7 +4847,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>469</v>
       </c>
@@ -4822,7 +4858,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>471</v>
       </c>
@@ -4833,7 +4869,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>472</v>
       </c>
@@ -4844,7 +4880,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>474</v>
       </c>
@@ -4855,7 +4891,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>477</v>
       </c>
@@ -4866,7 +4902,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>478</v>
       </c>
@@ -4877,7 +4913,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>480</v>
       </c>
@@ -4888,7 +4924,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>482</v>
       </c>
@@ -4899,7 +4935,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>484</v>
       </c>
@@ -4910,7 +4946,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>486</v>
       </c>
@@ -4921,7 +4957,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>488</v>
       </c>
@@ -4932,7 +4968,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>490</v>
       </c>
@@ -4943,7 +4979,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>492</v>
       </c>
@@ -4954,7 +4990,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>494</v>
       </c>
@@ -4965,7 +5001,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>496</v>
       </c>
@@ -4976,7 +5012,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>498</v>
       </c>
@@ -4987,7 +5023,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>500</v>
       </c>
@@ -4998,7 +5034,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>507</v>
       </c>
@@ -5009,7 +5045,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>502</v>
       </c>
@@ -5020,7 +5056,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>503</v>
       </c>
@@ -5031,7 +5067,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>504</v>
       </c>
@@ -5042,7 +5078,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>505</v>
       </c>
@@ -5053,7 +5089,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>506</v>
       </c>
@@ -5064,7 +5100,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>514</v>
       </c>
@@ -5075,7 +5111,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>516</v>
       </c>
@@ -5086,7 +5122,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>518</v>
       </c>
@@ -5097,7 +5133,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>520</v>
       </c>
@@ -5108,7 +5144,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>537</v>
       </c>
@@ -5119,7 +5155,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>535</v>
       </c>
@@ -5130,7 +5166,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>533</v>
       </c>
@@ -5141,7 +5177,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>531</v>
       </c>
@@ -5152,7 +5188,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>529</v>
       </c>
@@ -5163,7 +5199,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>527</v>
       </c>
@@ -5174,7 +5210,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>525</v>
       </c>
@@ -5185,7 +5221,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>523</v>
       </c>
@@ -5196,7 +5232,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>543</v>
       </c>
@@ -5207,7 +5243,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>544</v>
       </c>
@@ -5218,7 +5254,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>545</v>
       </c>
@@ -5229,7 +5265,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>546</v>
       </c>
@@ -5240,7 +5276,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>548</v>
       </c>
@@ -5251,7 +5287,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>550</v>
       </c>
@@ -5262,7 +5298,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>552</v>
       </c>
@@ -5273,7 +5309,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>554</v>
       </c>
@@ -5284,7 +5320,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>556</v>
       </c>
@@ -5295,7 +5331,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>558</v>
       </c>
@@ -5306,7 +5342,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>560</v>
       </c>
@@ -5317,7 +5353,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>562</v>
       </c>
@@ -5328,7 +5364,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>564</v>
       </c>
@@ -5339,7 +5375,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>566</v>
       </c>
@@ -5350,7 +5386,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>568</v>
       </c>
@@ -5361,7 +5397,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>570</v>
       </c>
@@ -5372,7 +5408,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>572</v>
       </c>
@@ -5383,7 +5419,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>574</v>
       </c>
@@ -5394,7 +5430,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>576</v>
       </c>
@@ -5405,7 +5441,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>578</v>
       </c>
@@ -5416,7 +5452,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>580</v>
       </c>
@@ -5427,7 +5463,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>582</v>
       </c>
@@ -5438,7 +5474,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>584</v>
       </c>
@@ -5449,7 +5485,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>586</v>
       </c>
@@ -5460,7 +5496,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>588</v>
       </c>
@@ -5471,7 +5507,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>590</v>
       </c>
@@ -5482,7 +5518,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>592</v>
       </c>
@@ -5493,7 +5529,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>594</v>
       </c>
@@ -5504,7 +5540,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>596</v>
       </c>
@@ -5515,7 +5551,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>598</v>
       </c>
@@ -5526,7 +5562,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>600</v>
       </c>
@@ -5535,6 +5571,72 @@
       </c>
       <c r="C301" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>613</v>
+      </c>
+      <c r="B302" t="s">
+        <v>612</v>
+      </c>
+      <c r="C302" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>611</v>
+      </c>
+      <c r="B303" t="s">
+        <v>610</v>
+      </c>
+      <c r="C303" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>609</v>
+      </c>
+      <c r="B304" t="s">
+        <v>608</v>
+      </c>
+      <c r="C304" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>607</v>
+      </c>
+      <c r="B305" t="s">
+        <v>606</v>
+      </c>
+      <c r="C305" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>605</v>
+      </c>
+      <c r="B306" t="s">
+        <v>604</v>
+      </c>
+      <c r="C306" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>603</v>
+      </c>
+      <c r="B307" t="s">
+        <v>602</v>
+      </c>
+      <c r="C307" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="692" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC431518-4B3C-4F6E-9EA3-C4E580A93287}"/>
+  <xr:revisionPtr revIDLastSave="697" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC85199F-6C26-4AC7-BDA5-78CA6E746EFB}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="604">
   <si>
     <t>Job</t>
   </si>
@@ -1352,12 +1352,6 @@
     <t>43 Tirimoana Place, Otamatea</t>
   </si>
   <si>
-    <t>3 Riverstone Grove, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1086010 - 00059961 - DG Label</t>
-  </si>
-  <si>
     <t>1132 Pohangina Valley East Road, Pohangina</t>
   </si>
   <si>
@@ -1763,24 +1757,12 @@
     <t>18 La Lena Grove, Fitzherbert</t>
   </si>
   <si>
-    <t>1086640 - 00056786 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Ake Ake Avenue, Hokowhitu</t>
-  </si>
-  <si>
     <t>1086639 - 00056782 - DG Label</t>
   </si>
   <si>
     <t>173 Valley Views, Fitzherbert</t>
   </si>
   <si>
-    <t>1086638 - 00056767 - DG Label</t>
-  </si>
-  <si>
-    <t>45 Pahiatua Street, Hokowhitu</t>
-  </si>
-  <si>
     <t>1086637 - 00056454 - DG Label</t>
   </si>
   <si>
@@ -1797,18 +1779,6 @@
   </si>
   <si>
     <t>9 Sharon Place, Awapuni</t>
-  </si>
-  <si>
-    <t>1086633 - 00053622 - DG Label</t>
-  </si>
-  <si>
-    <t>9 Montgomery Terrace, Hokowhitu</t>
-  </si>
-  <si>
-    <t>1086632 - 00048393 - DG Label</t>
-  </si>
-  <si>
-    <t>47 Newcastle Street, Hokowhitu</t>
   </si>
   <si>
     <t>1086631 - 00050566 - DG Label</t>
@@ -2253,7 +2223,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C307"/>
+  <dimension ref="A1:C302"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -3598,7 +3568,7 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C122" t="s">
         <v>244</v>
@@ -3862,7 +3832,7 @@
         <v>302</v>
       </c>
       <c r="B146" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C146" t="s">
         <v>245</v>
@@ -3961,7 +3931,7 @@
         <v>307</v>
       </c>
       <c r="B155" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C155" t="s">
         <v>244</v>
@@ -3994,7 +3964,7 @@
         <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C158" t="s">
         <v>244</v>
@@ -4060,7 +4030,7 @@
         <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C164" t="s">
         <v>245</v>
@@ -4695,10 +4665,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B222" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C222" t="s">
         <v>245</v>
@@ -4706,10 +4676,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C223" t="s">
         <v>245</v>
@@ -4717,10 +4687,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B224" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C224" t="s">
         <v>245</v>
@@ -4728,10 +4698,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C225" t="s">
         <v>244</v>
@@ -4739,10 +4709,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B226" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C226" t="s">
         <v>244</v>
@@ -4750,10 +4720,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B227" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C227" t="s">
         <v>244</v>
@@ -4761,10 +4731,10 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B228" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C228" t="s">
         <v>245</v>
@@ -4772,10 +4742,10 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B229" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C229" t="s">
         <v>245</v>
@@ -4783,10 +4753,10 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B230" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C230" t="s">
         <v>245</v>
@@ -4794,10 +4764,10 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B231" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C231" t="s">
         <v>244</v>
@@ -4805,10 +4775,10 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="B232" t="s">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="C232" t="s">
         <v>245</v>
@@ -4816,21 +4786,21 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B233" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="C233" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B234" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C234" t="s">
         <v>244</v>
@@ -4838,13 +4808,13 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B235" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C235" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
@@ -4852,18 +4822,18 @@
         <v>469</v>
       </c>
       <c r="B236" t="s">
-        <v>470</v>
+        <v>536</v>
       </c>
       <c r="C236" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
+        <v>470</v>
+      </c>
+      <c r="B237" t="s">
         <v>471</v>
-      </c>
-      <c r="B237" t="s">
-        <v>538</v>
       </c>
       <c r="C237" t="s">
         <v>244</v>
@@ -4882,10 +4852,10 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
+        <v>475</v>
+      </c>
+      <c r="B239" t="s">
         <v>474</v>
-      </c>
-      <c r="B239" t="s">
-        <v>475</v>
       </c>
       <c r="C239" t="s">
         <v>244</v>
@@ -4893,10 +4863,10 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
+        <v>476</v>
+      </c>
+      <c r="B240" t="s">
         <v>477</v>
-      </c>
-      <c r="B240" t="s">
-        <v>476</v>
       </c>
       <c r="C240" t="s">
         <v>244</v>
@@ -4910,7 +4880,7 @@
         <v>479</v>
       </c>
       <c r="C241" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -4921,7 +4891,7 @@
         <v>481</v>
       </c>
       <c r="C242" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
@@ -4943,7 +4913,7 @@
         <v>485</v>
       </c>
       <c r="C244" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
@@ -4954,7 +4924,7 @@
         <v>487</v>
       </c>
       <c r="C245" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
@@ -4965,7 +4935,7 @@
         <v>489</v>
       </c>
       <c r="C246" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -5009,7 +4979,7 @@
         <v>497</v>
       </c>
       <c r="C250" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -5020,37 +4990,37 @@
         <v>499</v>
       </c>
       <c r="C251" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B252" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C252" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
+        <v>500</v>
+      </c>
+      <c r="B253" t="s">
         <v>507</v>
       </c>
-      <c r="B253" t="s">
-        <v>508</v>
-      </c>
       <c r="C253" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B254" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C254" t="s">
         <v>245</v>
@@ -5058,21 +5028,21 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B255" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C255" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B256" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C256" t="s">
         <v>244</v>
@@ -5080,18 +5050,18 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B257" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C257" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="B258" t="s">
         <v>513</v>
@@ -5108,7 +5078,7 @@
         <v>515</v>
       </c>
       <c r="C259" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -5119,7 +5089,7 @@
         <v>517</v>
       </c>
       <c r="C260" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -5135,21 +5105,21 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="B262" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="C262" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B263" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C263" t="s">
         <v>244</v>
@@ -5157,65 +5127,65 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B264" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C264" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B265" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C265" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C266" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B267" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C267" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B268" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C268" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B269" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C269" t="s">
         <v>245</v>
@@ -5223,10 +5193,10 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="B270" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="C270" t="s">
         <v>245</v>
@@ -5234,21 +5204,21 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B271" t="s">
         <v>540</v>
       </c>
       <c r="C271" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B272" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C272" t="s">
         <v>244</v>
@@ -5256,10 +5226,10 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
+        <v>544</v>
+      </c>
+      <c r="B273" t="s">
         <v>545</v>
-      </c>
-      <c r="B273" t="s">
-        <v>539</v>
       </c>
       <c r="C273" t="s">
         <v>244</v>
@@ -5273,7 +5243,7 @@
         <v>547</v>
       </c>
       <c r="C274" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
@@ -5328,7 +5298,7 @@
         <v>557</v>
       </c>
       <c r="C279" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
@@ -5339,7 +5309,7 @@
         <v>559</v>
       </c>
       <c r="C280" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
@@ -5350,7 +5320,7 @@
         <v>561</v>
       </c>
       <c r="C281" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
@@ -5361,7 +5331,7 @@
         <v>563</v>
       </c>
       <c r="C282" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
@@ -5383,7 +5353,7 @@
         <v>567</v>
       </c>
       <c r="C284" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -5394,7 +5364,7 @@
         <v>569</v>
       </c>
       <c r="C285" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -5416,7 +5386,7 @@
         <v>573</v>
       </c>
       <c r="C287" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -5427,7 +5397,7 @@
         <v>575</v>
       </c>
       <c r="C288" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -5438,7 +5408,7 @@
         <v>577</v>
       </c>
       <c r="C289" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -5460,7 +5430,7 @@
         <v>581</v>
       </c>
       <c r="C291" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
@@ -5493,7 +5463,7 @@
         <v>587</v>
       </c>
       <c r="C294" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
@@ -5515,37 +5485,37 @@
         <v>591</v>
       </c>
       <c r="C296" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="B297" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="C297" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="B298" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C298" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B299" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C299" t="s">
         <v>244</v>
@@ -5553,10 +5523,10 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B300" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="C300" t="s">
         <v>245</v>
@@ -5564,10 +5534,10 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B301" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="C301" t="s">
         <v>244</v>
@@ -5575,67 +5545,12 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="B302" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="C302" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
-        <v>611</v>
-      </c>
-      <c r="B303" t="s">
-        <v>610</v>
-      </c>
-      <c r="C303" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A304" t="s">
-        <v>609</v>
-      </c>
-      <c r="B304" t="s">
-        <v>608</v>
-      </c>
-      <c r="C304" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A305" t="s">
-        <v>607</v>
-      </c>
-      <c r="B305" t="s">
-        <v>606</v>
-      </c>
-      <c r="C305" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A306" t="s">
-        <v>605</v>
-      </c>
-      <c r="B306" t="s">
-        <v>604</v>
-      </c>
-      <c r="C306" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A307" t="s">
-        <v>603</v>
-      </c>
-      <c r="B307" t="s">
-        <v>602</v>
-      </c>
-      <c r="C307" t="s">
         <v>245</v>
       </c>
     </row>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="697" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC85199F-6C26-4AC7-BDA5-78CA6E746EFB}"/>
+  <xr:revisionPtr revIDLastSave="717" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1438435-E7EF-437E-8CCE-954BF5FD1BF2}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="627">
   <si>
     <t>Job</t>
   </si>
@@ -1851,6 +1851,75 @@
   </si>
   <si>
     <t>1086971 - 00048813 - DG Label</t>
+  </si>
+  <si>
+    <t>1087125 - 00063134 - DG Label</t>
+  </si>
+  <si>
+    <t>34 Caroline Crescent, Highbury</t>
+  </si>
+  <si>
+    <t>1087124 - 00060146 - DG Label</t>
+  </si>
+  <si>
+    <t>4A Cedar Crescent, Feilding</t>
+  </si>
+  <si>
+    <t>1087123 - 00059710 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Blennerville Close, Marton</t>
+  </si>
+  <si>
+    <t>1087122 - 00056485 - DG Label</t>
+  </si>
+  <si>
+    <t>102 Rosina Road, Tangimoana</t>
+  </si>
+  <si>
+    <t>1087121 - 00062073 - DG Label</t>
+  </si>
+  <si>
+    <t>86 Pacific Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087120 - 00061616 - DG Label</t>
+  </si>
+  <si>
+    <t>5 Tower Place, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087119 - 00057022 - DG Label</t>
+  </si>
+  <si>
+    <t>132 Winchester Street, Ashhurst</t>
+  </si>
+  <si>
+    <t>1087118 - 00065860 - DG Label</t>
+  </si>
+  <si>
+    <t>27 Mahoney Street, Whanganui East</t>
+  </si>
+  <si>
+    <t>1087116 - 00052080 - DG Label</t>
+  </si>
+  <si>
+    <t>23 Renall Street, Masterton</t>
+  </si>
+  <si>
+    <t>1087115 - 00056539 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Diamond Street, Carterton</t>
+  </si>
+  <si>
+    <t>1087113 - 00057205 - DG Label</t>
+  </si>
+  <si>
+    <t>52 Cross Creek Road, Western Lake</t>
+  </si>
+  <si>
+    <t>S</t>
   </si>
 </sst>
 </file>
@@ -2223,7 +2292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C302"/>
+  <dimension ref="A1:E313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5554,6 +5623,130 @@
         <v>245</v>
       </c>
     </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>604</v>
+      </c>
+      <c r="B303" t="s">
+        <v>605</v>
+      </c>
+      <c r="C303" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>606</v>
+      </c>
+      <c r="B304" t="s">
+        <v>607</v>
+      </c>
+      <c r="C304" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>608</v>
+      </c>
+      <c r="B305" t="s">
+        <v>609</v>
+      </c>
+      <c r="C305" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>610</v>
+      </c>
+      <c r="B306" t="s">
+        <v>611</v>
+      </c>
+      <c r="C306" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>612</v>
+      </c>
+      <c r="B307" t="s">
+        <v>613</v>
+      </c>
+      <c r="C307" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>614</v>
+      </c>
+      <c r="B308" t="s">
+        <v>615</v>
+      </c>
+      <c r="C308" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>616</v>
+      </c>
+      <c r="B309" t="s">
+        <v>617</v>
+      </c>
+      <c r="C309" t="s">
+        <v>244</v>
+      </c>
+      <c r="E309" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>618</v>
+      </c>
+      <c r="B310" t="s">
+        <v>619</v>
+      </c>
+      <c r="C310" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>620</v>
+      </c>
+      <c r="B311" t="s">
+        <v>621</v>
+      </c>
+      <c r="C311" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>622</v>
+      </c>
+      <c r="B312" t="s">
+        <v>623</v>
+      </c>
+      <c r="C312" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>624</v>
+      </c>
+      <c r="B313" t="s">
+        <v>625</v>
+      </c>
+      <c r="C313" t="s">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="717" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1438435-E7EF-437E-8CCE-954BF5FD1BF2}"/>
+  <xr:revisionPtr revIDLastSave="734" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28E13D46-598E-40A5-BD99-BB5F04262D07}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="654">
   <si>
     <t>Job</t>
   </si>
@@ -1919,7 +1919,88 @@
     <t>52 Cross Creek Road, Western Lake</t>
   </si>
   <si>
-    <t>S</t>
+    <t>40 Johnson Street, Bulls</t>
+  </si>
+  <si>
+    <t>1087138 - 00070376 - DG Label</t>
+  </si>
+  <si>
+    <t>51 Coutts Way, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087139 - 00064745 - DG Label</t>
+  </si>
+  <si>
+    <t>257 Victoria Avenue, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087140 - 00065085 - DG Label</t>
+  </si>
+  <si>
+    <t>163 Nannestads Line, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1087141 - 00065202 - DG Label</t>
+  </si>
+  <si>
+    <t>6 Goodwyn Crescent, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087142 - 00065225 - DG Label</t>
+  </si>
+  <si>
+    <t>47 Collingwood Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087143 - 00065762 - DG Label</t>
+  </si>
+  <si>
+    <t>1 Sunshine Place, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087144 - 00067318 - DG Label</t>
+  </si>
+  <si>
+    <t>65 Stanley Avenue, Palmerston North</t>
+  </si>
+  <si>
+    <t>1087145 - 00027716 - DG Label</t>
+  </si>
+  <si>
+    <t>84 Waicola Drive, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087146 - 00028635 - DG Label</t>
+  </si>
+  <si>
+    <t>208 John F Kennedy Drive, Milson</t>
+  </si>
+  <si>
+    <t>1087147 - 00040396 - DG Label</t>
+  </si>
+  <si>
+    <t>32 Lincoln Terrace, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087148 - 00053854 - DG Label</t>
+  </si>
+  <si>
+    <t>81 Hillcrest Drive, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087149 - 00062522 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Logan Place, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087150 - 00029185 - DG Label</t>
+  </si>
+  <si>
+    <t>60 Ihaka Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087151 - 00053065 - DG Label</t>
   </si>
 </sst>
 </file>
@@ -2292,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:E313"/>
+  <dimension ref="A1:C327"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5645,7 +5726,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>608</v>
       </c>
@@ -5656,7 +5737,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>610</v>
       </c>
@@ -5667,7 +5748,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>612</v>
       </c>
@@ -5678,7 +5759,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>614</v>
       </c>
@@ -5689,7 +5770,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>616</v>
       </c>
@@ -5699,11 +5780,8 @@
       <c r="C309" t="s">
         <v>244</v>
       </c>
-      <c r="E309" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>618</v>
       </c>
@@ -5714,7 +5792,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>620</v>
       </c>
@@ -5725,7 +5803,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>622</v>
       </c>
@@ -5736,7 +5814,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>624</v>
       </c>
@@ -5744,6 +5822,160 @@
         <v>625</v>
       </c>
       <c r="C313" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>653</v>
+      </c>
+      <c r="B314" t="s">
+        <v>652</v>
+      </c>
+      <c r="C314" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>651</v>
+      </c>
+      <c r="B315" t="s">
+        <v>650</v>
+      </c>
+      <c r="C315" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>649</v>
+      </c>
+      <c r="B316" t="s">
+        <v>648</v>
+      </c>
+      <c r="C316" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>647</v>
+      </c>
+      <c r="B317" t="s">
+        <v>646</v>
+      </c>
+      <c r="C317" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>645</v>
+      </c>
+      <c r="B318" t="s">
+        <v>644</v>
+      </c>
+      <c r="C318" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>643</v>
+      </c>
+      <c r="B319" t="s">
+        <v>642</v>
+      </c>
+      <c r="C319" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>641</v>
+      </c>
+      <c r="B320" t="s">
+        <v>640</v>
+      </c>
+      <c r="C320" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>639</v>
+      </c>
+      <c r="B321" t="s">
+        <v>638</v>
+      </c>
+      <c r="C321" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>637</v>
+      </c>
+      <c r="B322" t="s">
+        <v>636</v>
+      </c>
+      <c r="C322" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>635</v>
+      </c>
+      <c r="B323" t="s">
+        <v>634</v>
+      </c>
+      <c r="C323" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>633</v>
+      </c>
+      <c r="B324" t="s">
+        <v>632</v>
+      </c>
+      <c r="C324" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>631</v>
+      </c>
+      <c r="B325" t="s">
+        <v>630</v>
+      </c>
+      <c r="C325" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>629</v>
+      </c>
+      <c r="B326" t="s">
+        <v>628</v>
+      </c>
+      <c r="C326" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>627</v>
+      </c>
+      <c r="B327" t="s">
+        <v>626</v>
+      </c>
+      <c r="C327" t="s">
         <v>244</v>
       </c>
     </row>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="734" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28E13D46-598E-40A5-BD99-BB5F04262D07}"/>
+  <xr:revisionPtr revIDLastSave="762" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C7C1B3-901F-49FD-B64D-E6228AD323DC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
+    <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="614">
   <si>
     <t>Job</t>
   </si>
@@ -68,12 +68,6 @@
     <t>1084461 - 00050984 - DG Label</t>
   </si>
   <si>
-    <t>1084307 - 00059085 - DG Label</t>
-  </si>
-  <si>
-    <t>985 Parewanui Road, Bulls</t>
-  </si>
-  <si>
     <t>1084171 - 00014163 - DG Label</t>
   </si>
   <si>
@@ -86,9 +80,6 @@
     <t>1084083 - 00057507 - DG Label</t>
   </si>
   <si>
-    <t>1084081 - 00056505 - DG Label</t>
-  </si>
-  <si>
     <t>1084080 - 00054165 - DG Label</t>
   </si>
   <si>
@@ -113,12 +104,6 @@
     <t>1084055 - 00021842 - DG Label</t>
   </si>
   <si>
-    <t>1083913 - 00050014 - DG Label</t>
-  </si>
-  <si>
-    <t>8 Toia Street, Marton</t>
-  </si>
-  <si>
     <t>1083912 - 00050108 - DG Label</t>
   </si>
   <si>
@@ -197,12 +182,6 @@
     <t>17 Richmond Road, Carterton</t>
   </si>
   <si>
-    <t>1083708 - 00055068 - DG Label</t>
-  </si>
-  <si>
-    <t>215 Calico Line, Marton</t>
-  </si>
-  <si>
     <t>1083706 - 00039727 - DG Label</t>
   </si>
   <si>
@@ -371,12 +350,6 @@
     <t>570 Roberts Line, Kelvin Grove</t>
   </si>
   <si>
-    <t>1083193 - 00058143 - DG Label</t>
-  </si>
-  <si>
-    <t>152 Turitea Road, Turitea</t>
-  </si>
-  <si>
     <t>1083189 - 00055734 - DG Label</t>
   </si>
   <si>
@@ -422,12 +395,6 @@
     <t>722 Upper Plain Road, Masterton</t>
   </si>
   <si>
-    <t>1083033 - 00039972 - DG Label</t>
-  </si>
-  <si>
-    <t>20 Langley Avenue, Milson</t>
-  </si>
-  <si>
     <t>1083023 - 00022620 - DG Label</t>
   </si>
   <si>
@@ -800,9 +767,6 @@
     <t>89 Dublin Street, Martinborough</t>
   </si>
   <si>
-    <t>1853 Rongotea Road, Rongotea</t>
-  </si>
-  <si>
     <t>4 Wake Place, Aokautere</t>
   </si>
   <si>
@@ -929,27 +893,12 @@
     <t>1085282 - 00063388 - DG Label</t>
   </si>
   <si>
-    <t>14 Tangaroa View, Otamatea</t>
-  </si>
-  <si>
-    <t>1085283 - 00062392 - DG Label</t>
-  </si>
-  <si>
     <t>142 West Street, Feilding</t>
   </si>
   <si>
     <t>1085285 - 00054784 - DG Label</t>
   </si>
   <si>
-    <t>5B Blennerville Close, Marton</t>
-  </si>
-  <si>
-    <t>1085287 - 00056035 - DG Label</t>
-  </si>
-  <si>
-    <t>1085288 - 00052613 - DG Label</t>
-  </si>
-  <si>
     <t>4 Barracks Avenue, Solway</t>
   </si>
   <si>
@@ -1121,12 +1070,6 @@
     <t>19 Bengston Street, Eketahuna</t>
   </si>
   <si>
-    <t>1085624 - 00045886 - DG Label</t>
-  </si>
-  <si>
-    <t>17 Pickwick Road, Otamatea</t>
-  </si>
-  <si>
     <t>1085623 - 00035552 - DG Label</t>
   </si>
   <si>
@@ -1271,12 +1214,6 @@
     <t>6 Monmouth Street, Feilding</t>
   </si>
   <si>
-    <t>1085712 - 00055446 - DG Label</t>
-  </si>
-  <si>
-    <t>262 Campbell Road, Brunswick</t>
-  </si>
-  <si>
     <t>1085711 - 00060489 - DG Label</t>
   </si>
   <si>
@@ -1322,12 +1259,6 @@
     <t>33 Hughes Line, Clareville</t>
   </si>
   <si>
-    <t>1085916 - 00050209 - DG Label</t>
-  </si>
-  <si>
-    <t>587 Rapanui Road, Kai Iwi</t>
-  </si>
-  <si>
     <t>1085915 - 00061776 - DG Label</t>
   </si>
   <si>
@@ -1346,12 +1277,6 @@
     <t>427C Ruahine Street, Terrace End</t>
   </si>
   <si>
-    <t>1085910 - 00061603 - DG Label</t>
-  </si>
-  <si>
-    <t>43 Tirimoana Place, Otamatea</t>
-  </si>
-  <si>
     <t>1132 Pohangina Valley East Road, Pohangina</t>
   </si>
   <si>
@@ -1418,9 +1343,6 @@
     <t>329 Kahuterawa Road, Linton</t>
   </si>
   <si>
-    <t>1086113 - 00061650 - DG Label</t>
-  </si>
-  <si>
     <t>1086116 - 00052128 - DG Label</t>
   </si>
   <si>
@@ -1430,24 +1352,12 @@
     <t>95 Pyke Road, Manawatu</t>
   </si>
   <si>
-    <t>40 Campbell Place, Marton, 4710</t>
-  </si>
-  <si>
     <t>51 Southdown Drive, Martinborough</t>
   </si>
   <si>
     <t>41 Kowhai Street, Castelcliff, Whanganui, 4501</t>
   </si>
   <si>
-    <t>178 Kilkern Road, Marton</t>
-  </si>
-  <si>
-    <t>1086148 - 00064275 - DG Label</t>
-  </si>
-  <si>
-    <t>15B Aitken Street, Bulls</t>
-  </si>
-  <si>
     <t>1086155 - 00059130 - DG Label</t>
   </si>
   <si>
@@ -1457,12 +1367,6 @@
     <t>38C Grove Road, Ashhurst</t>
   </si>
   <si>
-    <t>1086152 - 00063160 - DG Label</t>
-  </si>
-  <si>
-    <t>14 Twiss Road, Bulls</t>
-  </si>
-  <si>
     <t>633 Turakina Valley Road, Turakina</t>
   </si>
   <si>
@@ -1652,9 +1556,6 @@
     <t>283 Cambridge Avenue, Ashhurst</t>
   </si>
   <si>
-    <t>628 Pukepapa Road, Marton</t>
-  </si>
-  <si>
     <t>43 Tennyson Avenue, Kelvin Grove</t>
   </si>
   <si>
@@ -1670,9 +1571,6 @@
     <t>1078322 - DG Labelling request - 00038395</t>
   </si>
   <si>
-    <t>1085963 - 00057948 - DG Label</t>
-  </si>
-  <si>
     <t>1086655 - 00064086 - DG Label</t>
   </si>
   <si>
@@ -1721,12 +1619,6 @@
     <t>455A Taonui Road, Colyton</t>
   </si>
   <si>
-    <t>1086647 - 00056580 - DG Label</t>
-  </si>
-  <si>
-    <t>714 Waimutu Road, Turakina</t>
-  </si>
-  <si>
     <t>1086645 - 00055182 - DG Label</t>
   </si>
   <si>
@@ -1793,12 +1685,6 @@
     <t>58B London Street, Kimbolton</t>
   </si>
   <si>
-    <t>1086617 - 00050999 - DG Label</t>
-  </si>
-  <si>
-    <t>26 Tirimoana Place, Otamatea</t>
-  </si>
-  <si>
     <t>1086616 - 00061593 - DG Label</t>
   </si>
   <si>
@@ -1863,12 +1749,6 @@
   </si>
   <si>
     <t>4A Cedar Crescent, Feilding</t>
-  </si>
-  <si>
-    <t>1087123 - 00059710 - DG Label</t>
-  </si>
-  <si>
-    <t>5 Blennerville Close, Marton</t>
   </si>
   <si>
     <t>1087122 - 00056485 - DG Label</t>
@@ -2373,7 +2253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C327"/>
+  <dimension ref="A1:C307"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2390,590 +2270,590 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C8" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C16" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B19" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C20" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C34" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B35" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C38" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C42" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B44" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C44" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C45" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B47" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C47" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B49" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B52" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C52" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C53" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="C54" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -2981,10 +2861,10 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -2995,7 +2875,7 @@
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -3003,10 +2883,10 @@
         <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -3014,10 +2894,10 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -3025,10 +2905,10 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C59" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -3036,10 +2916,10 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -3047,21 +2927,21 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>245</v>
+        <v>241</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" t="s">
         <v>11</v>
       </c>
-      <c r="B62" t="s">
-        <v>252</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>245</v>
+      <c r="C62" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -3069,43 +2949,43 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>248</v>
       </c>
       <c r="C63" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="C64" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C65" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
         <v>16</v>
       </c>
-      <c r="B66" t="s">
-        <v>254</v>
-      </c>
       <c r="C66" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -3113,21 +2993,21 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>255</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>246</v>
       </c>
       <c r="C68" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -3135,21 +3015,21 @@
         <v>20</v>
       </c>
       <c r="B69" t="s">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="C69" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" t="s">
         <v>22</v>
       </c>
-      <c r="B70" t="s">
-        <v>258</v>
-      </c>
       <c r="C70" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -3157,274 +3037,274 @@
         <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>259</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B74" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C75" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C76" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C78" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C80" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C82" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B83" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C83" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B84" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C84" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C85" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C87" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B89" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C89" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B90" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B91" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C92" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C94" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="C95" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
@@ -3432,43 +3312,43 @@
         <v>72</v>
       </c>
       <c r="B96" t="s">
-        <v>73</v>
+        <v>245</v>
       </c>
       <c r="C96" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>73</v>
+      </c>
+      <c r="B97" t="s">
         <v>74</v>
       </c>
-      <c r="B97" t="s">
-        <v>75</v>
-      </c>
       <c r="C97" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98" t="s">
         <v>76</v>
       </c>
-      <c r="B98" t="s">
-        <v>77</v>
-      </c>
       <c r="C98" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>77</v>
+      </c>
+      <c r="B99" t="s">
         <v>78</v>
       </c>
-      <c r="B99" t="s">
-        <v>256</v>
-      </c>
       <c r="C99" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
@@ -3476,197 +3356,197 @@
         <v>79</v>
       </c>
       <c r="B100" t="s">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="C100" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C101" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C103" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B104" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C104" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B105" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C105" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C106" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B108" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C108" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B109" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C109" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C110" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B111" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C111" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C115" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C116" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>436</v>
       </c>
       <c r="C117" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
@@ -3677,7 +3557,7 @@
         <v>115</v>
       </c>
       <c r="C118" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
@@ -3688,7 +3568,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
@@ -3699,7 +3579,7 @@
         <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
@@ -3710,7 +3590,7 @@
         <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
@@ -3718,197 +3598,197 @@
         <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>462</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C123" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C124" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C125" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C126" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="C127" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="B128" t="s">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="C128" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="B129" t="s">
-        <v>136</v>
+        <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>137</v>
+        <v>258</v>
       </c>
       <c r="B130" t="s">
-        <v>138</v>
+        <v>257</v>
       </c>
       <c r="C130" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="C131" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="C132" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B133" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C133" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B134" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C134" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B135" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C135" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B136" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C136" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B137" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C137" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="B138" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="C138" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="B139" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C139" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -3919,7 +3799,7 @@
         <v>284</v>
       </c>
       <c r="C140" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -3930,7 +3810,7 @@
         <v>282</v>
       </c>
       <c r="C141" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -3941,7 +3821,7 @@
         <v>280</v>
       </c>
       <c r="C142" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -3952,172 +3832,172 @@
         <v>278</v>
       </c>
       <c r="C143" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="B144" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="C144" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="B145" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="C145" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B146" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="C146" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B147" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C148" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B149" t="s">
-        <v>296</v>
+        <v>438</v>
       </c>
       <c r="C149" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B150" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B151" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C151" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="C152" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B153" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="C153" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B154" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>464</v>
+        <v>506</v>
       </c>
       <c r="C155" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
+        <v>307</v>
+      </c>
+      <c r="B156" t="s">
         <v>308</v>
       </c>
-      <c r="B156" t="s">
-        <v>309</v>
-      </c>
       <c r="C156" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
+        <v>309</v>
+      </c>
+      <c r="B157" t="s">
         <v>310</v>
       </c>
-      <c r="B157" t="s">
-        <v>311</v>
-      </c>
       <c r="C157" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
+        <v>311</v>
+      </c>
+      <c r="B158" t="s">
         <v>312</v>
       </c>
-      <c r="B158" t="s">
-        <v>465</v>
-      </c>
       <c r="C158" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4128,7 +4008,7 @@
         <v>314</v>
       </c>
       <c r="C159" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4139,7 +4019,7 @@
         <v>316</v>
       </c>
       <c r="C160" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4150,7 +4030,7 @@
         <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4161,7 +4041,7 @@
         <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4172,7 +4052,7 @@
         <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4180,395 +4060,395 @@
         <v>323</v>
       </c>
       <c r="B164" t="s">
-        <v>539</v>
+        <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B165" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B166" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B168" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C168" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B169" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C169" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B170" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C170" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B172" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C172" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B173" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C173" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B174" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C174" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B175" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C175" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C176" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C177" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B178" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B179" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B181" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B182" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B183" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B184" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C184" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B185" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C185" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B186" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C186" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B187" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C187" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B188" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C188" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B189" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C189" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C190" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B191" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C191" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B192" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B193" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C193" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B194" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C194" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B195" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C195" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B196" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C196" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B197" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C197" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B198" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C198" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B199" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="C199" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -4579,7 +4459,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -4590,7 +4470,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -4601,7 +4481,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -4612,7 +4492,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -4623,7 +4503,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -4634,7 +4514,7 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
@@ -4645,7 +4525,7 @@
         <v>407</v>
       </c>
       <c r="C206" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
@@ -4656,7 +4536,7 @@
         <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -4667,62 +4547,62 @@
         <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="B209" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C209" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="B210" t="s">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="C210" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B211" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C211" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B212" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C212" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B213" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C213" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -4730,131 +4610,131 @@
         <v>421</v>
       </c>
       <c r="B214" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C214" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B215" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C215" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B216" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C216" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B217" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C217" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="B218" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="C218" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B219" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C219" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B220" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C220" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B221" t="s">
-        <v>436</v>
+        <v>504</v>
       </c>
       <c r="C221" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="B222" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="C222" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B223" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="C223" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B224" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C224" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B225" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C225" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -4862,175 +4742,175 @@
         <v>448</v>
       </c>
       <c r="B226" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C226" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B227" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C227" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B228" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C228" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B229" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="C229" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="B230" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C230" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="B231" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C231" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B232" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C232" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B233" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C233" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B234" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C234" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
+        <v>466</v>
+      </c>
+      <c r="B235" t="s">
         <v>467</v>
       </c>
-      <c r="B235" t="s">
-        <v>468</v>
-      </c>
       <c r="C235" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B236" t="s">
-        <v>536</v>
+        <v>474</v>
       </c>
       <c r="C236" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B237" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C237" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B238" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C238" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B239" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C239" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B240" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C240" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B241" t="s">
         <v>479</v>
       </c>
       <c r="C241" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -5041,7 +4921,7 @@
         <v>481</v>
       </c>
       <c r="C242" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
@@ -5052,7 +4932,7 @@
         <v>483</v>
       </c>
       <c r="C243" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
@@ -5063,7 +4943,7 @@
         <v>485</v>
       </c>
       <c r="C244" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
@@ -5074,304 +4954,304 @@
         <v>487</v>
       </c>
       <c r="C245" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="B246" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="C246" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B247" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C247" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B248" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C248" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B249" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C249" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B250" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C250" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B251" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="C251" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="B252" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="C252" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B253" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C253" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B254" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C254" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="B255" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C255" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B256" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C256" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B257" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C257" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B258" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C258" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B259" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C259" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B260" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C260" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B261" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C261" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="B262" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="C262" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="B263" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="C263" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B264" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C264" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" t="s">
         <v>529</v>
       </c>
-      <c r="B265" t="s">
-        <v>528</v>
-      </c>
       <c r="C265" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B266" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C266" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B267" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C267" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="B268" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="C268" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="B269" t="s">
-        <v>520</v>
+        <v>537</v>
       </c>
       <c r="C269" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B270" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C270" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B271" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C271" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
+        <v>542</v>
+      </c>
+      <c r="B272" t="s">
         <v>543</v>
       </c>
-      <c r="B272" t="s">
-        <v>537</v>
-      </c>
       <c r="C272" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
@@ -5382,7 +5262,7 @@
         <v>545</v>
       </c>
       <c r="C273" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -5393,7 +5273,7 @@
         <v>547</v>
       </c>
       <c r="C274" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
@@ -5404,7 +5284,7 @@
         <v>549</v>
       </c>
       <c r="C275" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
@@ -5415,7 +5295,7 @@
         <v>551</v>
       </c>
       <c r="C276" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
@@ -5426,73 +5306,73 @@
         <v>553</v>
       </c>
       <c r="C277" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B278" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C278" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B279" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C279" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B280" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C280" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B281" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C281" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B282" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C282" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="B283" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C283" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
@@ -5503,7 +5383,7 @@
         <v>567</v>
       </c>
       <c r="C284" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -5514,7 +5394,7 @@
         <v>569</v>
       </c>
       <c r="C285" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -5525,7 +5405,7 @@
         <v>571</v>
       </c>
       <c r="C286" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -5536,7 +5416,7 @@
         <v>573</v>
       </c>
       <c r="C287" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -5547,7 +5427,7 @@
         <v>575</v>
       </c>
       <c r="C288" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -5558,7 +5438,7 @@
         <v>577</v>
       </c>
       <c r="C289" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -5569,7 +5449,7 @@
         <v>579</v>
       </c>
       <c r="C290" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
@@ -5580,7 +5460,7 @@
         <v>581</v>
       </c>
       <c r="C291" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
@@ -5591,7 +5471,7 @@
         <v>583</v>
       </c>
       <c r="C292" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
@@ -5602,381 +5482,161 @@
         <v>585</v>
       </c>
       <c r="C293" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="B294" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="C294" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="B295" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="C295" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="B296" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="C296" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B297" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C297" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B298" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C298" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B299" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C299" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B300" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="C300" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B301" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C301" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B302" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C302" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B303" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="C303" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="B304" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="C304" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="B305" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="C305" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="B306" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="C306" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="B307" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="C307" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
-        <v>614</v>
-      </c>
-      <c r="B308" t="s">
-        <v>615</v>
-      </c>
-      <c r="C308" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
-        <v>616</v>
-      </c>
-      <c r="B309" t="s">
-        <v>617</v>
-      </c>
-      <c r="C309" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310" t="s">
-        <v>618</v>
-      </c>
-      <c r="B310" t="s">
-        <v>619</v>
-      </c>
-      <c r="C310" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
-        <v>620</v>
-      </c>
-      <c r="B311" t="s">
-        <v>621</v>
-      </c>
-      <c r="C311" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
-        <v>622</v>
-      </c>
-      <c r="B312" t="s">
-        <v>623</v>
-      </c>
-      <c r="C312" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313" t="s">
-        <v>624</v>
-      </c>
-      <c r="B313" t="s">
-        <v>625</v>
-      </c>
-      <c r="C313" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314" t="s">
-        <v>653</v>
-      </c>
-      <c r="B314" t="s">
-        <v>652</v>
-      </c>
-      <c r="C314" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315" t="s">
-        <v>651</v>
-      </c>
-      <c r="B315" t="s">
-        <v>650</v>
-      </c>
-      <c r="C315" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316" t="s">
-        <v>649</v>
-      </c>
-      <c r="B316" t="s">
-        <v>648</v>
-      </c>
-      <c r="C316" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317" t="s">
-        <v>647</v>
-      </c>
-      <c r="B317" t="s">
-        <v>646</v>
-      </c>
-      <c r="C317" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
-        <v>645</v>
-      </c>
-      <c r="B318" t="s">
-        <v>644</v>
-      </c>
-      <c r="C318" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
-        <v>643</v>
-      </c>
-      <c r="B319" t="s">
-        <v>642</v>
-      </c>
-      <c r="C319" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320" t="s">
-        <v>641</v>
-      </c>
-      <c r="B320" t="s">
-        <v>640</v>
-      </c>
-      <c r="C320" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
-        <v>639</v>
-      </c>
-      <c r="B321" t="s">
-        <v>638</v>
-      </c>
-      <c r="C321" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A322" t="s">
-        <v>637</v>
-      </c>
-      <c r="B322" t="s">
-        <v>636</v>
-      </c>
-      <c r="C322" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A323" t="s">
-        <v>635</v>
-      </c>
-      <c r="B323" t="s">
-        <v>634</v>
-      </c>
-      <c r="C323" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A324" t="s">
-        <v>633</v>
-      </c>
-      <c r="B324" t="s">
-        <v>632</v>
-      </c>
-      <c r="C324" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A325" t="s">
-        <v>631</v>
-      </c>
-      <c r="B325" t="s">
-        <v>630</v>
-      </c>
-      <c r="C325" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A326" t="s">
-        <v>629</v>
-      </c>
-      <c r="B326" t="s">
-        <v>628</v>
-      </c>
-      <c r="C326" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A327" t="s">
-        <v>627</v>
-      </c>
-      <c r="B327" t="s">
-        <v>626</v>
-      </c>
-      <c r="C327" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="762" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C7C1B3-901F-49FD-B64D-E6228AD323DC}"/>
+  <xr:revisionPtr revIDLastSave="800" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDED2A53-D47E-454B-9AB6-0633B2B75B54}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="630">
   <si>
     <t>Job</t>
   </si>
@@ -80,12 +80,6 @@
     <t>1084083 - 00057507 - DG Label</t>
   </si>
   <si>
-    <t>1084080 - 00054165 - DG Label</t>
-  </si>
-  <si>
-    <t>1084079 - 00059083 - DG Label</t>
-  </si>
-  <si>
     <t>1084059 - 00051796 - DG Label</t>
   </si>
   <si>
@@ -482,12 +476,6 @@
     <t>18 Ataahua Place, Featherston</t>
   </si>
   <si>
-    <t>1082675 - 00025196 - DG Label</t>
-  </si>
-  <si>
-    <t>241 Kahuterawa Road, Linton</t>
-  </si>
-  <si>
     <t>1082671 - 00016526 - DG Label</t>
   </si>
   <si>
@@ -767,12 +755,6 @@
     <t>89 Dublin Street, Martinborough</t>
   </si>
   <si>
-    <t>4 Wake Place, Aokautere</t>
-  </si>
-  <si>
-    <t>5 Castlebridge Lane, Aokautere</t>
-  </si>
-  <si>
     <t>46A Main Street, Greytown</t>
   </si>
   <si>
@@ -1881,6 +1863,72 @@
   </si>
   <si>
     <t>1087151 - 00053065 - DG Label</t>
+  </si>
+  <si>
+    <t>1087281 - 00067739 - DG Label</t>
+  </si>
+  <si>
+    <t>11A Ake Ake Avenue, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087279 - 00059033 - DG Label</t>
+  </si>
+  <si>
+    <t>9 Baton Place, Highbury</t>
+  </si>
+  <si>
+    <t>1087277 - 00059378 - DG Label</t>
+  </si>
+  <si>
+    <t>408 Albert Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087274 - 00055245 - DG Label</t>
+  </si>
+  <si>
+    <t>219a Hinekura Road, Hinakura</t>
+  </si>
+  <si>
+    <t>1087269 - 00052068 - DG Label</t>
+  </si>
+  <si>
+    <t>54 Burgundy Drive, Martinborough</t>
+  </si>
+  <si>
+    <t>1087312 - 00062120 - DG Label</t>
+  </si>
+  <si>
+    <t>14 Fitzherbert East Road, Aokautere</t>
+  </si>
+  <si>
+    <t>1087301 - 00043534 - DG Label</t>
+  </si>
+  <si>
+    <t>42 Harrison Street, Whanganui</t>
+  </si>
+  <si>
+    <t>1087300 - 00055403 - DG Label</t>
+  </si>
+  <si>
+    <t>15 Florin Lane, Rongotea</t>
+  </si>
+  <si>
+    <t>1087299 - 00065802 - DG Label</t>
+  </si>
+  <si>
+    <t>69 Marne Street, Hokowhitu</t>
+  </si>
+  <si>
+    <t>1087298 - 00065746 - DG Label</t>
+  </si>
+  <si>
+    <t>25 Highbury Avenue, Highbury</t>
+  </si>
+  <si>
+    <t>1087297 - 00065704 - DG Label</t>
+  </si>
+  <si>
+    <t>32 Armagh Terrace, Marton</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1971,22 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1934,6 +1997,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2253,13 +2320,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C307"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2270,1635 +2337,1635 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B15" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C15" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B17" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B19" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C20" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C29" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C30" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="C34" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C36" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C38" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C42" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C43" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B47" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C47" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C49" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B50" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C52" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>233</v>
       </c>
       <c r="C56" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C57" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B59" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C59" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C60" t="s">
-        <v>234</v>
+        <v>237</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>241</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>234</v>
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>242</v>
       </c>
       <c r="C62" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="C63" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B64" t="s">
-        <v>242</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C65" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>241</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C67" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>246</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>247</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C70" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C73" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C74" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C75" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C76" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C77" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C80" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C81" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C84" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C85" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C86" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C87" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B88" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C88" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B89" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C89" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C90" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
       <c r="C92" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>239</v>
       </c>
       <c r="C93" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C94" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="C95" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>76</v>
       </c>
       <c r="C96" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B97" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C97" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B98" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C99" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B101" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C102" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B103" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C103" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C104" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B105" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C105" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C106" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B107" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C107" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B108" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C111" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C112" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C113" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>108</v>
+        <v>430</v>
       </c>
       <c r="C114" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>436</v>
+        <v>117</v>
       </c>
       <c r="C117" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B118" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C118" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C120" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C121" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B122" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C122" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>259</v>
       </c>
       <c r="B123" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C123" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>126</v>
+        <v>258</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
+        <v>257</v>
       </c>
       <c r="C124" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="C125" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B126" t="s">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="C126" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B127" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C127" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B128" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C128" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B129" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C129" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B130" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C130" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B131" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C131" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B132" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C132" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C133" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="B134" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C134" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B135" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C135" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B136" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C136" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B137" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C137" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B138" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C138" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B139" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C139" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B140" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C140" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B141" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C141" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B142" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C142" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B143" t="s">
-        <v>278</v>
+        <v>431</v>
       </c>
       <c r="C143" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B144" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="C144" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="B145" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C145" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C146" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
+        <v>290</v>
+      </c>
+      <c r="B147" t="s">
         <v>291</v>
       </c>
-      <c r="B147" t="s">
-        <v>292</v>
-      </c>
       <c r="C147" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
+        <v>292</v>
+      </c>
+      <c r="B148" t="s">
         <v>293</v>
       </c>
-      <c r="B148" t="s">
-        <v>294</v>
-      </c>
       <c r="C148" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
+        <v>294</v>
+      </c>
+      <c r="B149" t="s">
         <v>295</v>
       </c>
-      <c r="B149" t="s">
-        <v>438</v>
-      </c>
       <c r="C149" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -3909,7 +3976,7 @@
         <v>297</v>
       </c>
       <c r="C150" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -3920,7 +3987,7 @@
         <v>299</v>
       </c>
       <c r="C151" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -3928,43 +3995,43 @@
         <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>301</v>
+        <v>500</v>
       </c>
       <c r="C152" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
+        <v>301</v>
+      </c>
+      <c r="B153" t="s">
         <v>302</v>
       </c>
-      <c r="B153" t="s">
-        <v>303</v>
-      </c>
       <c r="C153" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
+        <v>303</v>
+      </c>
+      <c r="B154" t="s">
         <v>304</v>
       </c>
-      <c r="B154" t="s">
-        <v>305</v>
-      </c>
       <c r="C154" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
+        <v>305</v>
+      </c>
+      <c r="B155" t="s">
         <v>306</v>
       </c>
-      <c r="B155" t="s">
-        <v>506</v>
-      </c>
       <c r="C155" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -3975,7 +4042,7 @@
         <v>308</v>
       </c>
       <c r="C156" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -3986,7 +4053,7 @@
         <v>310</v>
       </c>
       <c r="C157" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -3997,7 +4064,7 @@
         <v>312</v>
       </c>
       <c r="C158" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4008,7 +4075,7 @@
         <v>314</v>
       </c>
       <c r="C159" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4019,7 +4086,7 @@
         <v>316</v>
       </c>
       <c r="C160" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4030,7 +4097,7 @@
         <v>318</v>
       </c>
       <c r="C161" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4041,7 +4108,7 @@
         <v>320</v>
       </c>
       <c r="C162" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4052,7 +4119,7 @@
         <v>322</v>
       </c>
       <c r="C163" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4063,7 +4130,7 @@
         <v>324</v>
       </c>
       <c r="C164" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4074,7 +4141,7 @@
         <v>326</v>
       </c>
       <c r="C165" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4085,7 +4152,7 @@
         <v>328</v>
       </c>
       <c r="C166" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4096,7 +4163,7 @@
         <v>330</v>
       </c>
       <c r="C167" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -4107,7 +4174,7 @@
         <v>332</v>
       </c>
       <c r="C168" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -4118,7 +4185,7 @@
         <v>334</v>
       </c>
       <c r="C169" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -4129,7 +4196,7 @@
         <v>336</v>
       </c>
       <c r="C170" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -4140,7 +4207,7 @@
         <v>338</v>
       </c>
       <c r="C171" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -4151,7 +4218,7 @@
         <v>340</v>
       </c>
       <c r="C172" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -4162,7 +4229,7 @@
         <v>342</v>
       </c>
       <c r="C173" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -4173,7 +4240,7 @@
         <v>344</v>
       </c>
       <c r="C174" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
@@ -4184,7 +4251,7 @@
         <v>346</v>
       </c>
       <c r="C175" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
@@ -4195,7 +4262,7 @@
         <v>348</v>
       </c>
       <c r="C176" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -4206,7 +4273,7 @@
         <v>350</v>
       </c>
       <c r="C177" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -4217,7 +4284,7 @@
         <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
@@ -4228,7 +4295,7 @@
         <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
@@ -4239,7 +4306,7 @@
         <v>356</v>
       </c>
       <c r="C180" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -4250,7 +4317,7 @@
         <v>358</v>
       </c>
       <c r="C181" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -4261,7 +4328,7 @@
         <v>360</v>
       </c>
       <c r="C182" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -4272,7 +4339,7 @@
         <v>362</v>
       </c>
       <c r="C183" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -4283,7 +4350,7 @@
         <v>364</v>
       </c>
       <c r="C184" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -4294,7 +4361,7 @@
         <v>366</v>
       </c>
       <c r="C185" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -4305,7 +4372,7 @@
         <v>368</v>
       </c>
       <c r="C186" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -4316,7 +4383,7 @@
         <v>370</v>
       </c>
       <c r="C187" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -4327,7 +4394,7 @@
         <v>372</v>
       </c>
       <c r="C188" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -4338,7 +4405,7 @@
         <v>374</v>
       </c>
       <c r="C189" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -4349,7 +4416,7 @@
         <v>376</v>
       </c>
       <c r="C190" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -4360,7 +4427,7 @@
         <v>378</v>
       </c>
       <c r="C191" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -4371,7 +4438,7 @@
         <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -4382,7 +4449,7 @@
         <v>382</v>
       </c>
       <c r="C193" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -4393,7 +4460,7 @@
         <v>384</v>
       </c>
       <c r="C194" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -4404,7 +4471,7 @@
         <v>386</v>
       </c>
       <c r="C195" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -4412,43 +4479,43 @@
         <v>387</v>
       </c>
       <c r="B196" t="s">
-        <v>388</v>
+        <v>338</v>
       </c>
       <c r="C196" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
+        <v>388</v>
+      </c>
+      <c r="B197" t="s">
         <v>389</v>
       </c>
-      <c r="B197" t="s">
-        <v>390</v>
-      </c>
       <c r="C197" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
+        <v>390</v>
+      </c>
+      <c r="B198" t="s">
         <v>391</v>
       </c>
-      <c r="B198" t="s">
-        <v>392</v>
-      </c>
       <c r="C198" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
+        <v>392</v>
+      </c>
+      <c r="B199" t="s">
         <v>393</v>
       </c>
-      <c r="B199" t="s">
-        <v>344</v>
-      </c>
       <c r="C199" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -4459,7 +4526,7 @@
         <v>395</v>
       </c>
       <c r="C200" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -4470,7 +4537,7 @@
         <v>397</v>
       </c>
       <c r="C201" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -4481,7 +4548,7 @@
         <v>399</v>
       </c>
       <c r="C202" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -4492,7 +4559,7 @@
         <v>401</v>
       </c>
       <c r="C203" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -4503,7 +4570,7 @@
         <v>403</v>
       </c>
       <c r="C204" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -4514,183 +4581,183 @@
         <v>405</v>
       </c>
       <c r="C205" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>406</v>
+        <v>425</v>
       </c>
       <c r="B206" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="C206" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="B207" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="C207" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B208" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C208" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B209" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C209" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B210" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C210" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B211" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C211" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B212" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C212" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B213" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C213" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B214" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C214" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B215" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C215" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B216" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C216" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B217" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C217" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B218" t="s">
-        <v>412</v>
+        <v>498</v>
       </c>
       <c r="C218" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B219" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C219" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B220" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C220" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
+        <v>438</v>
+      </c>
+      <c r="B221" t="s">
         <v>439</v>
       </c>
-      <c r="B221" t="s">
-        <v>504</v>
-      </c>
       <c r="C221" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
@@ -4701,18 +4768,18 @@
         <v>441</v>
       </c>
       <c r="C222" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
+        <v>442</v>
+      </c>
+      <c r="B223" t="s">
         <v>443</v>
       </c>
-      <c r="B223" t="s">
-        <v>442</v>
-      </c>
       <c r="C223" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -4723,7 +4790,7 @@
         <v>445</v>
       </c>
       <c r="C224" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -4734,7 +4801,7 @@
         <v>447</v>
       </c>
       <c r="C225" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -4745,7 +4812,7 @@
         <v>449</v>
       </c>
       <c r="C226" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
@@ -4756,7 +4823,7 @@
         <v>451</v>
       </c>
       <c r="C227" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
@@ -4767,7 +4834,7 @@
         <v>453</v>
       </c>
       <c r="C228" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
@@ -4778,7 +4845,7 @@
         <v>455</v>
       </c>
       <c r="C229" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
@@ -4789,7 +4856,7 @@
         <v>457</v>
       </c>
       <c r="C230" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
@@ -4800,7 +4867,7 @@
         <v>459</v>
       </c>
       <c r="C231" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
@@ -4811,106 +4878,106 @@
         <v>461</v>
       </c>
       <c r="C232" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B233" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C233" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B234" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C234" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B235" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C235" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B236" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C236" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B237" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C237" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B238" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C238" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B239" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C239" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B240" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C240" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B241" t="s">
         <v>479</v>
       </c>
       <c r="C241" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
@@ -4921,150 +4988,150 @@
         <v>481</v>
       </c>
       <c r="C242" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B243" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C243" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B244" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="C244" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B245" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C245" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B246" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C246" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B247" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C247" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="B248" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="C248" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B249" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C249" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B250" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C250" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B251" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C251" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B252" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C252" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="B253" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="C253" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B254" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C254" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
+        <v>508</v>
+      </c>
+      <c r="B255" t="s">
         <v>509</v>
       </c>
-      <c r="B255" t="s">
-        <v>507</v>
-      </c>
       <c r="C255" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -5075,7 +5142,7 @@
         <v>511</v>
       </c>
       <c r="C256" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -5086,7 +5153,7 @@
         <v>513</v>
       </c>
       <c r="C257" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -5097,7 +5164,7 @@
         <v>515</v>
       </c>
       <c r="C258" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -5108,7 +5175,7 @@
         <v>517</v>
       </c>
       <c r="C259" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -5119,7 +5186,7 @@
         <v>519</v>
       </c>
       <c r="C260" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -5130,7 +5197,7 @@
         <v>521</v>
       </c>
       <c r="C261" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -5141,7 +5208,7 @@
         <v>523</v>
       </c>
       <c r="C262" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
@@ -5152,7 +5219,7 @@
         <v>525</v>
       </c>
       <c r="C263" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
@@ -5163,7 +5230,7 @@
         <v>527</v>
       </c>
       <c r="C264" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
@@ -5174,7 +5241,7 @@
         <v>529</v>
       </c>
       <c r="C265" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
@@ -5185,7 +5252,7 @@
         <v>531</v>
       </c>
       <c r="C266" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
@@ -5196,7 +5263,7 @@
         <v>533</v>
       </c>
       <c r="C267" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
@@ -5207,7 +5274,7 @@
         <v>535</v>
       </c>
       <c r="C268" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
@@ -5218,7 +5285,7 @@
         <v>537</v>
       </c>
       <c r="C269" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
@@ -5229,7 +5296,7 @@
         <v>539</v>
       </c>
       <c r="C270" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
@@ -5240,7 +5307,7 @@
         <v>541</v>
       </c>
       <c r="C271" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
@@ -5251,7 +5318,7 @@
         <v>543</v>
       </c>
       <c r="C272" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
@@ -5262,7 +5329,7 @@
         <v>545</v>
       </c>
       <c r="C273" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
@@ -5273,106 +5340,106 @@
         <v>547</v>
       </c>
       <c r="C274" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B275" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C275" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B276" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C276" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B277" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C277" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="B278" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="C278" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="B279" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C279" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="B280" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C280" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B281" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C281" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B282" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="C282" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B283" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="C283" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
@@ -5383,7 +5450,7 @@
         <v>567</v>
       </c>
       <c r="C284" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
@@ -5394,7 +5461,7 @@
         <v>569</v>
       </c>
       <c r="C285" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
@@ -5405,7 +5472,7 @@
         <v>571</v>
       </c>
       <c r="C286" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
@@ -5416,7 +5483,7 @@
         <v>573</v>
       </c>
       <c r="C287" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
@@ -5427,7 +5494,7 @@
         <v>575</v>
       </c>
       <c r="C288" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
@@ -5438,7 +5505,7 @@
         <v>577</v>
       </c>
       <c r="C289" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
@@ -5449,197 +5516,295 @@
         <v>579</v>
       </c>
       <c r="C290" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="B291" t="s">
-        <v>581</v>
+        <v>606</v>
       </c>
       <c r="C291" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="B292" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="C292" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>584</v>
+        <v>603</v>
       </c>
       <c r="B293" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="C293" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="B294" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C294" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="B295" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C295" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="B296" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C296" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="B297" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="C297" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="B298" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="C298" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="B299" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C299" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="B300" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="C300" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="B301" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="C301" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="B302" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="C302" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
       <c r="B303" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="C303" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
       <c r="B304" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C304" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="B305" t="s">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="C305" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B306" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="C306" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>587</v>
+        <v>612</v>
       </c>
       <c r="B307" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="C307" t="s">
-        <v>233</v>
+        <v>230</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>614</v>
+      </c>
+      <c r="B308" t="s">
+        <v>615</v>
+      </c>
+      <c r="C308" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>616</v>
+      </c>
+      <c r="B309" t="s">
+        <v>617</v>
+      </c>
+      <c r="C309" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>618</v>
+      </c>
+      <c r="B310" t="s">
+        <v>619</v>
+      </c>
+      <c r="C310" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>620</v>
+      </c>
+      <c r="B311" t="s">
+        <v>621</v>
+      </c>
+      <c r="C311" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>622</v>
+      </c>
+      <c r="B312" t="s">
+        <v>623</v>
+      </c>
+      <c r="C312" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>624</v>
+      </c>
+      <c r="B313" t="s">
+        <v>625</v>
+      </c>
+      <c r="C313" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>626</v>
+      </c>
+      <c r="B314" t="s">
+        <v>627</v>
+      </c>
+      <c r="C314" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>628</v>
+      </c>
+      <c r="B315" t="s">
+        <v>629</v>
+      </c>
+      <c r="C315" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>"NOT(COUNTIF($D$:$E,B1)=0)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D35">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>COUNTIF($B$1:$B$1000,D1048544)&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="800" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDED2A53-D47E-454B-9AB6-0633B2B75B54}"/>
+  <xr:revisionPtr revIDLastSave="808" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916EF7ED-6FC6-409E-89EE-0AE5EADDD4A3}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="642">
   <si>
     <t>Job</t>
   </si>
@@ -1929,6 +1929,42 @@
   </si>
   <si>
     <t>32 Armagh Terrace, Marton</t>
+  </si>
+  <si>
+    <t>1087365 - 00065152 - DG Label</t>
+  </si>
+  <si>
+    <t>68 Florence Avenue, Palmerston North</t>
+  </si>
+  <si>
+    <t>1087364 - 00066700 - DG Label</t>
+  </si>
+  <si>
+    <t>25C Stonebridge Heights, Feilding</t>
+  </si>
+  <si>
+    <t>1087363 - 00066901 - DG Label</t>
+  </si>
+  <si>
+    <t>40 Parkland Crescent, Terrace End</t>
+  </si>
+  <si>
+    <t>1087362 - 00056559 - DG Label</t>
+  </si>
+  <si>
+    <t>256 Manaia Road, Solway</t>
+  </si>
+  <si>
+    <t>1087361 - 00053770 - DG Label</t>
+  </si>
+  <si>
+    <t>1384 Taonui Road, Pohangina</t>
+  </si>
+  <si>
+    <t>1087360 - 00068226 - DG Label</t>
+  </si>
+  <si>
+    <t>64 Buick Crescent, Awapuni</t>
   </si>
 </sst>
 </file>
@@ -1997,10 +2033,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2320,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C315"/>
+  <dimension ref="A1:C321"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5791,6 +5823,72 @@
         <v>629</v>
       </c>
       <c r="C315" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>630</v>
+      </c>
+      <c r="B316" t="s">
+        <v>631</v>
+      </c>
+      <c r="C316" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>632</v>
+      </c>
+      <c r="B317" t="s">
+        <v>633</v>
+      </c>
+      <c r="C317" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>634</v>
+      </c>
+      <c r="B318" t="s">
+        <v>635</v>
+      </c>
+      <c r="C318" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>636</v>
+      </c>
+      <c r="B319" t="s">
+        <v>637</v>
+      </c>
+      <c r="C319" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>638</v>
+      </c>
+      <c r="B320" t="s">
+        <v>639</v>
+      </c>
+      <c r="C320" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>640</v>
+      </c>
+      <c r="B321" t="s">
+        <v>641</v>
+      </c>
+      <c r="C321" t="s">
         <v>230</v>
       </c>
     </row>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="808" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916EF7ED-6FC6-409E-89EE-0AE5EADDD4A3}"/>
+  <xr:revisionPtr revIDLastSave="859" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302C61AB-06AA-4486-97B1-3F0BEA548FF7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="630">
   <si>
     <t>Job</t>
   </si>
@@ -104,12 +104,6 @@
     <t>49 Weld Street, Martinborough</t>
   </si>
   <si>
-    <t>1083909 - 00051891 - DG Label</t>
-  </si>
-  <si>
-    <t>16 Mersey Street, Rongotea</t>
-  </si>
-  <si>
     <t>1083906 - 00047054 - DG Label</t>
   </si>
   <si>
@@ -128,12 +122,6 @@
     <t>54 Richmond Road, Carterton</t>
   </si>
   <si>
-    <t>1083901 - 00055289 - DG Label</t>
-  </si>
-  <si>
-    <t>353 Kahuterawa Road, Linton</t>
-  </si>
-  <si>
     <t>1083900 - 00049959 - DG Label</t>
   </si>
   <si>
@@ -362,21 +350,12 @@
     <t>346 State Highway 1, Foxton</t>
   </si>
   <si>
-    <t>1083184 - 00055338 - DG Label</t>
-  </si>
-  <si>
-    <t>499 Taikorea Road, Glen Oroua</t>
-  </si>
-  <si>
     <t>1083182 - 00055894 - DG Label</t>
   </si>
   <si>
     <t>22 South Street, Feilding</t>
   </si>
   <si>
-    <t>1083181 - 00049193 - DG Label</t>
-  </si>
-  <si>
     <t>1083037 - 00042253 - DG Label</t>
   </si>
   <si>
@@ -401,12 +380,6 @@
     <t>43 Fitzherbert Street, Featherston</t>
   </si>
   <si>
-    <t>1082897 - 00051235 - DG Label</t>
-  </si>
-  <si>
-    <t>87A Worcester Street, Ashhurst</t>
-  </si>
-  <si>
     <t>1082873 - 00037497 - DG Label</t>
   </si>
   <si>
@@ -440,12 +413,6 @@
     <t>682 ROBERTS LINE, PALMERSTON NORTH</t>
   </si>
   <si>
-    <t>1082787 - 00054940 - DG Label</t>
-  </si>
-  <si>
-    <t>69 Duncan Road, Rongotea</t>
-  </si>
-  <si>
     <t>1082687 - 00058152 - DG Label</t>
   </si>
   <si>
@@ -1331,9 +1298,6 @@
     <t>93 Chester Road, Clareville</t>
   </si>
   <si>
-    <t>95 Pyke Road, Manawatu</t>
-  </si>
-  <si>
     <t>51 Southdown Drive, Martinborough</t>
   </si>
   <si>
@@ -1541,9 +1505,6 @@
     <t>43 Tennyson Avenue, Kelvin Grove</t>
   </si>
   <si>
-    <t>70 Duddings Line, Featherson</t>
-  </si>
-  <si>
     <t xml:space="preserve">4a wellesley st </t>
   </si>
   <si>
@@ -1965,6 +1926,9 @@
   </si>
   <si>
     <t>64 Buick Crescent, Awapuni</t>
+  </si>
+  <si>
+    <t>70 Duddings Line, Tauwharenīkau 5771</t>
   </si>
 </sst>
 </file>
@@ -2007,11 +1971,77 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF002060"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2352,13 +2382,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C321"/>
+  <dimension ref="A1:C315"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2369,986 +2398,986 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C4" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C8" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C9" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="C13" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="B14" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C15" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C17" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="C34" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C41" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C42" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B43" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C43" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C44" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B46" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C46" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B49" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C50" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C51" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>231</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>222</v>
       </c>
       <c r="C55" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C56" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C57" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>236</v>
-      </c>
-      <c r="C59" t="s">
-        <v>230</v>
+        <v>226</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>230</v>
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="C61" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
-        <v>242</v>
+        <v>14</v>
       </c>
       <c r="C62" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="C64" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B66" t="s">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="C66" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B71" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C72" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C73" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C74" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C76" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C79" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C80" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C81" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C82" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C83" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C84" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C85" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C86" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B88" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C88" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>64</v>
+        <v>227</v>
       </c>
       <c r="C89" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>228</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
@@ -3359,7 +3388,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
@@ -3367,362 +3396,362 @@
         <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C94" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C96" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C97" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C98" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C100" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B101" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C101" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B102" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C102" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B103" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C103" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C104" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B105" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C105" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B106" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C106" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B107" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B108" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C108" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C109" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C110" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C111" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C113" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>430</v>
+        <v>114</v>
       </c>
       <c r="C114" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C115" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C116" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>116</v>
+        <v>248</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C117" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="C118" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>244</v>
       </c>
       <c r="C119" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="B120" t="s">
-        <v>123</v>
+        <v>242</v>
       </c>
       <c r="C120" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>240</v>
       </c>
       <c r="C121" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="B122" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="C122" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>236</v>
       </c>
       <c r="C123" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B124" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="C124" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
@@ -3733,7 +3762,7 @@
         <v>255</v>
       </c>
       <c r="C125" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
@@ -3744,7 +3773,7 @@
         <v>253</v>
       </c>
       <c r="C126" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
@@ -3755,7 +3784,7 @@
         <v>251</v>
       </c>
       <c r="C127" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
@@ -3766,172 +3795,172 @@
         <v>249</v>
       </c>
       <c r="C128" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="B129" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="C129" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="B130" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="C130" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>268</v>
+      </c>
+      <c r="B131" t="s">
         <v>267</v>
       </c>
-      <c r="B131" t="s">
-        <v>266</v>
-      </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
+        <v>266</v>
+      </c>
+      <c r="B132" t="s">
         <v>265</v>
       </c>
-      <c r="B132" t="s">
-        <v>264</v>
-      </c>
       <c r="C132" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" t="s">
         <v>263</v>
       </c>
-      <c r="B133" t="s">
-        <v>262</v>
-      </c>
       <c r="C133" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
+        <v>262</v>
+      </c>
+      <c r="B134" t="s">
         <v>261</v>
       </c>
-      <c r="B134" t="s">
-        <v>260</v>
-      </c>
       <c r="C134" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="B135" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="B136" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="C136" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B137" t="s">
-        <v>278</v>
+        <v>419</v>
       </c>
       <c r="C137" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B138" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C138" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B139" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C139" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B140" t="s">
-        <v>272</v>
+        <v>420</v>
       </c>
       <c r="C140" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B141" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C141" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C142" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>283</v>
+      </c>
+      <c r="B143" t="s">
         <v>284</v>
       </c>
-      <c r="B143" t="s">
-        <v>431</v>
-      </c>
       <c r="C143" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -3942,7 +3971,7 @@
         <v>286</v>
       </c>
       <c r="C144" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -3953,7 +3982,7 @@
         <v>288</v>
       </c>
       <c r="C145" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -3961,10 +3990,10 @@
         <v>289</v>
       </c>
       <c r="B146" t="s">
-        <v>432</v>
+        <v>629</v>
       </c>
       <c r="C146" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -3975,7 +4004,7 @@
         <v>291</v>
       </c>
       <c r="C147" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -3986,7 +4015,7 @@
         <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -3997,7 +4026,7 @@
         <v>295</v>
       </c>
       <c r="C149" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4008,7 +4037,7 @@
         <v>297</v>
       </c>
       <c r="C150" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4019,7 +4048,7 @@
         <v>299</v>
       </c>
       <c r="C151" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4027,428 +4056,428 @@
         <v>300</v>
       </c>
       <c r="B152" t="s">
-        <v>500</v>
+        <v>301</v>
       </c>
       <c r="C152" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C153" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B154" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B155" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C155" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B156" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B158" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C158" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B159" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C159" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B160" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C160" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B161" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C161" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C162" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B163" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C163" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B164" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C164" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B165" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C165" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B166" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C166" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B167" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C167" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B168" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C168" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B169" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C169" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B170" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C170" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C171" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B172" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C172" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B173" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C173" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B174" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C174" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B175" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C175" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B176" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C176" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B177" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C177" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B178" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C178" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B179" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C179" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B180" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C180" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B181" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C181" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B182" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C182" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B183" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C183" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B184" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C184" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B185" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C185" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B186" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C186" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B187" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C187" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B188" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C188" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C189" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B190" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="C190" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -4459,7 +4488,7 @@
         <v>378</v>
       </c>
       <c r="C191" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -4470,7 +4499,7 @@
         <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -4481,7 +4510,7 @@
         <v>382</v>
       </c>
       <c r="C193" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -4492,7 +4521,7 @@
         <v>384</v>
       </c>
       <c r="C194" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -4503,7 +4532,7 @@
         <v>386</v>
       </c>
       <c r="C195" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -4511,98 +4540,98 @@
         <v>387</v>
       </c>
       <c r="B196" t="s">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="C196" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B197" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C197" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B198" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C198" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B199" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C199" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="B200" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="C200" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B201" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C201" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B202" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C202" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B203" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C203" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B204" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C204" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -4610,153 +4639,153 @@
         <v>404</v>
       </c>
       <c r="B205" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C205" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B206" t="s">
-        <v>424</v>
+        <v>401</v>
       </c>
       <c r="C206" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
       <c r="B207" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="C207" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>421</v>
+        <v>398</v>
       </c>
       <c r="B208" t="s">
-        <v>420</v>
+        <v>397</v>
       </c>
       <c r="C208" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>419</v>
+        <v>396</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>395</v>
       </c>
       <c r="C209" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B210" t="s">
         <v>416</v>
       </c>
       <c r="C210" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B211" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C211" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B212" t="s">
-        <v>412</v>
+        <v>486</v>
       </c>
       <c r="C212" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B213" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C213" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="B214" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="C214" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="B215" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C215" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B216" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C216" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B217" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C217" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
+        <v>432</v>
+      </c>
+      <c r="B218" t="s">
         <v>433</v>
       </c>
-      <c r="B218" t="s">
-        <v>498</v>
-      </c>
       <c r="C218" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
@@ -4767,18 +4796,18 @@
         <v>435</v>
       </c>
       <c r="C219" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
+        <v>436</v>
+      </c>
+      <c r="B220" t="s">
         <v>437</v>
       </c>
-      <c r="B220" t="s">
-        <v>436</v>
-      </c>
       <c r="C220" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
@@ -4789,7 +4818,7 @@
         <v>439</v>
       </c>
       <c r="C221" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
@@ -4800,7 +4829,7 @@
         <v>441</v>
       </c>
       <c r="C222" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
@@ -4811,7 +4840,7 @@
         <v>443</v>
       </c>
       <c r="C223" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
@@ -4822,7 +4851,7 @@
         <v>445</v>
       </c>
       <c r="C224" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
@@ -4833,7 +4862,7 @@
         <v>447</v>
       </c>
       <c r="C225" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
@@ -4844,568 +4873,568 @@
         <v>449</v>
       </c>
       <c r="C226" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B227" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C227" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B228" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C228" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B229" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C229" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B230" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C230" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B231" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C231" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B232" t="s">
         <v>461</v>
       </c>
       <c r="C232" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B233" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C233" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B234" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C234" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B235" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C235" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B236" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C236" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B237" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C237" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="B238" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="C238" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B239" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C239" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B240" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C240" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B241" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C241" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B242" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="C242" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="B243" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="C243" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="B244" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="C244" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B245" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C245" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B246" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C246" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B247" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C247" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B248" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C248" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B249" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C249" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="B250" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="C250" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B251" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C251" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B252" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C252" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
+        <v>503</v>
+      </c>
+      <c r="B253" t="s">
         <v>504</v>
       </c>
-      <c r="B253" t="s">
-        <v>505</v>
-      </c>
       <c r="C253" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
+        <v>505</v>
+      </c>
+      <c r="B254" t="s">
         <v>506</v>
       </c>
-      <c r="B254" t="s">
-        <v>507</v>
-      </c>
       <c r="C254" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
+        <v>507</v>
+      </c>
+      <c r="B255" t="s">
         <v>508</v>
       </c>
-      <c r="B255" t="s">
-        <v>509</v>
-      </c>
       <c r="C255" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
+        <v>509</v>
+      </c>
+      <c r="B256" t="s">
         <v>510</v>
       </c>
-      <c r="B256" t="s">
-        <v>511</v>
-      </c>
       <c r="C256" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
+        <v>511</v>
+      </c>
+      <c r="B257" t="s">
         <v>512</v>
       </c>
-      <c r="B257" t="s">
-        <v>513</v>
-      </c>
       <c r="C257" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
+        <v>513</v>
+      </c>
+      <c r="B258" t="s">
         <v>514</v>
       </c>
-      <c r="B258" t="s">
-        <v>515</v>
-      </c>
       <c r="C258" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
+        <v>515</v>
+      </c>
+      <c r="B259" t="s">
         <v>516</v>
       </c>
-      <c r="B259" t="s">
-        <v>517</v>
-      </c>
       <c r="C259" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
+        <v>517</v>
+      </c>
+      <c r="B260" t="s">
         <v>518</v>
       </c>
-      <c r="B260" t="s">
-        <v>519</v>
-      </c>
       <c r="C260" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
+        <v>519</v>
+      </c>
+      <c r="B261" t="s">
         <v>520</v>
       </c>
-      <c r="B261" t="s">
-        <v>521</v>
-      </c>
       <c r="C261" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
+        <v>521</v>
+      </c>
+      <c r="B262" t="s">
         <v>522</v>
       </c>
-      <c r="B262" t="s">
-        <v>523</v>
-      </c>
       <c r="C262" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
+        <v>523</v>
+      </c>
+      <c r="B263" t="s">
         <v>524</v>
       </c>
-      <c r="B263" t="s">
-        <v>525</v>
-      </c>
       <c r="C263" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
+        <v>525</v>
+      </c>
+      <c r="B264" t="s">
         <v>526</v>
       </c>
-      <c r="B264" t="s">
-        <v>527</v>
-      </c>
       <c r="C264" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
+        <v>527</v>
+      </c>
+      <c r="B265" t="s">
         <v>528</v>
       </c>
-      <c r="B265" t="s">
-        <v>529</v>
-      </c>
       <c r="C265" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
+        <v>529</v>
+      </c>
+      <c r="B266" t="s">
         <v>530</v>
       </c>
-      <c r="B266" t="s">
-        <v>531</v>
-      </c>
       <c r="C266" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
+        <v>531</v>
+      </c>
+      <c r="B267" t="s">
         <v>532</v>
       </c>
-      <c r="B267" t="s">
-        <v>533</v>
-      </c>
       <c r="C267" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
+        <v>533</v>
+      </c>
+      <c r="B268" t="s">
         <v>534</v>
       </c>
-      <c r="B268" t="s">
-        <v>535</v>
-      </c>
       <c r="C268" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="B269" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C269" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B270" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C270" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B271" t="s">
         <v>541</v>
       </c>
       <c r="C271" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B272" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C272" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B273" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C273" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B274" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C274" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B275" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C275" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B276" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C276" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B277" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C277" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
@@ -5413,496 +5442,420 @@
         <v>553</v>
       </c>
       <c r="B278" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C278" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B279" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C279" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B280" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="C280" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
+        <v>559</v>
+      </c>
+      <c r="B281" t="s">
         <v>560</v>
       </c>
-      <c r="B281" t="s">
-        <v>561</v>
-      </c>
       <c r="C281" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
+        <v>561</v>
+      </c>
+      <c r="B282" t="s">
         <v>562</v>
       </c>
-      <c r="B282" t="s">
-        <v>563</v>
-      </c>
       <c r="C282" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
+        <v>563</v>
+      </c>
+      <c r="B283" t="s">
         <v>564</v>
       </c>
-      <c r="B283" t="s">
-        <v>565</v>
-      </c>
       <c r="C283" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
+        <v>565</v>
+      </c>
+      <c r="B284" t="s">
         <v>566</v>
       </c>
-      <c r="B284" t="s">
-        <v>567</v>
-      </c>
       <c r="C284" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="B285" t="s">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="C285" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="B286" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="C286" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B287" t="s">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="C287" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B288" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="C288" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C289" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B290" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C290" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="B291" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="C291" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>605</v>
+        <v>580</v>
       </c>
       <c r="B292" t="s">
-        <v>604</v>
+        <v>579</v>
       </c>
       <c r="C292" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>603</v>
+        <v>578</v>
       </c>
       <c r="B293" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="C293" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="B294" t="s">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="C294" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="B295" t="s">
-        <v>598</v>
+        <v>573</v>
       </c>
       <c r="C295" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>597</v>
+        <v>572</v>
       </c>
       <c r="B296" t="s">
-        <v>596</v>
+        <v>571</v>
       </c>
       <c r="C296" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>595</v>
+        <v>570</v>
       </c>
       <c r="B297" t="s">
-        <v>594</v>
+        <v>569</v>
       </c>
       <c r="C297" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>593</v>
+        <v>568</v>
       </c>
       <c r="B298" t="s">
-        <v>592</v>
+        <v>567</v>
       </c>
       <c r="C298" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B299" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C299" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="B300" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="C300" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B301" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="C301" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B302" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="C302" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="B303" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="C303" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="B304" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="C304" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
+        <v>607</v>
+      </c>
+      <c r="B305" t="s">
         <v>608</v>
       </c>
-      <c r="B305" t="s">
-        <v>609</v>
-      </c>
       <c r="C305" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
+        <v>609</v>
+      </c>
+      <c r="B306" t="s">
         <v>610</v>
       </c>
-      <c r="B306" t="s">
-        <v>611</v>
-      </c>
       <c r="C306" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
+        <v>611</v>
+      </c>
+      <c r="B307" t="s">
         <v>612</v>
       </c>
-      <c r="B307" t="s">
-        <v>613</v>
-      </c>
       <c r="C307" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
+        <v>613</v>
+      </c>
+      <c r="B308" t="s">
         <v>614</v>
       </c>
-      <c r="B308" t="s">
-        <v>615</v>
-      </c>
       <c r="C308" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
+        <v>615</v>
+      </c>
+      <c r="B309" t="s">
         <v>616</v>
       </c>
-      <c r="B309" t="s">
-        <v>617</v>
-      </c>
       <c r="C309" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
+        <v>617</v>
+      </c>
+      <c r="B310" t="s">
         <v>618</v>
       </c>
-      <c r="B310" t="s">
-        <v>619</v>
-      </c>
       <c r="C310" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
+        <v>619</v>
+      </c>
+      <c r="B311" t="s">
         <v>620</v>
       </c>
-      <c r="B311" t="s">
-        <v>621</v>
-      </c>
       <c r="C311" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
+        <v>621</v>
+      </c>
+      <c r="B312" t="s">
         <v>622</v>
       </c>
-      <c r="B312" t="s">
-        <v>623</v>
-      </c>
       <c r="C312" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
+        <v>623</v>
+      </c>
+      <c r="B313" t="s">
         <v>624</v>
       </c>
-      <c r="B313" t="s">
-        <v>625</v>
-      </c>
       <c r="C313" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
+        <v>625</v>
+      </c>
+      <c r="B314" t="s">
         <v>626</v>
       </c>
-      <c r="B314" t="s">
-        <v>627</v>
-      </c>
       <c r="C314" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
+        <v>627</v>
+      </c>
+      <c r="B315" t="s">
         <v>628</v>
       </c>
-      <c r="B315" t="s">
-        <v>629</v>
-      </c>
       <c r="C315" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A316" t="s">
-        <v>630</v>
-      </c>
-      <c r="B316" t="s">
-        <v>631</v>
-      </c>
-      <c r="C316" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A317" t="s">
-        <v>632</v>
-      </c>
-      <c r="B317" t="s">
-        <v>633</v>
-      </c>
-      <c r="C317" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A318" t="s">
-        <v>634</v>
-      </c>
-      <c r="B318" t="s">
-        <v>635</v>
-      </c>
-      <c r="C318" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A319" t="s">
-        <v>636</v>
-      </c>
-      <c r="B319" t="s">
-        <v>637</v>
-      </c>
-      <c r="C319" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A320" t="s">
-        <v>638</v>
-      </c>
-      <c r="B320" t="s">
-        <v>639</v>
-      </c>
-      <c r="C320" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A321" t="s">
-        <v>640</v>
-      </c>
-      <c r="B321" t="s">
-        <v>641</v>
-      </c>
-      <c r="C321" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="expression" dxfId="1" priority="4">
-      <formula>"NOT(COUNTIF($D$:$E,B1)=0)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D35">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>COUNTIF($B$1:$B$1000,D1048544)&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="859" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302C61AB-06AA-4486-97B1-3F0BEA548FF7}"/>
+  <xr:revisionPtr revIDLastSave="866" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D03A7069-A587-4F5B-A9E3-1AC9A020EDF5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="616">
   <si>
     <t>Job</t>
   </si>
@@ -50,12 +50,6 @@
     <t>1084531 - 00060784 - DG Label</t>
   </si>
   <si>
-    <t>1084467 - 00055841 - DG Label</t>
-  </si>
-  <si>
-    <t>685 Kairanga Bunnythorpe Road</t>
-  </si>
-  <si>
     <t>1084466 - 00057025 - DG Label</t>
   </si>
   <si>
@@ -77,9 +71,6 @@
     <t>The Lido</t>
   </si>
   <si>
-    <t>1084083 - 00057507 - DG Label</t>
-  </si>
-  <si>
     <t>1084059 - 00051796 - DG Label</t>
   </si>
   <si>
@@ -326,12 +317,6 @@
     <t>142A Dublin Street, Martinborough</t>
   </si>
   <si>
-    <t>1083503 - 00055234 - DG Label</t>
-  </si>
-  <si>
-    <t>570 Roberts Line, Kelvin Grove</t>
-  </si>
-  <si>
     <t>1083189 - 00055734 - DG Label</t>
   </si>
   <si>
@@ -407,12 +392,6 @@
     <t>56 FREDERICK ST, CARTERTON</t>
   </si>
   <si>
-    <t>1082789 - 00029633 - DG Label</t>
-  </si>
-  <si>
-    <t>682 ROBERTS LINE, PALMERSTON NORTH</t>
-  </si>
-  <si>
     <t>1082687 - 00058152 - DG Label</t>
   </si>
   <si>
@@ -734,9 +713,6 @@
     <t>16 Madden Place, Masterton</t>
   </si>
   <si>
-    <t>3 Paterson Lane, Kelvin Grove</t>
-  </si>
-  <si>
     <t>Nga Waka Winery, Martinborough</t>
   </si>
   <si>
@@ -971,12 +947,6 @@
     <t>4 Boydfield Street, Whanganui East</t>
   </si>
   <si>
-    <t>1085553 - 00057633 - DG Label</t>
-  </si>
-  <si>
-    <t>2a Buxton Road, Westmere</t>
-  </si>
-  <si>
     <t>1085551 - 00062161 - DG Label</t>
   </si>
   <si>
@@ -1061,12 +1031,6 @@
     <t>85 Watt Street, Featherston</t>
   </si>
   <si>
-    <t>1085734 - 00025403 - DG Label</t>
-  </si>
-  <si>
-    <t>7B Brassey Road, Saint Johns Hill</t>
-  </si>
-  <si>
     <t>1085733 - 00031648 - DG Label</t>
   </si>
   <si>
@@ -1644,12 +1608,6 @@
   </si>
   <si>
     <t>80 Jellicoe Street, Greytown</t>
-  </si>
-  <si>
-    <t>1 Kawau Place, Otamatea</t>
-  </si>
-  <si>
-    <t>1086965 - 00061608 - DG Label</t>
   </si>
   <si>
     <t>31 Koromiko Road, Gonville</t>
@@ -1971,88 +1929,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2382,7 +2259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C315"/>
+  <dimension ref="A1:C308"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -2398,590 +2275,590 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="B6" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C11" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B15" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B19" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C31" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="C32" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C36" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B37" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C39" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B41" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C42" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C50" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="C52" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -2989,10 +2866,10 @@
         <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -3000,10 +2877,10 @@
         <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C56" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -3011,10 +2888,10 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>224</v>
-      </c>
-      <c r="C57" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -3022,912 +2899,912 @@
         <v>8</v>
       </c>
       <c r="B58" t="s">
-        <v>225</v>
+        <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>226</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>219</v>
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="C62" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>229</v>
+        <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B65" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C70" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B75" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C75" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B77" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C83" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="C86" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>221</v>
       </c>
       <c r="C87" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B88" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B89" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="C89" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>228</v>
+        <v>69</v>
       </c>
       <c r="C90" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C92" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B94" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C94" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C95" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C96" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C98" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B99" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C99" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B100" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B101" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C101" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B102" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C102" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B104" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C104" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C105" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B106" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C106" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C107" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C108" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C110" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C111" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C112" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>238</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="C115" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>235</v>
       </c>
       <c r="B116" t="s">
-        <v>118</v>
+        <v>234</v>
       </c>
       <c r="C116" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B117" t="s">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="C117" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="B118" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="C118" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="B119" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="C119" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="B120" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C120" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B121" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B122" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C122" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B123" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C123" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B124" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C124" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B125" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C125" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B126" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C126" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="B127" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B128" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C128" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="C129" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="B130" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="C130" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B131" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C131" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="B132" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C132" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B133" t="s">
-        <v>263</v>
+        <v>407</v>
       </c>
       <c r="C133" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B134" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C134" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B135" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C135" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B136" t="s">
-        <v>257</v>
+        <v>408</v>
       </c>
       <c r="C136" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B137" t="s">
-        <v>419</v>
+        <v>272</v>
       </c>
       <c r="C137" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
+        <v>273</v>
+      </c>
+      <c r="B138" t="s">
         <v>274</v>
       </c>
-      <c r="B138" t="s">
-        <v>275</v>
-      </c>
       <c r="C138" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
+        <v>275</v>
+      </c>
+      <c r="B139" t="s">
         <v>276</v>
       </c>
-      <c r="B139" t="s">
-        <v>277</v>
-      </c>
       <c r="C139" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>277</v>
+      </c>
+      <c r="B140" t="s">
         <v>278</v>
       </c>
-      <c r="B140" t="s">
-        <v>420</v>
-      </c>
       <c r="C140" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -3938,7 +3815,7 @@
         <v>280</v>
       </c>
       <c r="C141" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -3946,54 +3823,54 @@
         <v>281</v>
       </c>
       <c r="B142" t="s">
-        <v>282</v>
+        <v>615</v>
       </c>
       <c r="C142" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>282</v>
+      </c>
+      <c r="B143" t="s">
         <v>283</v>
       </c>
-      <c r="B143" t="s">
-        <v>284</v>
-      </c>
       <c r="C143" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>284</v>
+      </c>
+      <c r="B144" t="s">
         <v>285</v>
       </c>
-      <c r="B144" t="s">
-        <v>286</v>
-      </c>
       <c r="C144" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
+        <v>286</v>
+      </c>
+      <c r="B145" t="s">
         <v>287</v>
       </c>
-      <c r="B145" t="s">
-        <v>288</v>
-      </c>
       <c r="C145" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
+        <v>288</v>
+      </c>
+      <c r="B146" t="s">
         <v>289</v>
       </c>
-      <c r="B146" t="s">
-        <v>629</v>
-      </c>
       <c r="C146" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -4004,7 +3881,7 @@
         <v>291</v>
       </c>
       <c r="C147" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -4015,7 +3892,7 @@
         <v>293</v>
       </c>
       <c r="C148" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -4026,7 +3903,7 @@
         <v>295</v>
       </c>
       <c r="C149" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -4037,7 +3914,7 @@
         <v>297</v>
       </c>
       <c r="C150" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -4048,7 +3925,7 @@
         <v>299</v>
       </c>
       <c r="C151" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
@@ -4059,7 +3936,7 @@
         <v>301</v>
       </c>
       <c r="C152" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -4070,7 +3947,7 @@
         <v>303</v>
       </c>
       <c r="C153" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
@@ -4081,7 +3958,7 @@
         <v>305</v>
       </c>
       <c r="C154" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -4092,7 +3969,7 @@
         <v>307</v>
       </c>
       <c r="C155" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -4103,7 +3980,7 @@
         <v>309</v>
       </c>
       <c r="C156" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
@@ -4114,7 +3991,7 @@
         <v>311</v>
       </c>
       <c r="C157" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
@@ -4125,7 +4002,7 @@
         <v>313</v>
       </c>
       <c r="C158" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
@@ -4136,7 +4013,7 @@
         <v>315</v>
       </c>
       <c r="C159" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
@@ -4147,7 +4024,7 @@
         <v>317</v>
       </c>
       <c r="C160" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -4158,7 +4035,7 @@
         <v>319</v>
       </c>
       <c r="C161" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -4169,7 +4046,7 @@
         <v>321</v>
       </c>
       <c r="C162" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -4180,7 +4057,7 @@
         <v>323</v>
       </c>
       <c r="C163" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -4191,7 +4068,7 @@
         <v>325</v>
       </c>
       <c r="C164" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
@@ -4202,7 +4079,7 @@
         <v>327</v>
       </c>
       <c r="C165" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -4213,7 +4090,7 @@
         <v>329</v>
       </c>
       <c r="C166" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
@@ -4224,7 +4101,7 @@
         <v>331</v>
       </c>
       <c r="C167" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
@@ -4235,7 +4112,7 @@
         <v>333</v>
       </c>
       <c r="C168" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
@@ -4246,7 +4123,7 @@
         <v>335</v>
       </c>
       <c r="C169" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
@@ -4257,7 +4134,7 @@
         <v>337</v>
       </c>
       <c r="C170" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
@@ -4268,7 +4145,7 @@
         <v>339</v>
       </c>
       <c r="C171" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
@@ -4279,7 +4156,7 @@
         <v>341</v>
       </c>
       <c r="C172" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -4290,7 +4167,7 @@
         <v>343</v>
       </c>
       <c r="C173" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -4301,7 +4178,7 @@
         <v>345</v>
       </c>
       <c r="C174" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
@@ -4312,7 +4189,7 @@
         <v>347</v>
       </c>
       <c r="C175" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
@@ -4323,7 +4200,7 @@
         <v>349</v>
       </c>
       <c r="C176" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -4334,7 +4211,7 @@
         <v>351</v>
       </c>
       <c r="C177" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -4345,7 +4222,7 @@
         <v>353</v>
       </c>
       <c r="C178" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
@@ -4356,7 +4233,7 @@
         <v>355</v>
       </c>
       <c r="C179" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
@@ -4367,7 +4244,7 @@
         <v>357</v>
       </c>
       <c r="C180" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -4378,7 +4255,7 @@
         <v>359</v>
       </c>
       <c r="C181" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -4389,7 +4266,7 @@
         <v>361</v>
       </c>
       <c r="C182" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -4400,7 +4277,7 @@
         <v>363</v>
       </c>
       <c r="C183" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -4408,76 +4285,76 @@
         <v>364</v>
       </c>
       <c r="B184" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="C184" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
+        <v>365</v>
+      </c>
+      <c r="B185" t="s">
         <v>366</v>
       </c>
-      <c r="B185" t="s">
-        <v>367</v>
-      </c>
       <c r="C185" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
+        <v>367</v>
+      </c>
+      <c r="B186" t="s">
         <v>368</v>
       </c>
-      <c r="B186" t="s">
-        <v>369</v>
-      </c>
       <c r="C186" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
+        <v>369</v>
+      </c>
+      <c r="B187" t="s">
         <v>370</v>
       </c>
-      <c r="B187" t="s">
-        <v>371</v>
-      </c>
       <c r="C187" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
+        <v>371</v>
+      </c>
+      <c r="B188" t="s">
         <v>372</v>
       </c>
-      <c r="B188" t="s">
-        <v>373</v>
-      </c>
       <c r="C188" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
+        <v>373</v>
+      </c>
+      <c r="B189" t="s">
         <v>374</v>
       </c>
-      <c r="B189" t="s">
-        <v>375</v>
-      </c>
       <c r="C189" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
+        <v>375</v>
+      </c>
+      <c r="B190" t="s">
         <v>376</v>
       </c>
-      <c r="B190" t="s">
-        <v>327</v>
-      </c>
       <c r="C190" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -4488,7 +4365,7 @@
         <v>378</v>
       </c>
       <c r="C191" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -4499,7 +4376,7 @@
         <v>380</v>
       </c>
       <c r="C192" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -4510,216 +4387,216 @@
         <v>382</v>
       </c>
       <c r="C193" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="B194" t="s">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="C194" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="B195" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="C195" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="B196" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C196" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B197" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C197" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B198" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C198" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B199" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C199" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="B200" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="C200" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="B201" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="C201" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B202" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C202" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B203" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="C203" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B204" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C204" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B205" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C205" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B206" t="s">
-        <v>401</v>
+        <v>474</v>
       </c>
       <c r="C206" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B207" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C207" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="B208" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C208" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="B209" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="C209" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B210" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C210" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B211" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C211" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
+        <v>420</v>
+      </c>
+      <c r="B212" t="s">
         <v>421</v>
       </c>
-      <c r="B212" t="s">
-        <v>486</v>
-      </c>
       <c r="C212" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
@@ -4730,18 +4607,18 @@
         <v>423</v>
       </c>
       <c r="C213" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
+        <v>424</v>
+      </c>
+      <c r="B214" t="s">
         <v>425</v>
       </c>
-      <c r="B214" t="s">
-        <v>424</v>
-      </c>
       <c r="C214" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.35">
@@ -4752,7 +4629,7 @@
         <v>427</v>
       </c>
       <c r="C215" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.35">
@@ -4763,7 +4640,7 @@
         <v>429</v>
       </c>
       <c r="C216" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.35">
@@ -4774,7 +4651,7 @@
         <v>431</v>
       </c>
       <c r="C217" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.35">
@@ -4785,7 +4662,7 @@
         <v>433</v>
       </c>
       <c r="C218" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.35">
@@ -4796,7 +4673,7 @@
         <v>435</v>
       </c>
       <c r="C219" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.35">
@@ -4807,293 +4684,293 @@
         <v>437</v>
       </c>
       <c r="C220" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B221" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C221" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B222" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C222" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B223" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C223" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B224" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C224" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B225" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C225" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B226" t="s">
         <v>449</v>
       </c>
       <c r="C226" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B227" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C227" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B228" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C228" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B229" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C229" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B230" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C230" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B231" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C231" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="B232" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="C232" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B233" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C233" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B234" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C234" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B235" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C235" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B236" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="C236" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="B237" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="C237" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="B238" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="C238" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B239" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C239" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B240" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C240" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B241" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C241" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B242" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C242" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="B243" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C243" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="B244" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="C244" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B245" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C245" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
+        <v>489</v>
+      </c>
+      <c r="B246" t="s">
         <v>490</v>
       </c>
-      <c r="B246" t="s">
-        <v>488</v>
-      </c>
       <c r="C246" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.35">
@@ -5104,7 +4981,7 @@
         <v>492</v>
       </c>
       <c r="C247" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.35">
@@ -5115,7 +4992,7 @@
         <v>494</v>
       </c>
       <c r="C248" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.35">
@@ -5126,7 +5003,7 @@
         <v>496</v>
       </c>
       <c r="C249" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.35">
@@ -5137,7 +5014,7 @@
         <v>498</v>
       </c>
       <c r="C250" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.35">
@@ -5148,7 +5025,7 @@
         <v>500</v>
       </c>
       <c r="C251" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.35">
@@ -5159,7 +5036,7 @@
         <v>502</v>
       </c>
       <c r="C252" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.35">
@@ -5170,7 +5047,7 @@
         <v>504</v>
       </c>
       <c r="C253" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.35">
@@ -5181,7 +5058,7 @@
         <v>506</v>
       </c>
       <c r="C254" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.35">
@@ -5192,7 +5069,7 @@
         <v>508</v>
       </c>
       <c r="C255" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.35">
@@ -5203,7 +5080,7 @@
         <v>510</v>
       </c>
       <c r="C256" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.35">
@@ -5214,7 +5091,7 @@
         <v>512</v>
       </c>
       <c r="C257" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.35">
@@ -5225,7 +5102,7 @@
         <v>514</v>
       </c>
       <c r="C258" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.35">
@@ -5236,7 +5113,7 @@
         <v>516</v>
       </c>
       <c r="C259" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.35">
@@ -5247,7 +5124,7 @@
         <v>518</v>
       </c>
       <c r="C260" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.35">
@@ -5258,7 +5135,7 @@
         <v>520</v>
       </c>
       <c r="C261" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.35">
@@ -5269,62 +5146,62 @@
         <v>522</v>
       </c>
       <c r="C262" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B263" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="C263" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B264" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C264" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
+        <v>528</v>
+      </c>
+      <c r="B265" t="s">
         <v>527</v>
       </c>
-      <c r="B265" t="s">
-        <v>528</v>
-      </c>
       <c r="C265" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B266" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C266" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="B267" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="C267" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.35">
@@ -5335,73 +5212,73 @@
         <v>534</v>
       </c>
       <c r="C268" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="B269" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="C269" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="B270" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C270" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B271" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C271" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B272" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C272" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B273" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="C273" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B274" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="C274" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.35">
@@ -5412,7 +5289,7 @@
         <v>548</v>
       </c>
       <c r="C275" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.35">
@@ -5423,7 +5300,7 @@
         <v>550</v>
       </c>
       <c r="C276" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.35">
@@ -5434,238 +5311,238 @@
         <v>552</v>
       </c>
       <c r="C277" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="B278" t="s">
-        <v>554</v>
+        <v>579</v>
       </c>
       <c r="C278" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="B279" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="C279" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="B280" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
       <c r="C280" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="B281" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C281" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="C282" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B283" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C283" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B284" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C284" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="B285" t="s">
-        <v>593</v>
+        <v>565</v>
       </c>
       <c r="C285" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="B286" t="s">
-        <v>591</v>
+        <v>563</v>
       </c>
       <c r="C286" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>590</v>
+        <v>562</v>
       </c>
       <c r="B287" t="s">
-        <v>589</v>
+        <v>561</v>
       </c>
       <c r="C287" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="B288" t="s">
-        <v>587</v>
+        <v>559</v>
       </c>
       <c r="C288" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="B289" t="s">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="C289" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="B290" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="C290" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="B291" t="s">
-        <v>581</v>
+        <v>553</v>
       </c>
       <c r="C291" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B292" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C292" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B293" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="C293" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="B294" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C294" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="B295" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C295" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="B296" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="C296" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="B297" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="C297" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>568</v>
+        <v>593</v>
       </c>
       <c r="B298" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="C298" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.35">
@@ -5676,7 +5553,7 @@
         <v>596</v>
       </c>
       <c r="C299" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.35">
@@ -5687,7 +5564,7 @@
         <v>598</v>
       </c>
       <c r="C300" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.35">
@@ -5698,7 +5575,7 @@
         <v>600</v>
       </c>
       <c r="C301" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.35">
@@ -5709,7 +5586,7 @@
         <v>602</v>
       </c>
       <c r="C302" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.35">
@@ -5720,7 +5597,7 @@
         <v>604</v>
       </c>
       <c r="C303" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.35">
@@ -5731,7 +5608,7 @@
         <v>606</v>
       </c>
       <c r="C304" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.35">
@@ -5742,7 +5619,7 @@
         <v>608</v>
       </c>
       <c r="C305" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.35">
@@ -5753,7 +5630,7 @@
         <v>610</v>
       </c>
       <c r="C306" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.35">
@@ -5764,7 +5641,7 @@
         <v>612</v>
       </c>
       <c r="C307" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.35">
@@ -5775,84 +5652,7 @@
         <v>614</v>
       </c>
       <c r="C308" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
-        <v>615</v>
-      </c>
-      <c r="B309" t="s">
-        <v>616</v>
-      </c>
-      <c r="C309" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A310" t="s">
-        <v>617</v>
-      </c>
-      <c r="B310" t="s">
-        <v>618</v>
-      </c>
-      <c r="C310" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
-        <v>619</v>
-      </c>
-      <c r="B311" t="s">
-        <v>620</v>
-      </c>
-      <c r="C311" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
-        <v>621</v>
-      </c>
-      <c r="B312" t="s">
-        <v>622</v>
-      </c>
-      <c r="C312" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A313" t="s">
-        <v>623</v>
-      </c>
-      <c r="B313" t="s">
-        <v>624</v>
-      </c>
-      <c r="C313" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A314" t="s">
-        <v>625</v>
-      </c>
-      <c r="B314" t="s">
-        <v>626</v>
-      </c>
-      <c r="C314" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A315" t="s">
-        <v>627</v>
-      </c>
-      <c r="B315" t="s">
-        <v>628</v>
-      </c>
-      <c r="C315" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="866" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D03A7069-A587-4F5B-A9E3-1AC9A020EDF5}"/>
+  <xr:revisionPtr revIDLastSave="876" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9FA2EF-4F8D-42E6-8AA8-1240CF0A8747}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="633">
   <si>
     <t>Job</t>
   </si>
@@ -1887,6 +1887,57 @@
   </si>
   <si>
     <t>70 Duddings Line, Tauwharenīkau 5771</t>
+  </si>
+  <si>
+    <t>1087504 - 00064753 - DG Label</t>
+  </si>
+  <si>
+    <t>220 Kahuterawa Road, Linton</t>
+  </si>
+  <si>
+    <t>1087503 - 00058006 - DG Label</t>
+  </si>
+  <si>
+    <t>1087501 - 00056422 - DG Label</t>
+  </si>
+  <si>
+    <t>104 Clifton Terrace, Fitzherbert</t>
+  </si>
+  <si>
+    <t>1087499 - 00062081 - DG Label</t>
+  </si>
+  <si>
+    <t>52 Clyde Crescent, Roslyn</t>
+  </si>
+  <si>
+    <t>1087498 - 00064089 - DG Label</t>
+  </si>
+  <si>
+    <t>18 Pukeko Road, Bunnythorpe</t>
+  </si>
+  <si>
+    <t>1087497 - 00057207 - DG Label</t>
+  </si>
+  <si>
+    <t>104 Slacks Road, Awapuni</t>
+  </si>
+  <si>
+    <t>1087495 - 00065119 - DG Label</t>
+  </si>
+  <si>
+    <t>69 Meridian Grove, Kelvin Grove</t>
+  </si>
+  <si>
+    <t>1087493 - 00055288 - DG Label</t>
+  </si>
+  <si>
+    <t>63 Tangimoana Beach Road, Tangimoana</t>
+  </si>
+  <si>
+    <t>1087492 - 00059113 - DG Label</t>
+  </si>
+  <si>
+    <t>577 Hughes Line, East Taratahi</t>
   </si>
 </sst>
 </file>
@@ -2259,7 +2310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C308"/>
+  <dimension ref="A1:C317"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5655,6 +5706,105 @@
         <v>212</v>
       </c>
     </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>616</v>
+      </c>
+      <c r="B309" t="s">
+        <v>617</v>
+      </c>
+      <c r="C309" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>618</v>
+      </c>
+      <c r="B310" t="s">
+        <v>404</v>
+      </c>
+      <c r="C310" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>619</v>
+      </c>
+      <c r="B311" t="s">
+        <v>620</v>
+      </c>
+      <c r="C311" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>621</v>
+      </c>
+      <c r="B312" t="s">
+        <v>622</v>
+      </c>
+      <c r="C312" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>623</v>
+      </c>
+      <c r="B313" t="s">
+        <v>624</v>
+      </c>
+      <c r="C313" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>625</v>
+      </c>
+      <c r="B314" t="s">
+        <v>626</v>
+      </c>
+      <c r="C314" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>627</v>
+      </c>
+      <c r="B315" t="s">
+        <v>628</v>
+      </c>
+      <c r="C315" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>629</v>
+      </c>
+      <c r="B316" t="s">
+        <v>630</v>
+      </c>
+      <c r="C316" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>631</v>
+      </c>
+      <c r="B317" t="s">
+        <v>632</v>
+      </c>
+      <c r="C317" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/DGS LIST.xlsx
+++ b/DGS LIST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feisst-my.sharepoint.com/personal/chisora_h_npe-tech_co_nz/Documents/Documents/NPE Tools/DG-Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="876" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A9FA2EF-4F8D-42E6-8AA8-1240CF0A8747}"/>
+  <xr:revisionPtr revIDLastSave="885" documentId="8_{CCCF0366-673B-4613-8CFF-E13952FC8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C3B1E4-595C-406C-A73B-581CD4205C02}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-11235" windowWidth="29040" windowHeight="15720" xr2:uid="{F977427A-6EEF-496F-83AC-E1A3F4E254D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="647">
   <si>
     <t>Job</t>
   </si>
@@ -1938,6 +1938,48 @@
   </si>
   <si>
     <t>577 Hughes Line, East Taratahi</t>
+  </si>
+  <si>
+    <t>1087547 - 00063691 - DG Label</t>
+  </si>
+  <si>
+    <t>30 Nicholson Drive, Kaitoke</t>
+  </si>
+  <si>
+    <t>1087546 - 00066181 - DG Label</t>
+  </si>
+  <si>
+    <t>220 Ruakokoputuna Road, Martinborough</t>
+  </si>
+  <si>
+    <t>1087545 - 00021197 - DG Label</t>
+  </si>
+  <si>
+    <t>550 Pohangina Road, Ashhurst</t>
+  </si>
+  <si>
+    <t>1087544 - 00020455 - DG Label</t>
+  </si>
+  <si>
+    <t>345 Forest Road, Parewanui</t>
+  </si>
+  <si>
+    <t>1087543 - 00019202 - DG Label</t>
+  </si>
+  <si>
+    <t>601 Oroua Valley Road, Apiti</t>
+  </si>
+  <si>
+    <t>1087542 - 00059047 - DG Label</t>
+  </si>
+  <si>
+    <t>58 Skerman Street, Marton</t>
+  </si>
+  <si>
+    <t>1087541 - 00057987 - DG Label</t>
+  </si>
+  <si>
+    <t>1688 Turakina Valley Road, Marton</t>
   </si>
 </sst>
 </file>
@@ -2310,7 +2352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6218D334-F914-43C7-B5ED-119730E8C2C7}">
-  <dimension ref="A1:C317"/>
+  <dimension ref="A1:C324"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -5805,6 +5847,83 @@
         <v>211</v>
       </c>
     </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>633</v>
+      </c>
+      <c r="B318" t="s">
+        <v>634</v>
+      </c>
+      <c r="C318" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>635</v>
+      </c>
+      <c r="B319" t="s">
+        <v>636</v>
+      </c>
+      <c r="C319" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>637</v>
+      </c>
+      <c r="B320" t="s">
+        <v>638</v>
+      </c>
+      <c r="C320" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>639</v>
+      </c>
+      <c r="B321" t="s">
+        <v>640</v>
+      </c>
+      <c r="C321" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>641</v>
+      </c>
+      <c r="B322" t="s">
+        <v>642</v>
+      </c>
+      <c r="C322" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>643</v>
+      </c>
+      <c r="B323" t="s">
+        <v>644</v>
+      </c>
+      <c r="C323" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>645</v>
+      </c>
+      <c r="B324" t="s">
+        <v>646</v>
+      </c>
+      <c r="C324" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
